--- a/Financial Analysis/EPAM.xlsx
+++ b/Financial Analysis/EPAM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D358863-7769-4E19-B859-20A238F1B61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48187BD9-3C1B-43B6-B4C5-9A0E1EB96207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{8184807C-F564-425B-AEBD-E3B1D55FAE77}"/>
   </bookViews>
@@ -293,7 +293,7 @@
     <t>Net Margin</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -406,14 +406,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -430,7 +430,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23614380" y="0"/>
+          <a:off x="24848820" y="0"/>
           <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -829,17 +829,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>149.62</v>
+        <v>153.46</v>
       </c>
       <c r="E3" s="3">
-        <v>45764</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="3">
-        <v>45785</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,10 +847,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>56.9</v>
+        <f>55.7</f>
+        <v>55.7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -859,7 +860,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>8513.3780000000006</v>
+        <v>8547.7220000000016</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -867,11 +868,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>1286.3+1.7</f>
-        <v>1288</v>
+        <f>1014.3</f>
+        <v>1014.3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -879,10 +880,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <v>25.2</v>
+        <f>25</f>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -891,7 +893,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>1262.8</v>
+        <v>989.3</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -900,7 +902,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>7250.5780000000004</v>
+        <v>7558.4220000000014</v>
       </c>
     </row>
   </sheetData>
@@ -918,7 +920,7 @@
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
     <col min="64" max="64" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="17" customWidth="1"/>
+    <col min="66" max="66" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:173" x14ac:dyDescent="0.3">
@@ -1219,20 +1221,18 @@
         <v>1248.2999999999997</v>
       </c>
       <c r="AM3" s="7">
-        <f>AI3*1.07</f>
-        <v>1247.085</v>
+        <v>1301.7</v>
       </c>
       <c r="AN3" s="7">
-        <f>AJ3*1.01</f>
-        <v>1158.066</v>
+        <v>1353.4</v>
       </c>
       <c r="AO3" s="7">
-        <f t="shared" ref="AO3:AP3" si="0">AK3*1.01</f>
-        <v>1179.175</v>
+        <f>AK3*1.18</f>
+        <v>1377.6499999999999</v>
       </c>
       <c r="AP3" s="7">
-        <f t="shared" si="0"/>
-        <v>1260.7829999999997</v>
+        <f>AL3*1.13</f>
+        <v>1410.5789999999995</v>
       </c>
       <c r="AR3" s="7">
         <f>SUM(C3:F3)</f>
@@ -1269,47 +1269,47 @@
       </c>
       <c r="BA3" s="7">
         <f>SUM(AM3:AP3)</f>
-        <v>4845.1089999999995</v>
+        <v>5443.3289999999997</v>
       </c>
       <c r="BB3" s="7">
-        <f>BA3*1.01</f>
-        <v>4893.5600899999999</v>
+        <f>BA3*1.1</f>
+        <v>5987.6619000000001</v>
       </c>
       <c r="BC3" s="7">
-        <f t="shared" ref="BC3:BK3" si="1">BB3*1.01</f>
-        <v>4942.4956909000002</v>
+        <f>BB3*1.06</f>
+        <v>6346.9216140000008</v>
       </c>
       <c r="BD3" s="7">
-        <f t="shared" si="1"/>
-        <v>4991.920647809</v>
+        <f>BC3*1.04</f>
+        <v>6600.7984785600011</v>
       </c>
       <c r="BE3" s="7">
-        <f t="shared" si="1"/>
-        <v>5041.83985428709</v>
+        <f>BD3*1.03</f>
+        <v>6798.8224329168015</v>
       </c>
       <c r="BF3" s="7">
-        <f t="shared" si="1"/>
-        <v>5092.2582528299608</v>
+        <f t="shared" ref="BF3:BK3" si="0">BE3*1.03</f>
+        <v>7002.7871059043055</v>
       </c>
       <c r="BG3" s="7">
-        <f t="shared" si="1"/>
-        <v>5143.1808353582601</v>
+        <f t="shared" si="0"/>
+        <v>7212.8707190814348</v>
       </c>
       <c r="BH3" s="7">
-        <f t="shared" si="1"/>
-        <v>5194.6126437118428</v>
+        <f t="shared" si="0"/>
+        <v>7429.2568406538776</v>
       </c>
       <c r="BI3" s="7">
-        <f t="shared" si="1"/>
-        <v>5246.5587701489612</v>
+        <f t="shared" si="0"/>
+        <v>7652.1345458734941</v>
       </c>
       <c r="BJ3" s="7">
-        <f t="shared" si="1"/>
-        <v>5299.0243578504505</v>
+        <f t="shared" si="0"/>
+        <v>7881.698582249699</v>
       </c>
       <c r="BK3" s="7">
-        <f t="shared" si="1"/>
-        <v>5352.0146014289548</v>
+        <f t="shared" si="0"/>
+        <v>8118.1495397171902</v>
       </c>
     </row>
     <row r="4" spans="2:173" x14ac:dyDescent="0.3">
@@ -1428,20 +1428,18 @@
         <v>868.3</v>
       </c>
       <c r="AM4" s="5">
-        <f>AM3-AM5</f>
-        <v>872.95950000000005</v>
+        <v>952</v>
       </c>
       <c r="AN4" s="5">
-        <f t="shared" ref="AN4:AP4" si="2">AN3-AN5</f>
-        <v>810.64620000000002</v>
+        <v>964</v>
       </c>
       <c r="AO4" s="5">
-        <f t="shared" si="2"/>
-        <v>825.4224999999999</v>
+        <f t="shared" ref="AO4:AP4" si="1">AO3-AO5</f>
+        <v>964.3549999999999</v>
       </c>
       <c r="AP4" s="5">
-        <f t="shared" si="2"/>
-        <v>882.54809999999975</v>
+        <f t="shared" si="1"/>
+        <v>987.40529999999967</v>
       </c>
       <c r="AR4" s="5">
         <f>SUM(C4:F4)</f>
@@ -1478,47 +1476,47 @@
       </c>
       <c r="BA4" s="5">
         <f>SUM(AM4:AP4)</f>
-        <v>3391.5762999999997</v>
+        <v>3867.7602999999999</v>
       </c>
       <c r="BB4" s="5">
-        <f t="shared" ref="BB4:BF4" si="3">BB3-BB5</f>
-        <v>3425.4920629999997</v>
+        <f t="shared" ref="BB4:BF4" si="2">BB3-BB5</f>
+        <v>4191.3633300000001</v>
       </c>
       <c r="BC4" s="5">
+        <f t="shared" si="2"/>
+        <v>4442.8451298000009</v>
+      </c>
+      <c r="BD4" s="5">
+        <f t="shared" si="2"/>
+        <v>4620.558934992001</v>
+      </c>
+      <c r="BE4" s="5">
+        <f t="shared" si="2"/>
+        <v>4759.1757030417612</v>
+      </c>
+      <c r="BF4" s="5">
+        <f t="shared" si="2"/>
+        <v>4901.9509741330139</v>
+      </c>
+      <c r="BG4" s="5">
+        <f t="shared" ref="BG4:BK4" si="3">BG3-BG5</f>
+        <v>5049.0095033570051</v>
+      </c>
+      <c r="BH4" s="5">
         <f t="shared" si="3"/>
-        <v>3459.7469836300002</v>
-      </c>
-      <c r="BD4" s="5">
+        <v>5200.4797884577147</v>
+      </c>
+      <c r="BI4" s="5">
         <f t="shared" si="3"/>
-        <v>3494.3444534663004</v>
-      </c>
-      <c r="BE4" s="5">
+        <v>5356.4941821114462</v>
+      </c>
+      <c r="BJ4" s="5">
         <f t="shared" si="3"/>
-        <v>3529.2878980009627</v>
-      </c>
-      <c r="BF4" s="5">
+        <v>5517.1890075747888</v>
+      </c>
+      <c r="BK4" s="5">
         <f t="shared" si="3"/>
-        <v>3564.5807769809726</v>
-      </c>
-      <c r="BG4" s="5">
-        <f t="shared" ref="BG4:BK4" si="4">BG3-BG5</f>
-        <v>3600.2265847507824</v>
-      </c>
-      <c r="BH4" s="5">
-        <f t="shared" si="4"/>
-        <v>3636.2288505982897</v>
-      </c>
-      <c r="BI4" s="5">
-        <f t="shared" si="4"/>
-        <v>3672.5911391042728</v>
-      </c>
-      <c r="BJ4" s="5">
-        <f t="shared" si="4"/>
-        <v>3709.3170504953155</v>
-      </c>
-      <c r="BK4" s="5">
-        <f t="shared" si="4"/>
-        <v>3746.4102210002684</v>
+        <v>5682.7046778020331</v>
       </c>
     </row>
     <row r="5" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1526,187 +1524,187 @@
         <v>30</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:X5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:X5" si="4">C3-C4</f>
         <v>117</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="4"/>
+        <v>103</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="4"/>
+        <v>107.5</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="4"/>
+        <v>115.30000000000001</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="4"/>
+        <v>117</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="4"/>
+        <v>128.9</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="4"/>
+        <v>138.1</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="4"/>
+        <v>145.20000000000002</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="4"/>
+        <v>146.5</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="4"/>
+        <v>156.5</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="4"/>
+        <v>167.09999999999997</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="4"/>
+        <v>185.89999999999998</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="4"/>
+        <v>176.59999999999997</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="4"/>
+        <v>195.67000000000002</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="4"/>
+        <v>210.60000000000002</v>
+      </c>
+      <c r="R5" s="7">
+        <f t="shared" si="4"/>
+        <v>222.69999999999993</v>
+      </c>
+      <c r="S5" s="7">
+        <f t="shared" si="4"/>
+        <v>227.59999999999997</v>
+      </c>
+      <c r="T5" s="7">
+        <f t="shared" si="4"/>
+        <v>212.83999999999997</v>
+      </c>
+      <c r="U5" s="7">
+        <f t="shared" si="4"/>
+        <v>228.80000000000007</v>
+      </c>
+      <c r="V5" s="7">
+        <f t="shared" si="4"/>
+        <v>257.7</v>
+      </c>
+      <c r="W5" s="7">
+        <f t="shared" si="4"/>
+        <v>261.5</v>
+      </c>
+      <c r="X5" s="7">
+        <f t="shared" si="4"/>
+        <v>297.69999999999993</v>
+      </c>
+      <c r="Y5" s="7">
+        <f t="shared" ref="Y5:Z5" si="5">Y3-Y4</f>
+        <v>335.1</v>
+      </c>
+      <c r="Z5" s="7">
         <f t="shared" si="5"/>
-        <v>103</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" si="5"/>
-        <v>107.5</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="5"/>
-        <v>115.30000000000001</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="5"/>
-        <v>117</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="5"/>
-        <v>128.9</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="5"/>
-        <v>138.1</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="5"/>
-        <v>145.20000000000002</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="5"/>
-        <v>146.5</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="5"/>
-        <v>156.5</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="5"/>
-        <v>167.09999999999997</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="5"/>
-        <v>185.89999999999998</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" si="5"/>
-        <v>176.59999999999997</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="5"/>
-        <v>195.67000000000002</v>
-      </c>
-      <c r="Q5" s="7">
-        <f t="shared" si="5"/>
-        <v>210.60000000000002</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" si="5"/>
-        <v>222.69999999999993</v>
-      </c>
-      <c r="S5" s="7">
-        <f t="shared" si="5"/>
-        <v>227.59999999999997</v>
-      </c>
-      <c r="T5" s="7">
-        <f t="shared" si="5"/>
-        <v>212.83999999999997</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="5"/>
-        <v>228.80000000000007</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="5"/>
-        <v>257.7</v>
-      </c>
-      <c r="W5" s="7">
-        <f t="shared" si="5"/>
-        <v>261.5</v>
-      </c>
-      <c r="X5" s="7">
-        <f t="shared" si="5"/>
-        <v>297.69999999999993</v>
-      </c>
-      <c r="Y5" s="7">
-        <f t="shared" ref="Y5:Z5" si="6">Y3-Y4</f>
-        <v>335.1</v>
-      </c>
-      <c r="Z5" s="7">
+        <v>380.20000000000005</v>
+      </c>
+      <c r="AA5" s="7">
+        <f t="shared" ref="AA5:AB5" si="6">AA3-AA4</f>
+        <v>390.79999999999995</v>
+      </c>
+      <c r="AB5" s="7">
         <f t="shared" si="6"/>
-        <v>380.20000000000005</v>
-      </c>
-      <c r="AA5" s="7">
-        <f t="shared" ref="AA5:AB5" si="7">AA3-AA4</f>
-        <v>390.79999999999995</v>
-      </c>
-      <c r="AB5" s="7">
+        <v>348.60000000000014</v>
+      </c>
+      <c r="AC5" s="7">
+        <f t="shared" ref="AC5:AE5" si="7">AC3-AC4</f>
+        <v>400.10000000000014</v>
+      </c>
+      <c r="AD5" s="7">
+        <f t="shared" ref="AD5" si="8">AD3-AD4</f>
+        <v>398.5</v>
+      </c>
+      <c r="AE5" s="7">
         <f t="shared" si="7"/>
-        <v>348.60000000000014</v>
-      </c>
-      <c r="AC5" s="7">
-        <f t="shared" ref="AC5:AE5" si="8">AC3-AC4</f>
-        <v>400.10000000000014</v>
-      </c>
-      <c r="AD5" s="7">
-        <f t="shared" ref="AD5" si="9">AD3-AD4</f>
-        <v>398.5</v>
-      </c>
-      <c r="AE5" s="7">
-        <f t="shared" si="8"/>
         <v>355.00000000000011</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" ref="AF5" si="10">AF3-AF4</f>
+        <f t="shared" ref="AF5" si="9">AF3-AF4</f>
         <v>361.5</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" ref="AG5:AH5" si="11">AG3-AG4</f>
+        <f t="shared" ref="AG5:AH5" si="10">AG3-AG4</f>
         <v>357.79999999999995</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>359.69999999999993</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" ref="AI5" si="12">AI3-AI4</f>
+        <f t="shared" ref="AI5" si="11">AI3-AI4</f>
         <v>331.20000000000005</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" ref="AJ5" si="13">AJ3-AJ4</f>
+        <f t="shared" ref="AJ5" si="12">AJ3-AJ4</f>
         <v>335.69999999999993</v>
       </c>
       <c r="AK5" s="7">
-        <f t="shared" ref="AK5:AL5" si="14">AK3-AK4</f>
+        <f t="shared" ref="AK5:AN5" si="13">AK3-AK4</f>
         <v>403.5</v>
       </c>
       <c r="AL5" s="7">
+        <f t="shared" si="13"/>
+        <v>379.99999999999977</v>
+      </c>
+      <c r="AM5" s="7">
+        <f t="shared" si="13"/>
+        <v>349.70000000000005</v>
+      </c>
+      <c r="AN5" s="7">
+        <f t="shared" si="13"/>
+        <v>389.40000000000009</v>
+      </c>
+      <c r="AO5" s="7">
+        <f t="shared" ref="AO5:AP5" si="14">AO3*0.3</f>
+        <v>413.29499999999996</v>
+      </c>
+      <c r="AP5" s="7">
         <f t="shared" si="14"/>
-        <v>379.99999999999977</v>
-      </c>
-      <c r="AM5" s="7">
-        <f>AM3*0.3</f>
-        <v>374.12549999999999</v>
-      </c>
-      <c r="AN5" s="7">
-        <f t="shared" ref="AN5:AP5" si="15">AN3*0.3</f>
-        <v>347.41980000000001</v>
-      </c>
-      <c r="AO5" s="7">
+        <v>423.17369999999983</v>
+      </c>
+      <c r="AR5" s="7">
+        <f t="shared" ref="AR5:AS5" si="15">AR3-AR4</f>
+        <v>442.79999999999995</v>
+      </c>
+      <c r="AS5" s="7">
         <f t="shared" si="15"/>
-        <v>353.7525</v>
-      </c>
-      <c r="AP5" s="7">
-        <f t="shared" si="15"/>
-        <v>378.23489999999987</v>
-      </c>
-      <c r="AR5" s="7">
-        <f t="shared" ref="AR5:AS5" si="16">AR3-AR4</f>
-        <v>442.79999999999995</v>
-      </c>
-      <c r="AS5" s="7">
+        <v>529.20000000000005</v>
+      </c>
+      <c r="AT5" s="7">
+        <f t="shared" ref="AT5:AU5" si="16">AT3-AT4</f>
+        <v>656</v>
+      </c>
+      <c r="AU5" s="7">
         <f t="shared" si="16"/>
-        <v>529.20000000000005</v>
-      </c>
-      <c r="AT5" s="7">
-        <f t="shared" ref="AT5:AU5" si="17">AT3-AT4</f>
-        <v>656</v>
-      </c>
-      <c r="AU5" s="7">
+        <v>805.57000000000016</v>
+      </c>
+      <c r="AV5" s="7">
+        <f t="shared" ref="AV5:AW5" si="17">AV3-AV4</f>
+        <v>926.94</v>
+      </c>
+      <c r="AW5" s="7">
         <f t="shared" si="17"/>
-        <v>805.57000000000016</v>
-      </c>
-      <c r="AV5" s="7">
-        <f t="shared" ref="AV5:AW5" si="18">AV3-AV4</f>
-        <v>926.94</v>
-      </c>
-      <c r="AW5" s="7">
-        <f t="shared" si="18"/>
         <v>1274.5</v>
       </c>
       <c r="AX5" s="7">
@@ -1723,47 +1721,47 @@
       </c>
       <c r="BA5" s="7">
         <f>BA3-BA4</f>
-        <v>1453.5326999999997</v>
+        <v>1575.5686999999998</v>
       </c>
       <c r="BB5" s="7">
         <f>BB3*0.3</f>
-        <v>1468.068027</v>
+        <v>1796.2985699999999</v>
       </c>
       <c r="BC5" s="7">
-        <f t="shared" ref="BC5:BK5" si="19">BC3*0.3</f>
-        <v>1482.7487072700001</v>
+        <f t="shared" ref="BC5:BK5" si="18">BC3*0.3</f>
+        <v>1904.0764842000001</v>
       </c>
       <c r="BD5" s="7">
-        <f t="shared" si="19"/>
-        <v>1497.5761943426999</v>
+        <f t="shared" si="18"/>
+        <v>1980.2395435680003</v>
       </c>
       <c r="BE5" s="7">
-        <f t="shared" si="19"/>
-        <v>1512.5519562861271</v>
+        <f t="shared" si="18"/>
+        <v>2039.6467298750404</v>
       </c>
       <c r="BF5" s="7">
-        <f t="shared" si="19"/>
-        <v>1527.6774758489883</v>
+        <f t="shared" si="18"/>
+        <v>2100.8361317712915</v>
       </c>
       <c r="BG5" s="7">
-        <f t="shared" si="19"/>
-        <v>1542.9542506074779</v>
+        <f t="shared" si="18"/>
+        <v>2163.8612157244302</v>
       </c>
       <c r="BH5" s="7">
-        <f t="shared" si="19"/>
-        <v>1558.3837931135529</v>
+        <f t="shared" si="18"/>
+        <v>2228.7770521961634</v>
       </c>
       <c r="BI5" s="7">
-        <f t="shared" si="19"/>
-        <v>1573.9676310446882</v>
+        <f t="shared" si="18"/>
+        <v>2295.6403637620483</v>
       </c>
       <c r="BJ5" s="7">
-        <f t="shared" si="19"/>
-        <v>1589.7073073551351</v>
+        <f t="shared" si="18"/>
+        <v>2364.5095746749098</v>
       </c>
       <c r="BK5" s="7">
-        <f t="shared" si="19"/>
-        <v>1605.6043804286865</v>
+        <f t="shared" si="18"/>
+        <v>2435.4448619151572</v>
       </c>
     </row>
     <row r="6" spans="2:173" x14ac:dyDescent="0.3">
@@ -1892,20 +1890,18 @@
         <v>216.89999999999998</v>
       </c>
       <c r="AM6" s="5">
-        <f>AI6*1.01</f>
-        <v>200.48500000000001</v>
+        <v>218.9</v>
       </c>
       <c r="AN6" s="5">
-        <f t="shared" ref="AN6:AP6" si="20">AJ6*1.01</f>
-        <v>196.041</v>
+        <v>231.7</v>
       </c>
       <c r="AO6" s="5">
-        <f t="shared" si="20"/>
-        <v>208.86800000000002</v>
+        <f>AK6*1.14</f>
+        <v>235.75199999999998</v>
       </c>
       <c r="AP6" s="5">
-        <f t="shared" si="20"/>
-        <v>219.06899999999999</v>
+        <f>AL6*1.12</f>
+        <v>242.928</v>
       </c>
       <c r="AR6" s="5">
         <f>SUM(C6:F6)</f>
@@ -1942,47 +1938,47 @@
       </c>
       <c r="BA6" s="5">
         <f>SUM(AM6:AP6)</f>
-        <v>824.46299999999997</v>
+        <v>929.28</v>
       </c>
       <c r="BB6" s="5">
-        <f>BA6*1.02</f>
-        <v>840.95226000000002</v>
+        <f>BA6*1.08</f>
+        <v>1003.6224000000001</v>
       </c>
       <c r="BC6" s="5">
-        <f>BB6*1.02</f>
-        <v>857.77130520000003</v>
+        <f>BB6*1.04</f>
+        <v>1043.7672960000002</v>
       </c>
       <c r="BD6" s="5">
-        <f t="shared" ref="BD6:BG6" si="21">BC6*1.01</f>
-        <v>866.34901825200006</v>
+        <f>BC6*1.03</f>
+        <v>1075.0803148800003</v>
       </c>
       <c r="BE6" s="5">
-        <f t="shared" si="21"/>
-        <v>875.0125084345201</v>
+        <f>BD6*1.02</f>
+        <v>1096.5819211776004</v>
       </c>
       <c r="BF6" s="5">
-        <f t="shared" si="21"/>
-        <v>883.7626335188653</v>
+        <f t="shared" ref="BF6:BK6" si="19">BE6*1.02</f>
+        <v>1118.5135596011523</v>
       </c>
       <c r="BG6" s="5">
-        <f t="shared" si="21"/>
-        <v>892.600259854054</v>
+        <f t="shared" si="19"/>
+        <v>1140.8838307931753</v>
       </c>
       <c r="BH6" s="5">
-        <f t="shared" ref="BH6" si="22">BG6*1.01</f>
-        <v>901.52626245259455</v>
+        <f t="shared" si="19"/>
+        <v>1163.7015074090389</v>
       </c>
       <c r="BI6" s="5">
-        <f t="shared" ref="BI6" si="23">BH6*1.01</f>
-        <v>910.54152507712047</v>
+        <f t="shared" si="19"/>
+        <v>1186.9755375572197</v>
       </c>
       <c r="BJ6" s="5">
-        <f t="shared" ref="BJ6" si="24">BI6*1.01</f>
-        <v>919.64694032789168</v>
+        <f t="shared" si="19"/>
+        <v>1210.7150483083642</v>
       </c>
       <c r="BK6" s="5">
-        <f t="shared" ref="BK6" si="25">BJ6*1.01</f>
-        <v>928.8434097311706</v>
+        <f t="shared" si="19"/>
+        <v>1234.9293492745314</v>
       </c>
     </row>
     <row r="7" spans="2:173" x14ac:dyDescent="0.3">
@@ -2102,10 +2098,10 @@
         <v>26.699999999999989</v>
       </c>
       <c r="AM7" s="5">
-        <v>22</v>
+        <v>31.4</v>
       </c>
       <c r="AN7" s="5">
-        <v>23</v>
+        <v>31.3</v>
       </c>
       <c r="AO7" s="5">
         <v>23</v>
@@ -2149,292 +2145,262 @@
       </c>
       <c r="BA7" s="5">
         <f>SUM(AM7:AP7)</f>
-        <v>93</v>
-      </c>
-      <c r="BB7" s="5">
-        <f>BA7*1.05</f>
-        <v>97.65</v>
-      </c>
-      <c r="BC7" s="5">
-        <f t="shared" ref="BC7:BG7" si="26">BB7*1.05</f>
-        <v>102.53250000000001</v>
-      </c>
-      <c r="BD7" s="5">
-        <f t="shared" si="26"/>
-        <v>107.65912500000002</v>
-      </c>
-      <c r="BE7" s="5">
-        <f t="shared" si="26"/>
-        <v>113.04208125000002</v>
-      </c>
-      <c r="BF7" s="5">
-        <f t="shared" si="26"/>
-        <v>118.69418531250003</v>
-      </c>
-      <c r="BG7" s="5">
-        <f t="shared" si="26"/>
-        <v>124.62889457812503</v>
-      </c>
-      <c r="BH7" s="5">
-        <f t="shared" ref="BH7" si="27">BG7*1.05</f>
-        <v>130.8603393070313</v>
-      </c>
-      <c r="BI7" s="5">
-        <f t="shared" ref="BI7" si="28">BH7*1.05</f>
-        <v>137.40335627238287</v>
-      </c>
-      <c r="BJ7" s="5">
-        <f t="shared" ref="BJ7" si="29">BI7*1.05</f>
-        <v>144.27352408600203</v>
-      </c>
-      <c r="BK7" s="5">
-        <f t="shared" ref="BK7" si="30">BJ7*1.05</f>
-        <v>151.48720029030213</v>
-      </c>
+        <v>110.7</v>
+      </c>
+      <c r="BB7" s="5"/>
+      <c r="BC7" s="5"/>
+      <c r="BD7" s="5"/>
+      <c r="BE7" s="5"/>
+      <c r="BF7" s="5"/>
+      <c r="BG7" s="5"/>
+      <c r="BH7" s="5"/>
+      <c r="BI7" s="5"/>
+      <c r="BJ7" s="5"/>
+      <c r="BK7" s="5"/>
     </row>
     <row r="8" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="7">
-        <f t="shared" ref="C8:V8" si="31">C5-C6-C7</f>
+        <f t="shared" ref="C8:V8" si="20">C5-C6-C7</f>
         <v>31.000000000000004</v>
       </c>
       <c r="D8" s="7">
+        <f t="shared" si="20"/>
+        <v>32.1</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="20"/>
+        <v>33.9</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="20"/>
+        <v>37.5</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="20"/>
+        <v>31.000000000000004</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="20"/>
+        <v>40.799999999999997</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="20"/>
+        <v>49.199999999999989</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="20"/>
+        <v>52.100000000000023</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="20"/>
+        <v>48.599999999999994</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="20"/>
+        <v>54.3</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="20"/>
+        <v>64.599999999999966</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="20"/>
+        <v>78.299999999999969</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="20"/>
+        <v>64.599999999999966</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="20"/>
+        <v>72.910000000000011</v>
+      </c>
+      <c r="Q8" s="7">
+        <f t="shared" si="20"/>
+        <v>80.600000000000023</v>
+      </c>
+      <c r="R8" s="7">
+        <f t="shared" si="20"/>
+        <v>84.699999999999932</v>
+      </c>
+      <c r="S8" s="7">
+        <f t="shared" si="20"/>
+        <v>87.599999999999966</v>
+      </c>
+      <c r="T8" s="7">
+        <f t="shared" si="20"/>
+        <v>83.419999999999973</v>
+      </c>
+      <c r="U8" s="7">
+        <f t="shared" si="20"/>
+        <v>96.400000000000063</v>
+      </c>
+      <c r="V8" s="7">
+        <f t="shared" si="20"/>
+        <v>111.99999999999999</v>
+      </c>
+      <c r="W8" s="7">
+        <f t="shared" ref="W8:Z8" si="21">W5-W6-W7</f>
+        <v>107.3</v>
+      </c>
+      <c r="X8" s="7">
+        <f t="shared" si="21"/>
+        <v>125.29999999999993</v>
+      </c>
+      <c r="Y8" s="7">
+        <f t="shared" si="21"/>
+        <v>144.10000000000002</v>
+      </c>
+      <c r="Z8" s="7">
+        <f t="shared" si="21"/>
+        <v>165.70000000000005</v>
+      </c>
+      <c r="AA8" s="7">
+        <f t="shared" ref="AA8:AB8" si="22">AA5-AA6-AA7</f>
+        <v>129.19999999999993</v>
+      </c>
+      <c r="AB8" s="7">
+        <f t="shared" si="22"/>
+        <v>93.100000000000136</v>
+      </c>
+      <c r="AC8" s="7">
+        <f t="shared" ref="AC8:AE8" si="23">AC5-AC6-AC7</f>
+        <v>180.20000000000013</v>
+      </c>
+      <c r="AD8" s="7">
+        <f t="shared" ref="AD8" si="24">AD5-AD6-AD7</f>
+        <v>170.40000000000006</v>
+      </c>
+      <c r="AE8" s="7">
+        <f t="shared" si="23"/>
+        <v>120.30000000000011</v>
+      </c>
+      <c r="AF8" s="7">
+        <f t="shared" ref="AF8" si="25">AF5-AF6-AF7</f>
+        <v>144.29999999999998</v>
+      </c>
+      <c r="AG8" s="7">
+        <f t="shared" ref="AG8:AH8" si="26">AG5-AG6-AG7</f>
+        <v>113.99999999999994</v>
+      </c>
+      <c r="AH8" s="7">
+        <f t="shared" si="26"/>
+        <v>122.59999999999997</v>
+      </c>
+      <c r="AI8" s="7">
+        <f t="shared" ref="AI8" si="27">AI5-AI6-AI7</f>
+        <v>110.60000000000005</v>
+      </c>
+      <c r="AJ8" s="7">
+        <f t="shared" ref="AJ8" si="28">AJ5-AJ6-AJ7</f>
+        <v>120.49999999999994</v>
+      </c>
+      <c r="AK8" s="7">
+        <f t="shared" ref="AK8:AP8" si="29">AK5-AK6-AK7</f>
+        <v>177</v>
+      </c>
+      <c r="AL8" s="7">
+        <f t="shared" si="29"/>
+        <v>136.39999999999981</v>
+      </c>
+      <c r="AM8" s="7">
+        <f t="shared" si="29"/>
+        <v>99.400000000000034</v>
+      </c>
+      <c r="AN8" s="7">
+        <f t="shared" si="29"/>
+        <v>126.40000000000011</v>
+      </c>
+      <c r="AO8" s="7">
+        <f t="shared" si="29"/>
+        <v>154.54299999999998</v>
+      </c>
+      <c r="AP8" s="7">
+        <f t="shared" si="29"/>
+        <v>155.24569999999983</v>
+      </c>
+      <c r="AR8" s="7">
+        <f t="shared" ref="AR8:AS8" si="30">AR5-AR6-AR7</f>
+        <v>134.49999999999991</v>
+      </c>
+      <c r="AS8" s="7">
+        <f t="shared" si="30"/>
+        <v>173.10000000000005</v>
+      </c>
+      <c r="AT8" s="7">
+        <f t="shared" ref="AT8:AU8" si="31">AT5-AT6-AT7</f>
+        <v>245.8</v>
+      </c>
+      <c r="AU8" s="7">
         <f t="shared" si="31"/>
-        <v>32.1</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" si="31"/>
-        <v>33.9</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="31"/>
-        <v>37.5</v>
-      </c>
-      <c r="G8" s="7">
-        <f t="shared" si="31"/>
-        <v>31.000000000000004</v>
-      </c>
-      <c r="H8" s="7">
-        <f t="shared" si="31"/>
-        <v>40.799999999999997</v>
-      </c>
-      <c r="I8" s="7">
-        <f t="shared" si="31"/>
-        <v>49.199999999999989</v>
-      </c>
-      <c r="J8" s="7">
-        <f t="shared" si="31"/>
-        <v>52.100000000000023</v>
-      </c>
-      <c r="K8" s="7">
-        <f t="shared" si="31"/>
-        <v>48.599999999999994</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="31"/>
-        <v>54.3</v>
-      </c>
-      <c r="M8" s="7">
-        <f t="shared" si="31"/>
-        <v>64.599999999999966</v>
-      </c>
-      <c r="N8" s="7">
-        <f t="shared" si="31"/>
-        <v>78.299999999999969</v>
-      </c>
-      <c r="O8" s="7">
-        <f t="shared" si="31"/>
-        <v>64.599999999999966</v>
-      </c>
-      <c r="P8" s="7">
-        <f t="shared" si="31"/>
-        <v>72.910000000000011</v>
-      </c>
-      <c r="Q8" s="7">
-        <f t="shared" si="31"/>
-        <v>80.600000000000023</v>
-      </c>
-      <c r="R8" s="7">
-        <f t="shared" si="31"/>
-        <v>84.699999999999932</v>
-      </c>
-      <c r="S8" s="7">
-        <f t="shared" si="31"/>
-        <v>87.599999999999966</v>
-      </c>
-      <c r="T8" s="7">
-        <f t="shared" si="31"/>
-        <v>83.419999999999973</v>
-      </c>
-      <c r="U8" s="7">
-        <f t="shared" si="31"/>
-        <v>96.400000000000063</v>
-      </c>
-      <c r="V8" s="7">
-        <f t="shared" si="31"/>
-        <v>111.99999999999999</v>
-      </c>
-      <c r="W8" s="7">
-        <f t="shared" ref="W8:Z8" si="32">W5-W6-W7</f>
-        <v>107.3</v>
-      </c>
-      <c r="X8" s="7">
+        <v>302.81000000000012</v>
+      </c>
+      <c r="AV8" s="7">
+        <f t="shared" ref="AV8:BF8" si="32">AV5-AV6-AV7</f>
+        <v>379.42000000000013</v>
+      </c>
+      <c r="AW8" s="7">
         <f t="shared" si="32"/>
-        <v>125.29999999999993</v>
-      </c>
-      <c r="Y8" s="7">
+        <v>542.4</v>
+      </c>
+      <c r="AX8" s="7">
+        <f t="shared" ref="AX8:AY8" si="33">AX5-AX6-AX7</f>
+        <v>572.90000000000009</v>
+      </c>
+      <c r="AY8" s="7">
+        <f t="shared" si="33"/>
+        <v>501.2</v>
+      </c>
+      <c r="AZ8" s="7">
         <f t="shared" si="32"/>
-        <v>144.10000000000002</v>
-      </c>
-      <c r="Z8" s="7">
+        <v>544.49999999999966</v>
+      </c>
+      <c r="BA8" s="7">
         <f t="shared" si="32"/>
-        <v>165.70000000000005</v>
-      </c>
-      <c r="AA8" s="7">
-        <f t="shared" ref="AA8:AB8" si="33">AA5-AA6-AA7</f>
-        <v>129.19999999999993</v>
-      </c>
-      <c r="AB8" s="7">
-        <f t="shared" si="33"/>
-        <v>93.100000000000136</v>
-      </c>
-      <c r="AC8" s="7">
-        <f t="shared" ref="AC8:AE8" si="34">AC5-AC6-AC7</f>
-        <v>180.20000000000013</v>
-      </c>
-      <c r="AD8" s="7">
-        <f t="shared" ref="AD8" si="35">AD5-AD6-AD7</f>
-        <v>170.40000000000006</v>
-      </c>
-      <c r="AE8" s="7">
+        <v>535.58869999999979</v>
+      </c>
+      <c r="BB8" s="7">
+        <f t="shared" si="32"/>
+        <v>792.67616999999984</v>
+      </c>
+      <c r="BC8" s="7">
+        <f t="shared" si="32"/>
+        <v>860.30918819999988</v>
+      </c>
+      <c r="BD8" s="7">
+        <f t="shared" si="32"/>
+        <v>905.15922868799998</v>
+      </c>
+      <c r="BE8" s="7">
+        <f t="shared" si="32"/>
+        <v>943.06480869743996</v>
+      </c>
+      <c r="BF8" s="7">
+        <f t="shared" si="32"/>
+        <v>982.32257217013921</v>
+      </c>
+      <c r="BG8" s="7">
+        <f t="shared" ref="BG8:BK8" si="34">BG5-BG6-BG7</f>
+        <v>1022.9773849312548</v>
+      </c>
+      <c r="BH8" s="7">
         <f t="shared" si="34"/>
-        <v>120.30000000000011</v>
-      </c>
-      <c r="AF8" s="7">
-        <f t="shared" ref="AF8" si="36">AF5-AF6-AF7</f>
-        <v>144.29999999999998</v>
-      </c>
-      <c r="AG8" s="7">
-        <f t="shared" ref="AG8:AH8" si="37">AG5-AG6-AG7</f>
-        <v>113.99999999999994</v>
-      </c>
-      <c r="AH8" s="7">
-        <f t="shared" si="37"/>
-        <v>122.59999999999997</v>
-      </c>
-      <c r="AI8" s="7">
-        <f t="shared" ref="AI8" si="38">AI5-AI6-AI7</f>
-        <v>110.60000000000005</v>
-      </c>
-      <c r="AJ8" s="7">
-        <f t="shared" ref="AJ8" si="39">AJ5-AJ6-AJ7</f>
-        <v>120.49999999999994</v>
-      </c>
-      <c r="AK8" s="7">
-        <f t="shared" ref="AK8:AP8" si="40">AK5-AK6-AK7</f>
-        <v>177</v>
-      </c>
-      <c r="AL8" s="7">
-        <f t="shared" si="40"/>
-        <v>136.39999999999981</v>
-      </c>
-      <c r="AM8" s="7">
-        <f t="shared" si="40"/>
-        <v>151.64049999999997</v>
-      </c>
-      <c r="AN8" s="7">
-        <f t="shared" si="40"/>
-        <v>128.37880000000001</v>
-      </c>
-      <c r="AO8" s="7">
-        <f t="shared" si="40"/>
-        <v>121.88449999999997</v>
-      </c>
-      <c r="AP8" s="7">
-        <f t="shared" si="40"/>
-        <v>134.16589999999988</v>
-      </c>
-      <c r="AR8" s="7">
-        <f t="shared" ref="AR8:AS8" si="41">AR5-AR6-AR7</f>
-        <v>134.49999999999991</v>
-      </c>
-      <c r="AS8" s="7">
-        <f t="shared" si="41"/>
-        <v>173.10000000000005</v>
-      </c>
-      <c r="AT8" s="7">
-        <f t="shared" ref="AT8:AU8" si="42">AT5-AT6-AT7</f>
-        <v>245.8</v>
-      </c>
-      <c r="AU8" s="7">
-        <f t="shared" si="42"/>
-        <v>302.81000000000012</v>
-      </c>
-      <c r="AV8" s="7">
-        <f t="shared" ref="AV8:BF8" si="43">AV5-AV6-AV7</f>
-        <v>379.42000000000013</v>
-      </c>
-      <c r="AW8" s="7">
-        <f t="shared" si="43"/>
-        <v>542.4</v>
-      </c>
-      <c r="AX8" s="7">
-        <f t="shared" ref="AX8:AY8" si="44">AX5-AX6-AX7</f>
-        <v>572.90000000000009</v>
-      </c>
-      <c r="AY8" s="7">
-        <f t="shared" si="44"/>
-        <v>501.2</v>
-      </c>
-      <c r="AZ8" s="7">
-        <f t="shared" si="43"/>
-        <v>544.49999999999966</v>
-      </c>
-      <c r="BA8" s="7">
-        <f t="shared" si="43"/>
-        <v>536.06969999999978</v>
-      </c>
-      <c r="BB8" s="7">
-        <f t="shared" si="43"/>
-        <v>529.46576700000003</v>
-      </c>
-      <c r="BC8" s="7">
-        <f t="shared" si="43"/>
-        <v>522.44490207000001</v>
-      </c>
-      <c r="BD8" s="7">
-        <f t="shared" si="43"/>
-        <v>523.56805109069978</v>
-      </c>
-      <c r="BE8" s="7">
-        <f t="shared" si="43"/>
-        <v>524.49736660160693</v>
-      </c>
-      <c r="BF8" s="7">
-        <f t="shared" si="43"/>
-        <v>525.2206570176229</v>
-      </c>
-      <c r="BG8" s="7">
-        <f t="shared" ref="BG8:BK8" si="45">BG5-BG6-BG7</f>
-        <v>525.72509617529886</v>
-      </c>
-      <c r="BH8" s="7">
-        <f t="shared" si="45"/>
-        <v>525.99719135392706</v>
+        <v>1065.0755447871245</v>
       </c>
       <c r="BI8" s="7">
-        <f t="shared" si="45"/>
-        <v>526.02274969518487</v>
+        <f t="shared" si="34"/>
+        <v>1108.6648262048286</v>
       </c>
       <c r="BJ8" s="7">
-        <f t="shared" si="45"/>
-        <v>525.78684294124139</v>
+        <f t="shared" si="34"/>
+        <v>1153.7945263665456</v>
       </c>
       <c r="BK8" s="7">
-        <f t="shared" si="45"/>
-        <v>525.27377040721376</v>
+        <f t="shared" si="34"/>
+        <v>1200.5155126406257</v>
       </c>
     </row>
     <row r="9" spans="2:173" x14ac:dyDescent="0.3">
@@ -2553,19 +2519,17 @@
         <v>-6.5999999999999943</v>
       </c>
       <c r="AM9" s="5">
-        <f>AI9*1.03</f>
-        <v>-15.450000000000001</v>
+        <v>-5.8</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" ref="AN9:AP9" si="46">AJ9*1.03</f>
-        <v>-12.36</v>
+        <v>-3.5</v>
       </c>
       <c r="AO9" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="AO9:AP9" si="35">AK9*1.03</f>
         <v>-13.699000000000002</v>
       </c>
       <c r="AP9" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="35"/>
         <v>-6.7979999999999947</v>
       </c>
       <c r="AR9" s="5">
@@ -2603,47 +2567,47 @@
       </c>
       <c r="BA9" s="5">
         <f>SUM(AM9:AP9)</f>
-        <v>-48.306999999999995</v>
+        <v>-29.796999999999997</v>
       </c>
       <c r="BB9" s="5">
-        <f t="shared" ref="BB9:BG9" si="47">BA9*1.02</f>
-        <v>-49.273139999999998</v>
+        <f t="shared" ref="BB9:BG9" si="36">BA9*1.02</f>
+        <v>-30.392939999999996</v>
       </c>
       <c r="BC9" s="5">
-        <f t="shared" si="47"/>
-        <v>-50.258602799999998</v>
+        <f t="shared" si="36"/>
+        <v>-31.000798799999995</v>
       </c>
       <c r="BD9" s="5">
-        <f t="shared" si="47"/>
-        <v>-51.263774855999998</v>
+        <f t="shared" si="36"/>
+        <v>-31.620814775999996</v>
       </c>
       <c r="BE9" s="5">
-        <f t="shared" si="47"/>
-        <v>-52.289050353119997</v>
+        <f t="shared" si="36"/>
+        <v>-32.253231071519998</v>
       </c>
       <c r="BF9" s="5">
-        <f t="shared" si="47"/>
-        <v>-53.334831360182399</v>
+        <f t="shared" si="36"/>
+        <v>-32.898295692950398</v>
       </c>
       <c r="BG9" s="5">
-        <f t="shared" si="47"/>
-        <v>-54.401527987386046</v>
+        <f t="shared" si="36"/>
+        <v>-33.556261606809407</v>
       </c>
       <c r="BH9" s="5">
-        <f t="shared" ref="BH9" si="48">BG9*1.02</f>
-        <v>-55.489558547133768</v>
+        <f t="shared" ref="BH9" si="37">BG9*1.02</f>
+        <v>-34.227386838945598</v>
       </c>
       <c r="BI9" s="5">
-        <f t="shared" ref="BI9" si="49">BH9*1.02</f>
-        <v>-56.599349718076446</v>
+        <f t="shared" ref="BI9" si="38">BH9*1.02</f>
+        <v>-34.911934575724509</v>
       </c>
       <c r="BJ9" s="5">
-        <f t="shared" ref="BJ9" si="50">BI9*1.02</f>
-        <v>-57.731336712437979</v>
+        <f t="shared" ref="BJ9" si="39">BI9*1.02</f>
+        <v>-35.610173267238999</v>
       </c>
       <c r="BK9" s="5">
-        <f t="shared" ref="BK9" si="51">BJ9*1.02</f>
-        <v>-58.885963446686738</v>
+        <f t="shared" ref="BK9" si="40">BJ9*1.02</f>
+        <v>-36.322376732583777</v>
       </c>
     </row>
     <row r="10" spans="2:173" x14ac:dyDescent="0.3">
@@ -2762,10 +2726,10 @@
         <v>5.6</v>
       </c>
       <c r="AM10" s="5">
-        <v>2</v>
+        <v>10.7</v>
       </c>
       <c r="AN10" s="5">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="AO10" s="5">
         <v>2</v>
@@ -2808,47 +2772,47 @@
       </c>
       <c r="BA10" s="5">
         <f>SUM(AM10:AP10)</f>
-        <v>8</v>
+        <v>20.9</v>
       </c>
       <c r="BB10" s="5">
-        <f t="shared" ref="BB10:BG10" si="52">BA10*0.95</f>
-        <v>7.6</v>
+        <f t="shared" ref="BB10:BG10" si="41">BA10*0.95</f>
+        <v>19.854999999999997</v>
       </c>
       <c r="BC10" s="5">
-        <f t="shared" si="52"/>
-        <v>7.22</v>
+        <f t="shared" si="41"/>
+        <v>18.862249999999996</v>
       </c>
       <c r="BD10" s="5">
-        <f t="shared" si="52"/>
-        <v>6.8589999999999991</v>
+        <f t="shared" si="41"/>
+        <v>17.919137499999994</v>
       </c>
       <c r="BE10" s="5">
-        <f t="shared" si="52"/>
-        <v>6.516049999999999</v>
+        <f t="shared" si="41"/>
+        <v>17.023180624999995</v>
       </c>
       <c r="BF10" s="5">
-        <f t="shared" si="52"/>
-        <v>6.190247499999999</v>
+        <f t="shared" si="41"/>
+        <v>16.172021593749996</v>
       </c>
       <c r="BG10" s="5">
-        <f t="shared" si="52"/>
-        <v>5.8807351249999984</v>
+        <f t="shared" si="41"/>
+        <v>15.363420514062495</v>
       </c>
       <c r="BH10" s="5">
-        <f t="shared" ref="BH10" si="53">BG10*0.95</f>
-        <v>5.5866983687499978</v>
+        <f t="shared" ref="BH10" si="42">BG10*0.95</f>
+        <v>14.59524948835937</v>
       </c>
       <c r="BI10" s="5">
-        <f t="shared" ref="BI10" si="54">BH10*0.95</f>
-        <v>5.307363450312498</v>
+        <f t="shared" ref="BI10" si="43">BH10*0.95</f>
+        <v>13.865487013941401</v>
       </c>
       <c r="BJ10" s="5">
-        <f t="shared" ref="BJ10" si="55">BI10*0.95</f>
-        <v>5.0419952777968726</v>
+        <f t="shared" ref="BJ10" si="44">BI10*0.95</f>
+        <v>13.172212663244331</v>
       </c>
       <c r="BK10" s="5">
-        <f t="shared" ref="BK10" si="56">BJ10*0.95</f>
-        <v>4.7898955139070285</v>
+        <f t="shared" ref="BK10" si="45">BJ10*0.95</f>
+        <v>12.513602030082113</v>
       </c>
     </row>
     <row r="11" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2856,244 +2820,244 @@
         <v>34</v>
       </c>
       <c r="C11" s="7">
-        <f t="shared" ref="C11:V11" si="57">C8-C9-C10</f>
+        <f t="shared" ref="C11:V11" si="46">C8-C9-C10</f>
         <v>28.600000000000005</v>
       </c>
       <c r="D11" s="7">
+        <f t="shared" si="46"/>
+        <v>30.900000000000002</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" si="46"/>
+        <v>33.199999999999996</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="46"/>
+        <v>32.1</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="46"/>
+        <v>28.600000000000005</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="46"/>
+        <v>43.199999999999996</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="46"/>
+        <v>50.499999999999986</v>
+      </c>
+      <c r="J11" s="7">
+        <f t="shared" si="46"/>
+        <v>52.100000000000023</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="46"/>
+        <v>47.79999999999999</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="46"/>
+        <v>57.199999999999996</v>
+      </c>
+      <c r="M11" s="7">
+        <f t="shared" si="46"/>
+        <v>65.999999999999972</v>
+      </c>
+      <c r="N11" s="7">
+        <f t="shared" si="46"/>
+        <v>78.799999999999969</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="46"/>
+        <v>64.099999999999966</v>
+      </c>
+      <c r="P11" s="7">
+        <f t="shared" si="46"/>
+        <v>70.510000000000019</v>
+      </c>
+      <c r="Q11" s="7">
+        <f t="shared" si="46"/>
+        <v>80.000000000000028</v>
+      </c>
+      <c r="R11" s="7">
+        <f t="shared" si="46"/>
+        <v>84.799999999999926</v>
+      </c>
+      <c r="S11" s="7">
+        <f t="shared" si="46"/>
+        <v>96.499999999999972</v>
+      </c>
+      <c r="T11" s="7">
+        <f t="shared" si="46"/>
+        <v>76.069999999999965</v>
+      </c>
+      <c r="U11" s="7">
+        <f t="shared" si="46"/>
+        <v>103.97000000000007</v>
+      </c>
+      <c r="V11" s="7">
+        <f t="shared" si="46"/>
+        <v>102.09999999999998</v>
+      </c>
+      <c r="W11" s="7">
+        <f t="shared" ref="W11:Z11" si="47">W8-W9-W10</f>
+        <v>115</v>
+      </c>
+      <c r="X11" s="7">
+        <f t="shared" si="47"/>
+        <v>123.19999999999992</v>
+      </c>
+      <c r="Y11" s="7">
+        <f t="shared" si="47"/>
+        <v>135.4</v>
+      </c>
+      <c r="Z11" s="7">
+        <f t="shared" si="47"/>
+        <v>159.90000000000003</v>
+      </c>
+      <c r="AA11" s="7">
+        <f t="shared" ref="AA11:AB11" si="48">AA8-AA9-AA10</f>
+        <v>106.19999999999995</v>
+      </c>
+      <c r="AB11" s="7">
+        <f t="shared" si="48"/>
+        <v>8.8000000000001251</v>
+      </c>
+      <c r="AC11" s="7">
+        <f t="shared" ref="AC11:AE11" si="49">AC8-AC9-AC10</f>
+        <v>191.10000000000011</v>
+      </c>
+      <c r="AD11" s="7">
+        <f t="shared" ref="AD11" si="50">AD8-AD9-AD10</f>
+        <v>201.10000000000008</v>
+      </c>
+      <c r="AE11" s="7">
+        <f t="shared" si="49"/>
+        <v>127.20000000000013</v>
+      </c>
+      <c r="AF11" s="7">
+        <f t="shared" ref="AF11" si="51">AF8-AF9-AF10</f>
+        <v>149.99999999999997</v>
+      </c>
+      <c r="AG11" s="7">
+        <f t="shared" ref="AG11:AH11" si="52">AG8-AG9-AG10</f>
+        <v>123.99999999999994</v>
+      </c>
+      <c r="AH11" s="7">
+        <f t="shared" si="52"/>
+        <v>135.29999999999995</v>
+      </c>
+      <c r="AI11" s="7">
+        <f t="shared" ref="AI11" si="53">AI8-AI9-AI10</f>
+        <v>123.70000000000005</v>
+      </c>
+      <c r="AJ11" s="7">
+        <f t="shared" ref="AJ11" si="54">AJ8-AJ9-AJ10</f>
+        <v>133.69999999999993</v>
+      </c>
+      <c r="AK11" s="7">
+        <f t="shared" ref="AK11:AP11" si="55">AK8-AK9-AK10</f>
+        <v>189.60000000000002</v>
+      </c>
+      <c r="AL11" s="7">
+        <f t="shared" si="55"/>
+        <v>137.39999999999981</v>
+      </c>
+      <c r="AM11" s="7">
+        <f t="shared" si="55"/>
+        <v>94.500000000000028</v>
+      </c>
+      <c r="AN11" s="7">
+        <f t="shared" si="55"/>
+        <v>123.70000000000009</v>
+      </c>
+      <c r="AO11" s="7">
+        <f t="shared" si="55"/>
+        <v>166.24199999999999</v>
+      </c>
+      <c r="AP11" s="7">
+        <f t="shared" si="55"/>
+        <v>160.04369999999983</v>
+      </c>
+      <c r="AR11" s="7">
+        <f t="shared" ref="AR11:AS11" si="56">AR8-AR9-AR10</f>
+        <v>124.79999999999991</v>
+      </c>
+      <c r="AS11" s="7">
+        <f t="shared" si="56"/>
+        <v>174.40000000000003</v>
+      </c>
+      <c r="AT11" s="7">
+        <f t="shared" ref="AT11:AU11" si="57">AT8-AT9-AT10</f>
+        <v>249.8</v>
+      </c>
+      <c r="AU11" s="7">
         <f t="shared" si="57"/>
-        <v>30.900000000000002</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" si="57"/>
-        <v>33.199999999999996</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" si="57"/>
-        <v>32.1</v>
-      </c>
-      <c r="G11" s="7">
-        <f t="shared" si="57"/>
-        <v>28.600000000000005</v>
-      </c>
-      <c r="H11" s="7">
-        <f t="shared" si="57"/>
-        <v>43.199999999999996</v>
-      </c>
-      <c r="I11" s="7">
-        <f t="shared" si="57"/>
-        <v>50.499999999999986</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" si="57"/>
-        <v>52.100000000000023</v>
-      </c>
-      <c r="K11" s="7">
-        <f t="shared" si="57"/>
-        <v>47.79999999999999</v>
-      </c>
-      <c r="L11" s="7">
-        <f t="shared" si="57"/>
-        <v>57.199999999999996</v>
-      </c>
-      <c r="M11" s="7">
-        <f t="shared" si="57"/>
-        <v>65.999999999999972</v>
-      </c>
-      <c r="N11" s="7">
-        <f t="shared" si="57"/>
-        <v>78.799999999999969</v>
-      </c>
-      <c r="O11" s="7">
-        <f t="shared" si="57"/>
-        <v>64.099999999999966</v>
-      </c>
-      <c r="P11" s="7">
-        <f t="shared" si="57"/>
-        <v>70.510000000000019</v>
-      </c>
-      <c r="Q11" s="7">
-        <f t="shared" si="57"/>
-        <v>80.000000000000028</v>
-      </c>
-      <c r="R11" s="7">
-        <f t="shared" si="57"/>
-        <v>84.799999999999926</v>
-      </c>
-      <c r="S11" s="7">
-        <f t="shared" si="57"/>
-        <v>96.499999999999972</v>
-      </c>
-      <c r="T11" s="7">
-        <f t="shared" si="57"/>
-        <v>76.069999999999965</v>
-      </c>
-      <c r="U11" s="7">
-        <f t="shared" si="57"/>
-        <v>103.97000000000007</v>
-      </c>
-      <c r="V11" s="7">
-        <f t="shared" si="57"/>
-        <v>102.09999999999998</v>
-      </c>
-      <c r="W11" s="7">
-        <f t="shared" ref="W11:Z11" si="58">W8-W9-W10</f>
-        <v>115</v>
-      </c>
-      <c r="X11" s="7">
+        <v>299.41000000000008</v>
+      </c>
+      <c r="AV11" s="7">
+        <f t="shared" ref="AV11:AW11" si="58">AV8-AV9-AV10</f>
+        <v>378.6400000000001</v>
+      </c>
+      <c r="AW11" s="7">
         <f t="shared" si="58"/>
-        <v>123.19999999999992</v>
-      </c>
-      <c r="Y11" s="7">
-        <f t="shared" si="58"/>
-        <v>135.4</v>
-      </c>
-      <c r="Z11" s="7">
-        <f t="shared" si="58"/>
-        <v>159.90000000000003</v>
-      </c>
-      <c r="AA11" s="7">
-        <f t="shared" ref="AA11:AB11" si="59">AA8-AA9-AA10</f>
-        <v>106.19999999999995</v>
-      </c>
-      <c r="AB11" s="7">
+        <v>533.49999999999989</v>
+      </c>
+      <c r="AX11" s="7">
+        <f t="shared" ref="AX11:AY11" si="59">AX8-AX9-AX10</f>
+        <v>507.2000000000001</v>
+      </c>
+      <c r="AY11" s="7">
         <f t="shared" si="59"/>
-        <v>8.8000000000001251</v>
-      </c>
-      <c r="AC11" s="7">
-        <f t="shared" ref="AC11:AE11" si="60">AC8-AC9-AC10</f>
-        <v>191.10000000000011</v>
-      </c>
-      <c r="AD11" s="7">
-        <f t="shared" ref="AD11" si="61">AD8-AD9-AD10</f>
-        <v>201.10000000000008</v>
-      </c>
-      <c r="AE11" s="7">
+        <v>536.5</v>
+      </c>
+      <c r="AZ11" s="7">
+        <f t="shared" ref="AZ11:BF11" si="60">AZ8-AZ9-AZ10</f>
+        <v>584.39999999999964</v>
+      </c>
+      <c r="BA11" s="7">
         <f t="shared" si="60"/>
-        <v>127.20000000000013</v>
-      </c>
-      <c r="AF11" s="7">
-        <f t="shared" ref="AF11" si="62">AF8-AF9-AF10</f>
-        <v>149.99999999999997</v>
-      </c>
-      <c r="AG11" s="7">
-        <f t="shared" ref="AG11:AH11" si="63">AG8-AG9-AG10</f>
-        <v>123.99999999999994</v>
-      </c>
-      <c r="AH11" s="7">
-        <f t="shared" si="63"/>
-        <v>135.29999999999995</v>
-      </c>
-      <c r="AI11" s="7">
-        <f t="shared" ref="AI11" si="64">AI8-AI9-AI10</f>
-        <v>123.70000000000005</v>
-      </c>
-      <c r="AJ11" s="7">
-        <f t="shared" ref="AJ11" si="65">AJ8-AJ9-AJ10</f>
-        <v>133.69999999999993</v>
-      </c>
-      <c r="AK11" s="7">
-        <f t="shared" ref="AK11:AP11" si="66">AK8-AK9-AK10</f>
-        <v>189.60000000000002</v>
-      </c>
-      <c r="AL11" s="7">
-        <f t="shared" si="66"/>
-        <v>137.39999999999981</v>
-      </c>
-      <c r="AM11" s="7">
-        <f t="shared" si="66"/>
-        <v>165.09049999999996</v>
-      </c>
-      <c r="AN11" s="7">
-        <f t="shared" si="66"/>
-        <v>138.73880000000003</v>
-      </c>
-      <c r="AO11" s="7">
-        <f t="shared" si="66"/>
-        <v>133.58349999999999</v>
-      </c>
-      <c r="AP11" s="7">
-        <f t="shared" si="66"/>
-        <v>138.96389999999988</v>
-      </c>
-      <c r="AR11" s="7">
-        <f t="shared" ref="AR11:AS11" si="67">AR8-AR9-AR10</f>
-        <v>124.79999999999991</v>
-      </c>
-      <c r="AS11" s="7">
-        <f t="shared" si="67"/>
-        <v>174.40000000000003</v>
-      </c>
-      <c r="AT11" s="7">
-        <f t="shared" ref="AT11:AU11" si="68">AT8-AT9-AT10</f>
-        <v>249.8</v>
-      </c>
-      <c r="AU11" s="7">
-        <f t="shared" si="68"/>
-        <v>299.41000000000008</v>
-      </c>
-      <c r="AV11" s="7">
-        <f t="shared" ref="AV11:AW11" si="69">AV8-AV9-AV10</f>
-        <v>378.6400000000001</v>
-      </c>
-      <c r="AW11" s="7">
-        <f t="shared" si="69"/>
-        <v>533.49999999999989</v>
-      </c>
-      <c r="AX11" s="7">
-        <f t="shared" ref="AX11:AY11" si="70">AX8-AX9-AX10</f>
-        <v>507.2000000000001</v>
-      </c>
-      <c r="AY11" s="7">
-        <f t="shared" si="70"/>
-        <v>536.5</v>
-      </c>
-      <c r="AZ11" s="7">
-        <f t="shared" ref="AZ11:BF11" si="71">AZ8-AZ9-AZ10</f>
-        <v>584.39999999999964</v>
-      </c>
-      <c r="BA11" s="7">
-        <f t="shared" si="71"/>
-        <v>576.3766999999998</v>
+        <v>544.48569999999984</v>
       </c>
       <c r="BB11" s="7">
-        <f t="shared" si="71"/>
-        <v>571.13890700000002</v>
+        <f t="shared" si="60"/>
+        <v>803.21410999999978</v>
       </c>
       <c r="BC11" s="7">
-        <f t="shared" si="71"/>
-        <v>565.48350486999993</v>
+        <f t="shared" si="60"/>
+        <v>872.44773699999985</v>
       </c>
       <c r="BD11" s="7">
-        <f t="shared" si="71"/>
-        <v>567.9728259466998</v>
+        <f t="shared" si="60"/>
+        <v>918.86090596399993</v>
       </c>
       <c r="BE11" s="7">
-        <f t="shared" si="71"/>
-        <v>570.27036695472702</v>
+        <f t="shared" si="60"/>
+        <v>958.29485914395991</v>
       </c>
       <c r="BF11" s="7">
-        <f t="shared" si="71"/>
-        <v>572.36524087780526</v>
+        <f t="shared" si="60"/>
+        <v>999.04884626933961</v>
       </c>
       <c r="BG11" s="7">
-        <f t="shared" ref="BG11:BK11" si="72">BG8-BG9-BG10</f>
-        <v>574.24588903768495</v>
+        <f t="shared" ref="BG11:BK11" si="61">BG8-BG9-BG10</f>
+        <v>1041.1702260240017</v>
       </c>
       <c r="BH11" s="7">
-        <f t="shared" si="72"/>
-        <v>575.90005153231084</v>
+        <f t="shared" si="61"/>
+        <v>1084.7076821377109</v>
       </c>
       <c r="BI11" s="7">
-        <f t="shared" si="72"/>
-        <v>577.31473596294882</v>
+        <f t="shared" si="61"/>
+        <v>1129.7112737666116</v>
       </c>
       <c r="BJ11" s="7">
-        <f t="shared" si="72"/>
-        <v>578.47618437588244</v>
+        <f t="shared" si="61"/>
+        <v>1176.2324869705401</v>
       </c>
       <c r="BK11" s="7">
-        <f t="shared" si="72"/>
-        <v>579.36983833999352</v>
+        <f t="shared" si="61"/>
+        <v>1224.3242873431273</v>
       </c>
     </row>
     <row r="12" spans="2:173" x14ac:dyDescent="0.3">
@@ -3213,20 +3177,18 @@
         <v>34.000000000000007</v>
       </c>
       <c r="AM12" s="5">
-        <f>AM11*0.22</f>
-        <v>36.319909999999993</v>
+        <v>20.9</v>
       </c>
       <c r="AN12" s="5">
-        <f t="shared" ref="AN12:AP12" si="73">AN11*0.22</f>
-        <v>30.522536000000006</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" si="73"/>
-        <v>29.388369999999998</v>
+        <f t="shared" ref="AO12:AP12" si="62">AO11*0.22</f>
+        <v>36.573239999999998</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" si="73"/>
-        <v>30.572057999999974</v>
+        <f t="shared" si="62"/>
+        <v>35.209613999999966</v>
       </c>
       <c r="AR12" s="5">
         <f>SUM(C12:F12)</f>
@@ -3263,47 +3225,47 @@
       </c>
       <c r="BA12" s="5">
         <f>SUM(AM12:AP12)</f>
-        <v>126.80287399999996</v>
+        <v>128.38285399999995</v>
       </c>
       <c r="BB12" s="5">
         <f>BB11*0.22</f>
-        <v>125.65055954</v>
+        <v>176.70710419999995</v>
       </c>
       <c r="BC12" s="5">
-        <f t="shared" ref="BC12:BK12" si="74">BC11*0.22</f>
-        <v>124.40637107139999</v>
+        <f t="shared" ref="BC12:BK12" si="63">BC11*0.22</f>
+        <v>191.93850213999997</v>
       </c>
       <c r="BD12" s="5">
-        <f t="shared" si="74"/>
-        <v>124.95402170827396</v>
+        <f t="shared" si="63"/>
+        <v>202.14939931207999</v>
       </c>
       <c r="BE12" s="5">
-        <f t="shared" si="74"/>
-        <v>125.45948073003994</v>
+        <f t="shared" si="63"/>
+        <v>210.82486901167118</v>
       </c>
       <c r="BF12" s="5">
-        <f t="shared" si="74"/>
-        <v>125.92035299311716</v>
+        <f t="shared" si="63"/>
+        <v>219.79074617925471</v>
       </c>
       <c r="BG12" s="5">
-        <f t="shared" si="74"/>
-        <v>126.33409558829069</v>
+        <f t="shared" si="63"/>
+        <v>229.05744972528038</v>
       </c>
       <c r="BH12" s="5">
-        <f t="shared" si="74"/>
-        <v>126.69801133710838</v>
+        <f t="shared" si="63"/>
+        <v>238.63569007029639</v>
       </c>
       <c r="BI12" s="5">
-        <f t="shared" si="74"/>
-        <v>127.00924191184875</v>
+        <f t="shared" si="63"/>
+        <v>248.53648022865457</v>
       </c>
       <c r="BJ12" s="5">
-        <f t="shared" si="74"/>
-        <v>127.26476056269414</v>
+        <f t="shared" si="63"/>
+        <v>258.77114713351881</v>
       </c>
       <c r="BK12" s="5">
-        <f t="shared" si="74"/>
-        <v>127.46136443479857</v>
+        <f t="shared" si="63"/>
+        <v>269.35134321548799</v>
       </c>
     </row>
     <row r="13" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3311,684 +3273,684 @@
         <v>36</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:T13" si="75">C11-C12</f>
+        <f t="shared" ref="C13:T13" si="64">C11-C12</f>
         <v>23.600000000000005</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="64"/>
+        <v>24.400000000000002</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="64"/>
+        <v>26.199999999999996</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="64"/>
+        <v>24.8</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="64"/>
+        <v>23.600000000000005</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="64"/>
+        <v>37.499999999999993</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="64"/>
+        <v>42.499999999999986</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="64"/>
+        <v>-30.899999999999977</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="64"/>
+        <v>64.299999999999983</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="64"/>
+        <v>50.3</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="64"/>
+        <v>65.599999999999966</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="64"/>
+        <v>59.999999999999972</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="64"/>
+        <v>60.599999999999966</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="64"/>
+        <v>58.810000000000016</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="64"/>
+        <v>67.000000000000028</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="64"/>
+        <v>74.499999999999929</v>
+      </c>
+      <c r="S13" s="7">
+        <f t="shared" si="64"/>
+        <v>85.599999999999966</v>
+      </c>
+      <c r="T13" s="7">
+        <f t="shared" si="64"/>
+        <v>66.619999999999962</v>
+      </c>
+      <c r="U13" s="7">
+        <f t="shared" ref="U13:V13" si="65">U11-U12</f>
+        <v>89.47000000000007</v>
+      </c>
+      <c r="V13" s="7">
+        <f t="shared" si="65"/>
+        <v>85.59999999999998</v>
+      </c>
+      <c r="W13" s="7">
+        <f t="shared" ref="W13:X13" si="66">W11-W12</f>
+        <v>109.1</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="66"/>
+        <v>114.69999999999992</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" ref="Y13:Z13" si="67">Y11-Y12</f>
+        <v>115.7</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" si="67"/>
+        <v>142.20000000000005</v>
+      </c>
+      <c r="AA13" s="7">
+        <f t="shared" ref="AA13:AB13" si="68">AA11-AA12</f>
+        <v>89.599999999999937</v>
+      </c>
+      <c r="AB13" s="7">
+        <f t="shared" si="68"/>
+        <v>18.700000000000124</v>
+      </c>
+      <c r="AC13" s="7">
+        <f t="shared" ref="AC13:AE13" si="69">AC11-AC12</f>
+        <v>156.00000000000011</v>
+      </c>
+      <c r="AD13" s="7">
+        <f t="shared" ref="AD13" si="70">AD11-AD12</f>
+        <v>155.10000000000008</v>
+      </c>
+      <c r="AE13" s="7">
+        <f t="shared" si="69"/>
+        <v>102.20000000000013</v>
+      </c>
+      <c r="AF13" s="7">
+        <f t="shared" ref="AF13" si="71">AF11-AF12</f>
+        <v>119.99999999999997</v>
+      </c>
+      <c r="AG13" s="7">
+        <f t="shared" ref="AG13:AH13" si="72">AG11-AG12</f>
+        <v>89.399999999999949</v>
+      </c>
+      <c r="AH13" s="7">
+        <f t="shared" si="72"/>
+        <v>105.39999999999995</v>
+      </c>
+      <c r="AI13" s="7">
+        <f t="shared" ref="AI13" si="73">AI11-AI12</f>
+        <v>116.30000000000004</v>
+      </c>
+      <c r="AJ13" s="7">
+        <f t="shared" ref="AJ13" si="74">AJ11-AJ12</f>
+        <v>98.499999999999929</v>
+      </c>
+      <c r="AK13" s="7">
+        <f t="shared" ref="AK13:AL13" si="75">AK11-AK12</f>
+        <v>136.30000000000001</v>
+      </c>
+      <c r="AL13" s="7">
         <f t="shared" si="75"/>
-        <v>24.400000000000002</v>
-      </c>
-      <c r="E13" s="7">
-        <f t="shared" si="75"/>
-        <v>26.199999999999996</v>
-      </c>
-      <c r="F13" s="7">
-        <f t="shared" si="75"/>
-        <v>24.8</v>
-      </c>
-      <c r="G13" s="7">
-        <f t="shared" si="75"/>
-        <v>23.600000000000005</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="75"/>
-        <v>37.499999999999993</v>
-      </c>
-      <c r="I13" s="7">
-        <f t="shared" si="75"/>
-        <v>42.499999999999986</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="75"/>
-        <v>-30.899999999999977</v>
-      </c>
-      <c r="K13" s="7">
-        <f t="shared" si="75"/>
-        <v>64.299999999999983</v>
-      </c>
-      <c r="L13" s="7">
-        <f t="shared" si="75"/>
-        <v>50.3</v>
-      </c>
-      <c r="M13" s="7">
-        <f t="shared" si="75"/>
-        <v>65.599999999999966</v>
-      </c>
-      <c r="N13" s="7">
-        <f t="shared" si="75"/>
-        <v>59.999999999999972</v>
-      </c>
-      <c r="O13" s="7">
-        <f t="shared" si="75"/>
-        <v>60.599999999999966</v>
-      </c>
-      <c r="P13" s="7">
-        <f t="shared" si="75"/>
-        <v>58.810000000000016</v>
-      </c>
-      <c r="Q13" s="7">
-        <f t="shared" si="75"/>
-        <v>67.000000000000028</v>
-      </c>
-      <c r="R13" s="7">
-        <f t="shared" si="75"/>
-        <v>74.499999999999929</v>
-      </c>
-      <c r="S13" s="7">
-        <f t="shared" si="75"/>
-        <v>85.599999999999966</v>
-      </c>
-      <c r="T13" s="7">
-        <f t="shared" si="75"/>
-        <v>66.619999999999962</v>
-      </c>
-      <c r="U13" s="7">
-        <f t="shared" ref="U13:V13" si="76">U11-U12</f>
-        <v>89.47000000000007</v>
-      </c>
-      <c r="V13" s="7">
+        <v>103.39999999999981</v>
+      </c>
+      <c r="AM13" s="7">
+        <f t="shared" ref="AM13:AP13" si="76">AM11-AM12</f>
+        <v>73.600000000000023</v>
+      </c>
+      <c r="AN13" s="7">
         <f t="shared" si="76"/>
-        <v>85.59999999999998</v>
-      </c>
-      <c r="W13" s="7">
-        <f t="shared" ref="W13:X13" si="77">W11-W12</f>
-        <v>109.1</v>
-      </c>
-      <c r="X13" s="7">
+        <v>88.000000000000085</v>
+      </c>
+      <c r="AO13" s="7">
+        <f t="shared" si="76"/>
+        <v>129.66875999999999</v>
+      </c>
+      <c r="AP13" s="7">
+        <f t="shared" si="76"/>
+        <v>124.83408599999987</v>
+      </c>
+      <c r="AR13" s="7">
+        <f t="shared" ref="AR13:AS13" si="77">AR11-AR12</f>
+        <v>98.999999999999915</v>
+      </c>
+      <c r="AS13" s="7">
         <f t="shared" si="77"/>
-        <v>114.69999999999992</v>
-      </c>
-      <c r="Y13" s="7">
-        <f t="shared" ref="Y13:Z13" si="78">Y11-Y12</f>
-        <v>115.7</v>
-      </c>
-      <c r="Z13" s="7">
+        <v>72.700000000000031</v>
+      </c>
+      <c r="AT13" s="7">
+        <f t="shared" ref="AT13:AU13" si="78">AT11-AT12</f>
+        <v>240.20000000000002</v>
+      </c>
+      <c r="AU13" s="7">
         <f t="shared" si="78"/>
-        <v>142.20000000000005</v>
-      </c>
-      <c r="AA13" s="7">
-        <f t="shared" ref="AA13:AB13" si="79">AA11-AA12</f>
-        <v>89.599999999999937</v>
-      </c>
-      <c r="AB13" s="7">
+        <v>260.91000000000008</v>
+      </c>
+      <c r="AV13" s="7">
+        <f t="shared" ref="AV13:AW13" si="79">AV11-AV12</f>
+        <v>327.29000000000008</v>
+      </c>
+      <c r="AW13" s="7">
         <f t="shared" si="79"/>
-        <v>18.700000000000124</v>
-      </c>
-      <c r="AC13" s="7">
-        <f t="shared" ref="AC13:AE13" si="80">AC11-AC12</f>
-        <v>156.00000000000011</v>
-      </c>
-      <c r="AD13" s="7">
-        <f t="shared" ref="AD13" si="81">AD11-AD12</f>
-        <v>155.10000000000008</v>
-      </c>
-      <c r="AE13" s="7">
+        <v>481.69999999999987</v>
+      </c>
+      <c r="AX13" s="7">
+        <f t="shared" ref="AX13:AY13" si="80">AX11-AX12</f>
+        <v>419.40000000000009</v>
+      </c>
+      <c r="AY13" s="7">
         <f t="shared" si="80"/>
-        <v>102.20000000000013</v>
-      </c>
-      <c r="AF13" s="7">
-        <f t="shared" ref="AF13" si="82">AF11-AF12</f>
-        <v>119.99999999999997</v>
-      </c>
-      <c r="AG13" s="7">
-        <f t="shared" ref="AG13:AH13" si="83">AG11-AG12</f>
-        <v>89.399999999999949</v>
-      </c>
-      <c r="AH13" s="7">
+        <v>417</v>
+      </c>
+      <c r="AZ13" s="7">
+        <f t="shared" ref="AZ13:BF13" si="81">AZ11-AZ12</f>
+        <v>454.49999999999966</v>
+      </c>
+      <c r="BA13" s="7">
+        <f t="shared" si="81"/>
+        <v>416.10284599999989</v>
+      </c>
+      <c r="BB13" s="7">
+        <f t="shared" si="81"/>
+        <v>626.50700579999989</v>
+      </c>
+      <c r="BC13" s="7">
+        <f t="shared" si="81"/>
+        <v>680.50923485999988</v>
+      </c>
+      <c r="BD13" s="7">
+        <f t="shared" si="81"/>
+        <v>716.71150665191999</v>
+      </c>
+      <c r="BE13" s="7">
+        <f t="shared" si="81"/>
+        <v>747.46999013228879</v>
+      </c>
+      <c r="BF13" s="7">
+        <f t="shared" si="81"/>
+        <v>779.25810009008489</v>
+      </c>
+      <c r="BG13" s="7">
+        <f t="shared" ref="BG13:BK13" si="82">BG11-BG12</f>
+        <v>812.11277629872143</v>
+      </c>
+      <c r="BH13" s="7">
+        <f t="shared" si="82"/>
+        <v>846.0719920674145</v>
+      </c>
+      <c r="BI13" s="7">
+        <f t="shared" si="82"/>
+        <v>881.17479353795704</v>
+      </c>
+      <c r="BJ13" s="7">
+        <f t="shared" si="82"/>
+        <v>917.46133983702134</v>
+      </c>
+      <c r="BK13" s="7">
+        <f t="shared" si="82"/>
+        <v>954.97294412763927</v>
+      </c>
+      <c r="BL13" s="1">
+        <f t="shared" ref="BL13:CQ13" si="83">BK13*(1+$BN$19)</f>
+        <v>945.42321468636283</v>
+      </c>
+      <c r="BM13" s="1">
         <f t="shared" si="83"/>
-        <v>105.39999999999995</v>
-      </c>
-      <c r="AI13" s="7">
-        <f t="shared" ref="AI13" si="84">AI11-AI12</f>
-        <v>116.30000000000004</v>
-      </c>
-      <c r="AJ13" s="7">
-        <f t="shared" ref="AJ13" si="85">AJ11-AJ12</f>
-        <v>98.499999999999929</v>
-      </c>
-      <c r="AK13" s="7">
-        <f t="shared" ref="AK13:AL13" si="86">AK11-AK12</f>
-        <v>136.30000000000001</v>
-      </c>
-      <c r="AL13" s="7">
+        <v>935.96898253949917</v>
+      </c>
+      <c r="BN13" s="1">
+        <f t="shared" si="83"/>
+        <v>926.60929271410419</v>
+      </c>
+      <c r="BO13" s="1">
+        <f t="shared" si="83"/>
+        <v>917.34319978696317</v>
+      </c>
+      <c r="BP13" s="1">
+        <f t="shared" si="83"/>
+        <v>908.1697677890935</v>
+      </c>
+      <c r="BQ13" s="1">
+        <f t="shared" si="83"/>
+        <v>899.08807011120257</v>
+      </c>
+      <c r="BR13" s="1">
+        <f t="shared" si="83"/>
+        <v>890.09718941009055</v>
+      </c>
+      <c r="BS13" s="1">
+        <f t="shared" si="83"/>
+        <v>881.19621751598959</v>
+      </c>
+      <c r="BT13" s="1">
+        <f t="shared" si="83"/>
+        <v>872.38425534082967</v>
+      </c>
+      <c r="BU13" s="1">
+        <f t="shared" si="83"/>
+        <v>863.66041278742136</v>
+      </c>
+      <c r="BV13" s="1">
+        <f t="shared" si="83"/>
+        <v>855.02380865954717</v>
+      </c>
+      <c r="BW13" s="1">
+        <f t="shared" si="83"/>
+        <v>846.47357057295164</v>
+      </c>
+      <c r="BX13" s="1">
+        <f t="shared" si="83"/>
+        <v>838.00883486722216</v>
+      </c>
+      <c r="BY13" s="1">
+        <f t="shared" si="83"/>
+        <v>829.62874651854997</v>
+      </c>
+      <c r="BZ13" s="1">
+        <f t="shared" si="83"/>
+        <v>821.33245905336446</v>
+      </c>
+      <c r="CA13" s="1">
+        <f t="shared" si="83"/>
+        <v>813.11913446283086</v>
+      </c>
+      <c r="CB13" s="1">
+        <f t="shared" si="83"/>
+        <v>804.98794311820257</v>
+      </c>
+      <c r="CC13" s="1">
+        <f t="shared" si="83"/>
+        <v>796.93806368702053</v>
+      </c>
+      <c r="CD13" s="1">
+        <f t="shared" si="83"/>
+        <v>788.96868305015028</v>
+      </c>
+      <c r="CE13" s="1">
+        <f t="shared" si="83"/>
+        <v>781.07899621964873</v>
+      </c>
+      <c r="CF13" s="1">
+        <f t="shared" si="83"/>
+        <v>773.26820625745222</v>
+      </c>
+      <c r="CG13" s="1">
+        <f t="shared" si="83"/>
+        <v>765.53552419487767</v>
+      </c>
+      <c r="CH13" s="1">
+        <f t="shared" si="83"/>
+        <v>757.8801689529289</v>
+      </c>
+      <c r="CI13" s="1">
+        <f t="shared" si="83"/>
+        <v>750.30136726339958</v>
+      </c>
+      <c r="CJ13" s="1">
+        <f t="shared" si="83"/>
+        <v>742.7983535907656</v>
+      </c>
+      <c r="CK13" s="1">
+        <f t="shared" si="83"/>
+        <v>735.37037005485797</v>
+      </c>
+      <c r="CL13" s="1">
+        <f t="shared" si="83"/>
+        <v>728.01666635430934</v>
+      </c>
+      <c r="CM13" s="1">
+        <f t="shared" si="83"/>
+        <v>720.73649969076621</v>
+      </c>
+      <c r="CN13" s="1">
+        <f t="shared" si="83"/>
+        <v>713.52913469385851</v>
+      </c>
+      <c r="CO13" s="1">
+        <f t="shared" si="83"/>
+        <v>706.39384334691988</v>
+      </c>
+      <c r="CP13" s="1">
+        <f t="shared" si="83"/>
+        <v>699.32990491345072</v>
+      </c>
+      <c r="CQ13" s="1">
+        <f t="shared" si="83"/>
+        <v>692.3366058643162</v>
+      </c>
+      <c r="CR13" s="1">
+        <f t="shared" ref="CR13:DW13" si="84">CQ13*(1+$BN$19)</f>
+        <v>685.41323980567302</v>
+      </c>
+      <c r="CS13" s="1">
+        <f t="shared" si="84"/>
+        <v>678.55910740761624</v>
+      </c>
+      <c r="CT13" s="1">
+        <f t="shared" si="84"/>
+        <v>671.7735163335401</v>
+      </c>
+      <c r="CU13" s="1">
+        <f t="shared" si="84"/>
+        <v>665.05578117020468</v>
+      </c>
+      <c r="CV13" s="1">
+        <f t="shared" si="84"/>
+        <v>658.40522335850267</v>
+      </c>
+      <c r="CW13" s="1">
+        <f t="shared" si="84"/>
+        <v>651.82117112491767</v>
+      </c>
+      <c r="CX13" s="1">
+        <f t="shared" si="84"/>
+        <v>645.30295941366853</v>
+      </c>
+      <c r="CY13" s="1">
+        <f t="shared" si="84"/>
+        <v>638.84992981953189</v>
+      </c>
+      <c r="CZ13" s="1">
+        <f t="shared" si="84"/>
+        <v>632.46143052133652</v>
+      </c>
+      <c r="DA13" s="1">
+        <f t="shared" si="84"/>
+        <v>626.13681621612318</v>
+      </c>
+      <c r="DB13" s="1">
+        <f t="shared" si="84"/>
+        <v>619.87544805396192</v>
+      </c>
+      <c r="DC13" s="1">
+        <f t="shared" si="84"/>
+        <v>613.67669357342231</v>
+      </c>
+      <c r="DD13" s="1">
+        <f t="shared" si="84"/>
+        <v>607.53992663768804</v>
+      </c>
+      <c r="DE13" s="1">
+        <f t="shared" si="84"/>
+        <v>601.46452737131119</v>
+      </c>
+      <c r="DF13" s="1">
+        <f t="shared" si="84"/>
+        <v>595.44988209759811</v>
+      </c>
+      <c r="DG13" s="1">
+        <f t="shared" si="84"/>
+        <v>589.49538327662208</v>
+      </c>
+      <c r="DH13" s="1">
+        <f t="shared" si="84"/>
+        <v>583.60042944385589</v>
+      </c>
+      <c r="DI13" s="1">
+        <f t="shared" si="84"/>
+        <v>577.76442514941732</v>
+      </c>
+      <c r="DJ13" s="1">
+        <f t="shared" si="84"/>
+        <v>571.98678089792315</v>
+      </c>
+      <c r="DK13" s="1">
+        <f t="shared" si="84"/>
+        <v>566.26691308894397</v>
+      </c>
+      <c r="DL13" s="1">
+        <f t="shared" si="84"/>
+        <v>560.60424395805455</v>
+      </c>
+      <c r="DM13" s="1">
+        <f t="shared" si="84"/>
+        <v>554.99820151847405</v>
+      </c>
+      <c r="DN13" s="1">
+        <f t="shared" si="84"/>
+        <v>549.44821950328935</v>
+      </c>
+      <c r="DO13" s="1">
+        <f t="shared" si="84"/>
+        <v>543.95373730825645</v>
+      </c>
+      <c r="DP13" s="1">
+        <f t="shared" si="84"/>
+        <v>538.51419993517391</v>
+      </c>
+      <c r="DQ13" s="1">
+        <f t="shared" si="84"/>
+        <v>533.12905793582217</v>
+      </c>
+      <c r="DR13" s="1">
+        <f t="shared" si="84"/>
+        <v>527.79776735646396</v>
+      </c>
+      <c r="DS13" s="1">
+        <f t="shared" si="84"/>
+        <v>522.51978968289927</v>
+      </c>
+      <c r="DT13" s="1">
+        <f t="shared" si="84"/>
+        <v>517.29459178607033</v>
+      </c>
+      <c r="DU13" s="1">
+        <f t="shared" si="84"/>
+        <v>512.12164586820961</v>
+      </c>
+      <c r="DV13" s="1">
+        <f t="shared" si="84"/>
+        <v>507.0004294095275</v>
+      </c>
+      <c r="DW13" s="1">
+        <f t="shared" si="84"/>
+        <v>501.93042511543223</v>
+      </c>
+      <c r="DX13" s="1">
+        <f t="shared" ref="DX13:FC13" si="85">DW13*(1+$BN$19)</f>
+        <v>496.9111208642779</v>
+      </c>
+      <c r="DY13" s="1">
+        <f t="shared" si="85"/>
+        <v>491.9420096556351</v>
+      </c>
+      <c r="DZ13" s="1">
+        <f t="shared" si="85"/>
+        <v>487.02258955907877</v>
+      </c>
+      <c r="EA13" s="1">
+        <f t="shared" si="85"/>
+        <v>482.15236366348796</v>
+      </c>
+      <c r="EB13" s="1">
+        <f t="shared" si="85"/>
+        <v>477.33084002685308</v>
+      </c>
+      <c r="EC13" s="1">
+        <f t="shared" si="85"/>
+        <v>472.55753162658453</v>
+      </c>
+      <c r="ED13" s="1">
+        <f t="shared" si="85"/>
+        <v>467.83195631031867</v>
+      </c>
+      <c r="EE13" s="1">
+        <f t="shared" si="85"/>
+        <v>463.1536367472155</v>
+      </c>
+      <c r="EF13" s="1">
+        <f t="shared" si="85"/>
+        <v>458.52210037974334</v>
+      </c>
+      <c r="EG13" s="1">
+        <f t="shared" si="85"/>
+        <v>453.93687937594592</v>
+      </c>
+      <c r="EH13" s="1">
+        <f t="shared" si="85"/>
+        <v>449.39751058218644</v>
+      </c>
+      <c r="EI13" s="1">
+        <f t="shared" si="85"/>
+        <v>444.9035354763646</v>
+      </c>
+      <c r="EJ13" s="1">
+        <f t="shared" si="85"/>
+        <v>440.45450012160097</v>
+      </c>
+      <c r="EK13" s="1">
+        <f t="shared" si="85"/>
+        <v>436.04995512038494</v>
+      </c>
+      <c r="EL13" s="1">
+        <f t="shared" si="85"/>
+        <v>431.68945556918106</v>
+      </c>
+      <c r="EM13" s="1">
+        <f t="shared" si="85"/>
+        <v>427.37256101348925</v>
+      </c>
+      <c r="EN13" s="1">
+        <f t="shared" si="85"/>
+        <v>423.09883540335437</v>
+      </c>
+      <c r="EO13" s="1">
+        <f t="shared" si="85"/>
+        <v>418.8678470493208</v>
+      </c>
+      <c r="EP13" s="1">
+        <f t="shared" si="85"/>
+        <v>414.67916857882761</v>
+      </c>
+      <c r="EQ13" s="1">
+        <f t="shared" si="85"/>
+        <v>410.53237689303933</v>
+      </c>
+      <c r="ER13" s="1">
+        <f t="shared" si="85"/>
+        <v>406.42705312410891</v>
+      </c>
+      <c r="ES13" s="1">
+        <f t="shared" si="85"/>
+        <v>402.3627825928678</v>
+      </c>
+      <c r="ET13" s="1">
+        <f t="shared" si="85"/>
+        <v>398.33915476693915</v>
+      </c>
+      <c r="EU13" s="1">
+        <f t="shared" si="85"/>
+        <v>394.35576321926976</v>
+      </c>
+      <c r="EV13" s="1">
+        <f t="shared" si="85"/>
+        <v>390.41220558707704</v>
+      </c>
+      <c r="EW13" s="1">
+        <f t="shared" si="85"/>
+        <v>386.50808353120624</v>
+      </c>
+      <c r="EX13" s="1">
+        <f t="shared" si="85"/>
+        <v>382.64300269589415</v>
+      </c>
+      <c r="EY13" s="1">
+        <f t="shared" si="85"/>
+        <v>378.81657266893524</v>
+      </c>
+      <c r="EZ13" s="1">
+        <f t="shared" si="85"/>
+        <v>375.02840694224591</v>
+      </c>
+      <c r="FA13" s="1">
+        <f t="shared" si="85"/>
+        <v>371.27812287282347</v>
+      </c>
+      <c r="FB13" s="1">
+        <f t="shared" si="85"/>
+        <v>367.56534164409521</v>
+      </c>
+      <c r="FC13" s="1">
+        <f t="shared" si="85"/>
+        <v>363.88968822765423</v>
+      </c>
+      <c r="FD13" s="1">
+        <f t="shared" ref="FD13:FQ13" si="86">FC13*(1+$BN$19)</f>
+        <v>360.25079134537771</v>
+      </c>
+      <c r="FE13" s="1">
         <f t="shared" si="86"/>
-        <v>103.39999999999981</v>
-      </c>
-      <c r="AM13" s="7">
-        <f t="shared" ref="AM13:AP13" si="87">AM11-AM12</f>
-        <v>128.77058999999997</v>
-      </c>
-      <c r="AN13" s="7">
-        <f t="shared" si="87"/>
-        <v>108.21626400000002</v>
-      </c>
-      <c r="AO13" s="7">
-        <f t="shared" si="87"/>
-        <v>104.19512999999999</v>
-      </c>
-      <c r="AP13" s="7">
-        <f t="shared" si="87"/>
-        <v>108.39184199999991</v>
-      </c>
-      <c r="AR13" s="7">
-        <f t="shared" ref="AR13:AS13" si="88">AR11-AR12</f>
-        <v>98.999999999999915</v>
-      </c>
-      <c r="AS13" s="7">
-        <f t="shared" si="88"/>
-        <v>72.700000000000031</v>
-      </c>
-      <c r="AT13" s="7">
-        <f t="shared" ref="AT13:AU13" si="89">AT11-AT12</f>
-        <v>240.20000000000002</v>
-      </c>
-      <c r="AU13" s="7">
-        <f t="shared" si="89"/>
-        <v>260.91000000000008</v>
-      </c>
-      <c r="AV13" s="7">
-        <f t="shared" ref="AV13:AW13" si="90">AV11-AV12</f>
-        <v>327.29000000000008</v>
-      </c>
-      <c r="AW13" s="7">
-        <f t="shared" si="90"/>
-        <v>481.69999999999987</v>
-      </c>
-      <c r="AX13" s="7">
-        <f t="shared" ref="AX13:AY13" si="91">AX11-AX12</f>
-        <v>419.40000000000009</v>
-      </c>
-      <c r="AY13" s="7">
-        <f t="shared" si="91"/>
-        <v>417</v>
-      </c>
-      <c r="AZ13" s="7">
-        <f t="shared" ref="AZ13:BF13" si="92">AZ11-AZ12</f>
-        <v>454.49999999999966</v>
-      </c>
-      <c r="BA13" s="7">
-        <f t="shared" si="92"/>
-        <v>449.57382599999983</v>
-      </c>
-      <c r="BB13" s="7">
-        <f t="shared" si="92"/>
-        <v>445.48834746</v>
-      </c>
-      <c r="BC13" s="7">
-        <f t="shared" si="92"/>
-        <v>441.07713379859996</v>
-      </c>
-      <c r="BD13" s="7">
-        <f t="shared" si="92"/>
-        <v>443.01880423842584</v>
-      </c>
-      <c r="BE13" s="7">
-        <f t="shared" si="92"/>
-        <v>444.81088622468707</v>
-      </c>
-      <c r="BF13" s="7">
-        <f t="shared" si="92"/>
-        <v>446.44488788468811</v>
-      </c>
-      <c r="BG13" s="7">
-        <f t="shared" ref="BG13:BK13" si="93">BG11-BG12</f>
-        <v>447.91179344939428</v>
-      </c>
-      <c r="BH13" s="7">
-        <f t="shared" si="93"/>
-        <v>449.20204019520247</v>
-      </c>
-      <c r="BI13" s="7">
-        <f t="shared" si="93"/>
-        <v>450.30549405110008</v>
-      </c>
-      <c r="BJ13" s="7">
-        <f t="shared" si="93"/>
-        <v>451.21142381318828</v>
-      </c>
-      <c r="BK13" s="7">
-        <f t="shared" si="93"/>
-        <v>451.90847390519497</v>
-      </c>
-      <c r="BL13" s="1">
-        <f t="shared" ref="BL13:CQ13" si="94">BK13*(1+$BN$19)</f>
-        <v>447.38938916614302</v>
-      </c>
-      <c r="BM13" s="1">
-        <f t="shared" si="94"/>
-        <v>442.9154952744816</v>
-      </c>
-      <c r="BN13" s="1">
-        <f t="shared" si="94"/>
-        <v>438.4863403217368</v>
-      </c>
-      <c r="BO13" s="1">
-        <f t="shared" si="94"/>
-        <v>434.10147691851944</v>
-      </c>
-      <c r="BP13" s="1">
-        <f t="shared" si="94"/>
-        <v>429.76046214933422</v>
-      </c>
-      <c r="BQ13" s="1">
-        <f t="shared" si="94"/>
-        <v>425.46285752784087</v>
-      </c>
-      <c r="BR13" s="1">
-        <f t="shared" si="94"/>
-        <v>421.20822895256248</v>
-      </c>
-      <c r="BS13" s="1">
-        <f t="shared" si="94"/>
-        <v>416.99614666303682</v>
-      </c>
-      <c r="BT13" s="1">
-        <f t="shared" si="94"/>
-        <v>412.82618519640647</v>
-      </c>
-      <c r="BU13" s="1">
-        <f t="shared" si="94"/>
-        <v>408.69792334444242</v>
-      </c>
-      <c r="BV13" s="1">
-        <f t="shared" si="94"/>
-        <v>404.61094411099799</v>
-      </c>
-      <c r="BW13" s="1">
-        <f t="shared" si="94"/>
-        <v>400.564834669888</v>
-      </c>
-      <c r="BX13" s="1">
-        <f t="shared" si="94"/>
-        <v>396.55918632318912</v>
-      </c>
-      <c r="BY13" s="1">
-        <f t="shared" si="94"/>
-        <v>392.59359445995722</v>
-      </c>
-      <c r="BZ13" s="1">
-        <f t="shared" si="94"/>
-        <v>388.66765851535763</v>
-      </c>
-      <c r="CA13" s="1">
-        <f t="shared" si="94"/>
-        <v>384.78098193020406</v>
-      </c>
-      <c r="CB13" s="1">
-        <f t="shared" si="94"/>
-        <v>380.93317211090204</v>
-      </c>
-      <c r="CC13" s="1">
-        <f t="shared" si="94"/>
-        <v>377.12384038979303</v>
-      </c>
-      <c r="CD13" s="1">
-        <f t="shared" si="94"/>
-        <v>373.35260198589509</v>
-      </c>
-      <c r="CE13" s="1">
-        <f t="shared" si="94"/>
-        <v>369.61907596603612</v>
-      </c>
-      <c r="CF13" s="1">
-        <f t="shared" si="94"/>
-        <v>365.92288520637578</v>
-      </c>
-      <c r="CG13" s="1">
-        <f t="shared" si="94"/>
-        <v>362.26365635431205</v>
-      </c>
-      <c r="CH13" s="1">
-        <f t="shared" si="94"/>
-        <v>358.64101979076895</v>
-      </c>
-      <c r="CI13" s="1">
-        <f t="shared" si="94"/>
-        <v>355.05460959286125</v>
-      </c>
-      <c r="CJ13" s="1">
-        <f t="shared" si="94"/>
-        <v>351.50406349693264</v>
-      </c>
-      <c r="CK13" s="1">
-        <f t="shared" si="94"/>
-        <v>347.98902286196329</v>
-      </c>
-      <c r="CL13" s="1">
-        <f t="shared" si="94"/>
-        <v>344.50913263334365</v>
-      </c>
-      <c r="CM13" s="1">
-        <f t="shared" si="94"/>
-        <v>341.0640413070102</v>
-      </c>
-      <c r="CN13" s="1">
-        <f t="shared" si="94"/>
-        <v>337.6534008939401</v>
-      </c>
-      <c r="CO13" s="1">
-        <f t="shared" si="94"/>
-        <v>334.27686688500069</v>
-      </c>
-      <c r="CP13" s="1">
-        <f t="shared" si="94"/>
-        <v>330.93409821615069</v>
-      </c>
-      <c r="CQ13" s="1">
-        <f t="shared" si="94"/>
-        <v>327.62475723398916</v>
-      </c>
-      <c r="CR13" s="1">
-        <f t="shared" ref="CR13:DW13" si="95">CQ13*(1+$BN$19)</f>
-        <v>324.34850966164925</v>
-      </c>
-      <c r="CS13" s="1">
-        <f t="shared" si="95"/>
-        <v>321.10502456503275</v>
-      </c>
-      <c r="CT13" s="1">
-        <f t="shared" si="95"/>
-        <v>317.89397431938244</v>
-      </c>
-      <c r="CU13" s="1">
-        <f t="shared" si="95"/>
-        <v>314.7150345761886</v>
-      </c>
-      <c r="CV13" s="1">
-        <f t="shared" si="95"/>
-        <v>311.56788423042673</v>
-      </c>
-      <c r="CW13" s="1">
-        <f t="shared" si="95"/>
-        <v>308.45220538812248</v>
-      </c>
-      <c r="CX13" s="1">
-        <f t="shared" si="95"/>
-        <v>305.36768333424124</v>
-      </c>
-      <c r="CY13" s="1">
-        <f t="shared" si="95"/>
-        <v>302.31400650089881</v>
-      </c>
-      <c r="CZ13" s="1">
-        <f t="shared" si="95"/>
-        <v>299.29086643588982</v>
-      </c>
-      <c r="DA13" s="1">
-        <f t="shared" si="95"/>
-        <v>296.29795777153095</v>
-      </c>
-      <c r="DB13" s="1">
-        <f t="shared" si="95"/>
-        <v>293.33497819381563</v>
-      </c>
-      <c r="DC13" s="1">
-        <f t="shared" si="95"/>
-        <v>290.40162841187748</v>
-      </c>
-      <c r="DD13" s="1">
-        <f t="shared" si="95"/>
-        <v>287.49761212775871</v>
-      </c>
-      <c r="DE13" s="1">
-        <f t="shared" si="95"/>
-        <v>284.62263600648112</v>
-      </c>
-      <c r="DF13" s="1">
-        <f t="shared" si="95"/>
-        <v>281.77640964641631</v>
-      </c>
-      <c r="DG13" s="1">
-        <f t="shared" si="95"/>
-        <v>278.95864554995217</v>
-      </c>
-      <c r="DH13" s="1">
-        <f t="shared" si="95"/>
-        <v>276.16905909445262</v>
-      </c>
-      <c r="DI13" s="1">
-        <f t="shared" si="95"/>
-        <v>273.40736850350811</v>
-      </c>
-      <c r="DJ13" s="1">
-        <f t="shared" si="95"/>
-        <v>270.67329481847304</v>
-      </c>
-      <c r="DK13" s="1">
-        <f t="shared" si="95"/>
-        <v>267.96656187028833</v>
-      </c>
-      <c r="DL13" s="1">
-        <f t="shared" si="95"/>
-        <v>265.28689625158546</v>
-      </c>
-      <c r="DM13" s="1">
-        <f t="shared" si="95"/>
-        <v>262.63402728906959</v>
-      </c>
-      <c r="DN13" s="1">
-        <f t="shared" si="95"/>
-        <v>260.00768701617892</v>
-      </c>
-      <c r="DO13" s="1">
-        <f t="shared" si="95"/>
-        <v>257.40761014601713</v>
-      </c>
-      <c r="DP13" s="1">
-        <f t="shared" si="95"/>
-        <v>254.83353404455696</v>
-      </c>
-      <c r="DQ13" s="1">
-        <f t="shared" si="95"/>
-        <v>252.28519870411139</v>
-      </c>
-      <c r="DR13" s="1">
-        <f t="shared" si="95"/>
-        <v>249.76234671707027</v>
-      </c>
-      <c r="DS13" s="1">
-        <f t="shared" si="95"/>
-        <v>247.26472324989956</v>
-      </c>
-      <c r="DT13" s="1">
-        <f t="shared" si="95"/>
-        <v>244.79207601740057</v>
-      </c>
-      <c r="DU13" s="1">
-        <f t="shared" si="95"/>
-        <v>242.34415525722656</v>
-      </c>
-      <c r="DV13" s="1">
-        <f t="shared" si="95"/>
-        <v>239.9207137046543</v>
-      </c>
-      <c r="DW13" s="1">
-        <f t="shared" si="95"/>
-        <v>237.52150656760776</v>
-      </c>
-      <c r="DX13" s="1">
-        <f t="shared" ref="DX13:FC13" si="96">DW13*(1+$BN$19)</f>
-        <v>235.14629150193167</v>
-      </c>
-      <c r="DY13" s="1">
-        <f t="shared" si="96"/>
-        <v>232.79482858691236</v>
-      </c>
-      <c r="DZ13" s="1">
-        <f t="shared" si="96"/>
-        <v>230.46688030104323</v>
-      </c>
-      <c r="EA13" s="1">
-        <f t="shared" si="96"/>
-        <v>228.1622114980328</v>
-      </c>
-      <c r="EB13" s="1">
-        <f t="shared" si="96"/>
-        <v>225.88058938305247</v>
-      </c>
-      <c r="EC13" s="1">
-        <f t="shared" si="96"/>
-        <v>223.62178348922194</v>
-      </c>
-      <c r="ED13" s="1">
-        <f t="shared" si="96"/>
-        <v>221.38556565432972</v>
-      </c>
-      <c r="EE13" s="1">
-        <f t="shared" si="96"/>
-        <v>219.17170999778642</v>
-      </c>
-      <c r="EF13" s="1">
-        <f t="shared" si="96"/>
-        <v>216.97999289780856</v>
-      </c>
-      <c r="EG13" s="1">
-        <f t="shared" si="96"/>
-        <v>214.81019296883048</v>
-      </c>
-      <c r="EH13" s="1">
-        <f t="shared" si="96"/>
-        <v>212.66209103914218</v>
-      </c>
-      <c r="EI13" s="1">
-        <f t="shared" si="96"/>
-        <v>210.53547012875075</v>
-      </c>
-      <c r="EJ13" s="1">
-        <f t="shared" si="96"/>
-        <v>208.43011542746325</v>
-      </c>
-      <c r="EK13" s="1">
-        <f t="shared" si="96"/>
-        <v>206.34581427318861</v>
-      </c>
-      <c r="EL13" s="1">
-        <f t="shared" si="96"/>
-        <v>204.28235613045672</v>
-      </c>
-      <c r="EM13" s="1">
-        <f t="shared" si="96"/>
-        <v>202.23953256915215</v>
-      </c>
-      <c r="EN13" s="1">
-        <f t="shared" si="96"/>
-        <v>200.21713724346063</v>
-      </c>
-      <c r="EO13" s="1">
-        <f t="shared" si="96"/>
-        <v>198.21496587102601</v>
-      </c>
-      <c r="EP13" s="1">
-        <f t="shared" si="96"/>
-        <v>196.23281621231575</v>
-      </c>
-      <c r="EQ13" s="1">
-        <f t="shared" si="96"/>
-        <v>194.2704880501926</v>
-      </c>
-      <c r="ER13" s="1">
-        <f t="shared" si="96"/>
-        <v>192.32778316969066</v>
-      </c>
-      <c r="ES13" s="1">
-        <f t="shared" si="96"/>
-        <v>190.40450533799375</v>
-      </c>
-      <c r="ET13" s="1">
-        <f t="shared" si="96"/>
-        <v>188.50046028461381</v>
-      </c>
-      <c r="EU13" s="1">
-        <f t="shared" si="96"/>
-        <v>186.61545568176766</v>
-      </c>
-      <c r="EV13" s="1">
-        <f t="shared" si="96"/>
-        <v>184.74930112494997</v>
-      </c>
-      <c r="EW13" s="1">
-        <f t="shared" si="96"/>
-        <v>182.90180811370047</v>
-      </c>
-      <c r="EX13" s="1">
-        <f t="shared" si="96"/>
-        <v>181.07279003256346</v>
-      </c>
-      <c r="EY13" s="1">
-        <f t="shared" si="96"/>
-        <v>179.26206213223782</v>
-      </c>
-      <c r="EZ13" s="1">
-        <f t="shared" si="96"/>
-        <v>177.46944151091543</v>
-      </c>
-      <c r="FA13" s="1">
-        <f t="shared" si="96"/>
-        <v>175.69474709580626</v>
-      </c>
-      <c r="FB13" s="1">
-        <f t="shared" si="96"/>
-        <v>173.9377996248482</v>
-      </c>
-      <c r="FC13" s="1">
-        <f t="shared" si="96"/>
-        <v>172.1984216285997</v>
-      </c>
-      <c r="FD13" s="1">
-        <f t="shared" ref="FD13:FQ13" si="97">FC13*(1+$BN$19)</f>
-        <v>170.47643741231371</v>
-      </c>
-      <c r="FE13" s="1">
-        <f t="shared" si="97"/>
-        <v>168.77167303819058</v>
+        <v>356.64828343192391</v>
       </c>
       <c r="FF13" s="1">
-        <f t="shared" si="97"/>
-        <v>167.08395630780868</v>
+        <f t="shared" si="86"/>
+        <v>353.08180059760468</v>
       </c>
       <c r="FG13" s="1">
-        <f t="shared" si="97"/>
-        <v>165.41311674473059</v>
+        <f t="shared" si="86"/>
+        <v>349.55098259162861</v>
       </c>
       <c r="FH13" s="1">
-        <f t="shared" si="97"/>
-        <v>163.75898557728328</v>
+        <f t="shared" si="86"/>
+        <v>346.0554727657123</v>
       </c>
       <c r="FI13" s="1">
-        <f t="shared" si="97"/>
-        <v>162.12139572151045</v>
+        <f t="shared" si="86"/>
+        <v>342.59491803805514</v>
       </c>
       <c r="FJ13" s="1">
-        <f t="shared" si="97"/>
-        <v>160.50018176429535</v>
+        <f t="shared" si="86"/>
+        <v>339.1689688576746</v>
       </c>
       <c r="FK13" s="1">
-        <f t="shared" si="97"/>
-        <v>158.89517994665241</v>
+        <f t="shared" si="86"/>
+        <v>335.77727916909782</v>
       </c>
       <c r="FL13" s="1">
-        <f t="shared" si="97"/>
-        <v>157.30622814718589</v>
+        <f t="shared" si="86"/>
+        <v>332.41950637740683</v>
       </c>
       <c r="FM13" s="1">
-        <f t="shared" si="97"/>
-        <v>155.73316586571403</v>
+        <f t="shared" si="86"/>
+        <v>329.09531131363275</v>
       </c>
       <c r="FN13" s="1">
-        <f t="shared" si="97"/>
-        <v>154.17583420705688</v>
+        <f t="shared" si="86"/>
+        <v>325.80435820049644</v>
       </c>
       <c r="FO13" s="1">
-        <f t="shared" si="97"/>
-        <v>152.6340758649863</v>
+        <f t="shared" si="86"/>
+        <v>322.54631461849146</v>
       </c>
       <c r="FP13" s="1">
-        <f t="shared" si="97"/>
-        <v>151.10773510633643</v>
+        <f t="shared" si="86"/>
+        <v>319.32085147230657</v>
       </c>
       <c r="FQ13" s="1">
-        <f t="shared" si="97"/>
-        <v>149.59665775527307</v>
+        <f t="shared" si="86"/>
+        <v>316.12764295758348</v>
       </c>
     </row>
     <row r="14" spans="2:173" x14ac:dyDescent="0.3">
@@ -4104,16 +4066,20 @@
         <v>56.9</v>
       </c>
       <c r="AM14" s="5">
-        <v>56.9</v>
+        <f>56.7</f>
+        <v>56.7</v>
       </c>
       <c r="AN14" s="5">
-        <v>56.9</v>
+        <f>55.7</f>
+        <v>55.7</v>
       </c>
       <c r="AO14" s="5">
-        <v>56.9</v>
+        <f>55.7</f>
+        <v>55.7</v>
       </c>
       <c r="AP14" s="5">
-        <v>56.9</v>
+        <f>55.7</f>
+        <v>55.7</v>
       </c>
       <c r="AR14" s="5">
         <v>55.85</v>
@@ -4143,37 +4109,48 @@
         <v>56.9</v>
       </c>
       <c r="BA14" s="5">
-        <v>56.9</v>
+        <f t="shared" ref="BA14:BK14" si="87">55.7</f>
+        <v>55.7</v>
       </c>
       <c r="BB14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BC14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BD14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BE14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BF14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BG14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BH14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BI14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BJ14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
       <c r="BK14" s="5">
-        <v>56.9</v>
+        <f t="shared" si="87"/>
+        <v>55.7</v>
       </c>
     </row>
     <row r="15" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4181,244 +4158,244 @@
         <v>37</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:T15" si="98">C13/C14</f>
+        <f t="shared" ref="C15:T15" si="88">C13/C14</f>
         <v>0.42256042972247099</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.43688451208594453</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.46911369740375997</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.44404655326768128</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.42256042972247099</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.67144136078782435</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.76096687555953424</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>-0.55326768128916703</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.1512981199641894</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>0.90062667860340184</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.1745747538048337</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.0743061772605187</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.0850492390331239</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.0529991047448526</v>
       </c>
       <c r="Q15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.1996418979409136</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.3339301700984767</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.5326768128916735</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="88"/>
         <v>1.1928379588182625</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" ref="U15:V15" si="99">U13/U14</f>
+        <f t="shared" ref="U15:V15" si="89">U13/U14</f>
         <v>1.6019695613249789</v>
       </c>
       <c r="V15" s="8">
+        <f t="shared" si="89"/>
+        <v>1.5326768128916737</v>
+      </c>
+      <c r="W15" s="8">
+        <f t="shared" ref="W15:X15" si="90">W13/W14</f>
+        <v>1.9534467323187106</v>
+      </c>
+      <c r="X15" s="8">
+        <f t="shared" si="90"/>
+        <v>2.0158172231985927</v>
+      </c>
+      <c r="Y15" s="8">
+        <f t="shared" ref="Y15:Z15" si="91">Y13/Y14</f>
+        <v>2.0333919156414764</v>
+      </c>
+      <c r="Z15" s="8">
+        <f t="shared" si="91"/>
+        <v>2.4991212653778567</v>
+      </c>
+      <c r="AA15" s="8">
+        <f t="shared" ref="AA15:AB15" si="92">AA13/AA14</f>
+        <v>1.5746924428822484</v>
+      </c>
+      <c r="AB15" s="8">
+        <f t="shared" si="92"/>
+        <v>0.32864674868190025</v>
+      </c>
+      <c r="AC15" s="8">
+        <f t="shared" ref="AC15:AE15" si="93">AC13/AC14</f>
+        <v>2.7416520210896329</v>
+      </c>
+      <c r="AD15" s="8">
+        <f t="shared" ref="AD15" si="94">AD13/AD14</f>
+        <v>2.7258347978910384</v>
+      </c>
+      <c r="AE15" s="8">
+        <f t="shared" si="93"/>
+        <v>1.7961335676625683</v>
+      </c>
+      <c r="AF15" s="8">
+        <f t="shared" ref="AF15" si="95">AF13/AF14</f>
+        <v>2.1089630931458694</v>
+      </c>
+      <c r="AG15" s="8">
+        <f t="shared" ref="AG15:AH15" si="96">AG13/AG14</f>
+        <v>1.5711775043936722</v>
+      </c>
+      <c r="AH15" s="8">
+        <f t="shared" si="96"/>
+        <v>1.8523725834797882</v>
+      </c>
+      <c r="AI15" s="8">
+        <f t="shared" ref="AI15" si="97">AI13/AI14</f>
+        <v>2.0439367311072063</v>
+      </c>
+      <c r="AJ15" s="8">
+        <f t="shared" ref="AJ15" si="98">AJ13/AJ14</f>
+        <v>1.7311072056239003</v>
+      </c>
+      <c r="AK15" s="8">
+        <f t="shared" ref="AK15:AL15" si="99">AK13/AK14</f>
+        <v>2.395430579964851</v>
+      </c>
+      <c r="AL15" s="8">
         <f t="shared" si="99"/>
-        <v>1.5326768128916737</v>
-      </c>
-      <c r="W15" s="8">
-        <f t="shared" ref="W15:X15" si="100">W13/W14</f>
-        <v>1.9534467323187106</v>
-      </c>
-      <c r="X15" s="8">
+        <v>1.8172231985940213</v>
+      </c>
+      <c r="AM15" s="8">
+        <f t="shared" ref="AM15:AP15" si="100">AM13/AM14</f>
+        <v>1.2980599647266318</v>
+      </c>
+      <c r="AN15" s="8">
         <f t="shared" si="100"/>
-        <v>2.0158172231985927</v>
-      </c>
-      <c r="Y15" s="8">
-        <f t="shared" ref="Y15:Z15" si="101">Y13/Y14</f>
-        <v>2.0333919156414764</v>
-      </c>
-      <c r="Z15" s="8">
+        <v>1.5798922800718147</v>
+      </c>
+      <c r="AO15" s="8">
+        <f t="shared" si="100"/>
+        <v>2.3279849192100537</v>
+      </c>
+      <c r="AP15" s="8">
+        <f t="shared" si="100"/>
+        <v>2.2411864631956888</v>
+      </c>
+      <c r="AR15" s="8">
+        <f t="shared" ref="AR15:AS15" si="101">AR13/AR14</f>
+        <v>1.7726051924798552</v>
+      </c>
+      <c r="AS15" s="8">
         <f t="shared" si="101"/>
-        <v>2.4991212653778567</v>
-      </c>
-      <c r="AA15" s="8">
-        <f t="shared" ref="AA15:AB15" si="102">AA13/AA14</f>
-        <v>1.5746924428822484</v>
-      </c>
-      <c r="AB15" s="8">
+        <v>1.3017009847806631</v>
+      </c>
+      <c r="AT15" s="8">
+        <f t="shared" ref="AT15:AU15" si="102">AT13/AT14</f>
+        <v>4.3008057296329456</v>
+      </c>
+      <c r="AU15" s="8">
         <f t="shared" si="102"/>
-        <v>0.32864674868190025</v>
-      </c>
-      <c r="AC15" s="8">
-        <f t="shared" ref="AC15:AE15" si="103">AC13/AC14</f>
-        <v>2.7416520210896329</v>
-      </c>
-      <c r="AD15" s="8">
-        <f t="shared" ref="AD15" si="104">AD13/AD14</f>
-        <v>2.7258347978910384</v>
-      </c>
-      <c r="AE15" s="8">
+        <v>4.6716204118173694</v>
+      </c>
+      <c r="AV15" s="8">
+        <f t="shared" ref="AV15:AW15" si="103">AV13/AV14</f>
+        <v>5.8601611459265905</v>
+      </c>
+      <c r="AW15" s="8">
         <f t="shared" si="103"/>
-        <v>1.7961335676625683</v>
-      </c>
-      <c r="AF15" s="8">
-        <f t="shared" ref="AF15" si="105">AF13/AF14</f>
-        <v>2.1089630931458694</v>
-      </c>
-      <c r="AG15" s="8">
-        <f t="shared" ref="AG15:AH15" si="106">AG13/AG14</f>
-        <v>1.5711775043936722</v>
-      </c>
-      <c r="AH15" s="8">
+        <v>8.6248880931065326</v>
+      </c>
+      <c r="AX15" s="8">
+        <f t="shared" ref="AX15:AY15" si="104">AX13/AX14</f>
+        <v>7.3708260105448176</v>
+      </c>
+      <c r="AY15" s="8">
+        <f t="shared" si="104"/>
+        <v>7.3286467486818987</v>
+      </c>
+      <c r="AZ15" s="8">
+        <f t="shared" ref="AZ15:BF15" si="105">AZ13/AZ14</f>
+        <v>7.9876977152899764</v>
+      </c>
+      <c r="BA15" s="8">
+        <f t="shared" si="105"/>
+        <v>7.4704281149012539</v>
+      </c>
+      <c r="BB15" s="8">
+        <f t="shared" si="105"/>
+        <v>11.247881612208255</v>
+      </c>
+      <c r="BC15" s="8">
+        <f t="shared" si="105"/>
+        <v>12.217400984919207</v>
+      </c>
+      <c r="BD15" s="8">
+        <f t="shared" si="105"/>
+        <v>12.8673520045228</v>
+      </c>
+      <c r="BE15" s="8">
+        <f t="shared" si="105"/>
+        <v>13.419568943129061</v>
+      </c>
+      <c r="BF15" s="8">
+        <f t="shared" si="105"/>
+        <v>13.990271096769925</v>
+      </c>
+      <c r="BG15" s="8">
+        <f t="shared" ref="BG15:BK15" si="106">BG13/BG14</f>
+        <v>14.580121657068606</v>
+      </c>
+      <c r="BH15" s="8">
         <f t="shared" si="106"/>
-        <v>1.8523725834797882</v>
-      </c>
-      <c r="AI15" s="8">
-        <f t="shared" ref="AI15" si="107">AI13/AI14</f>
-        <v>2.0439367311072063</v>
-      </c>
-      <c r="AJ15" s="8">
-        <f t="shared" ref="AJ15" si="108">AJ13/AJ14</f>
-        <v>1.7311072056239003</v>
-      </c>
-      <c r="AK15" s="8">
-        <f t="shared" ref="AK15:AL15" si="109">AK13/AK14</f>
-        <v>2.395430579964851</v>
-      </c>
-      <c r="AL15" s="8">
-        <f t="shared" si="109"/>
-        <v>1.8172231985940213</v>
-      </c>
-      <c r="AM15" s="8">
-        <f t="shared" ref="AM15:AP15" si="110">AM13/AM14</f>
-        <v>2.2631035149384879</v>
-      </c>
-      <c r="AN15" s="8">
-        <f t="shared" si="110"/>
-        <v>1.9018675571177508</v>
-      </c>
-      <c r="AO15" s="8">
-        <f t="shared" si="110"/>
-        <v>1.8311973637961334</v>
-      </c>
-      <c r="AP15" s="8">
-        <f t="shared" si="110"/>
-        <v>1.9049532864674854</v>
-      </c>
-      <c r="AR15" s="8">
-        <f t="shared" ref="AR15:AS15" si="111">AR13/AR14</f>
-        <v>1.7726051924798552</v>
-      </c>
-      <c r="AS15" s="8">
-        <f t="shared" si="111"/>
-        <v>1.3017009847806631</v>
-      </c>
-      <c r="AT15" s="8">
-        <f t="shared" ref="AT15:AU15" si="112">AT13/AT14</f>
-        <v>4.3008057296329456</v>
-      </c>
-      <c r="AU15" s="8">
-        <f t="shared" si="112"/>
-        <v>4.6716204118173694</v>
-      </c>
-      <c r="AV15" s="8">
-        <f t="shared" ref="AV15:AW15" si="113">AV13/AV14</f>
-        <v>5.8601611459265905</v>
-      </c>
-      <c r="AW15" s="8">
-        <f t="shared" si="113"/>
-        <v>8.6248880931065326</v>
-      </c>
-      <c r="AX15" s="8">
-        <f t="shared" ref="AX15:AY15" si="114">AX13/AX14</f>
-        <v>7.3708260105448176</v>
-      </c>
-      <c r="AY15" s="8">
-        <f t="shared" si="114"/>
-        <v>7.3286467486818987</v>
-      </c>
-      <c r="AZ15" s="8">
-        <f t="shared" ref="AZ15:BF15" si="115">AZ13/AZ14</f>
-        <v>7.9876977152899764</v>
-      </c>
-      <c r="BA15" s="8">
-        <f t="shared" si="115"/>
-        <v>7.9011217223198562</v>
-      </c>
-      <c r="BB15" s="8">
-        <f t="shared" si="115"/>
-        <v>7.8293206934973636</v>
-      </c>
-      <c r="BC15" s="8">
-        <f t="shared" si="115"/>
-        <v>7.7517949700984179</v>
-      </c>
-      <c r="BD15" s="8">
-        <f t="shared" si="115"/>
-        <v>7.7859192309037937</v>
-      </c>
-      <c r="BE15" s="8">
-        <f t="shared" si="115"/>
-        <v>7.8174145206447641</v>
-      </c>
-      <c r="BF15" s="8">
-        <f t="shared" si="115"/>
-        <v>7.8461315972704417</v>
-      </c>
-      <c r="BG15" s="8">
-        <f t="shared" ref="BG15:BK15" si="116">BG13/BG14</f>
-        <v>7.8719120114129053</v>
-      </c>
-      <c r="BH15" s="8">
-        <f t="shared" si="116"/>
-        <v>7.8945877011459133</v>
+        <v>15.189802371048733</v>
       </c>
       <c r="BI15" s="8">
-        <f t="shared" si="116"/>
-        <v>7.9139805632882263</v>
+        <f t="shared" si="106"/>
+        <v>15.820014246641957</v>
       </c>
       <c r="BJ15" s="8">
-        <f t="shared" si="116"/>
-        <v>7.9299020002317802</v>
+        <f t="shared" si="106"/>
+        <v>16.471478273555139</v>
       </c>
       <c r="BK15" s="8">
-        <f t="shared" si="116"/>
-        <v>7.9421524412160807</v>
+        <f t="shared" si="106"/>
+        <v>17.144936160280775</v>
       </c>
     </row>
     <row r="17" spans="2:66" x14ac:dyDescent="0.3">
@@ -4430,220 +4407,220 @@
         <v>0</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" ref="H17:V17" si="117">H3/D3-1</f>
+        <f t="shared" ref="H17:V17" si="107">H3/D3-1</f>
         <v>0.22973925299506681</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.26550452564532345</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.27368421052631575</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.30612873421619979</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.27707736389684801</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.2402649006622517</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.26446280991735538</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.22919122848384799</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.23758133273502358</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.2560871422469031</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.2533174886116063</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.24956838672549408</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.14646748490726802</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.10899506886583921</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="107"/>
         <v>0.14333122629582817</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17" si="118">W3/S3-1</f>
+        <f t="shared" ref="W17" si="108">W3/S3-1</f>
         <v>0.198649063555419</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" ref="X17" si="119">X3/T3-1</f>
+        <f t="shared" ref="X17" si="109">X3/T3-1</f>
         <v>0.39378221955153547</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="120">Y3/U3-1</f>
+        <f t="shared" ref="Y17" si="110">Y3/U3-1</f>
         <v>0.51563937442502294</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="121">Z3/V3-1</f>
+        <f t="shared" ref="Z17" si="111">Z3/V3-1</f>
         <v>0.53075328265376642</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17" si="122">AA3/W3-1</f>
+        <f t="shared" ref="AA17" si="112">AA3/W3-1</f>
         <v>0.50051229508196715</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" ref="AB17" si="123">AB3/X3-1</f>
+        <f t="shared" ref="AB17" si="113">AB3/X3-1</f>
         <v>0.35568413886997963</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" ref="AC17" si="124">AC3/Y3-1</f>
+        <f t="shared" ref="AC17" si="114">AC3/Y3-1</f>
         <v>0.24117349519473952</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" ref="AD17" si="125">AD3/Z3-1</f>
+        <f t="shared" ref="AD17" si="115">AD3/Z3-1</f>
         <v>0.11178329571106072</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17" si="126">AE3/AA3-1</f>
+        <f t="shared" ref="AE17" si="116">AE3/AA3-1</f>
         <v>3.3543871628542332E-2</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" ref="AF17" si="127">AF3/AB3-1</f>
+        <f t="shared" ref="AF17" si="117">AF3/AB3-1</f>
         <v>-2.0671185873294862E-2</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" ref="AG17" si="128">AG3/AC3-1</f>
+        <f t="shared" ref="AG17" si="118">AG3/AC3-1</f>
         <v>-6.0966663949792332E-2</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" ref="AH17" si="129">AH3/AD3-1</f>
+        <f t="shared" ref="AH17" si="119">AH3/AD3-1</f>
         <v>-6.0099082270770765E-2</v>
       </c>
       <c r="AI17" s="9">
-        <f t="shared" ref="AI17" si="130">AI3/AE3-1</f>
+        <f t="shared" ref="AI17" si="120">AI3/AE3-1</f>
         <v>-3.7492773969774573E-2</v>
       </c>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17" si="131">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ17" si="121">AJ3/AF3-1</f>
         <v>-2.0167492736284487E-2</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" ref="AK17" si="132">AK3/AG3-1</f>
+        <f t="shared" ref="AK17" si="122">AK3/AG3-1</f>
         <v>1.3366895234788734E-2</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" ref="AL17" si="133">AL3/AH3-1</f>
+        <f t="shared" ref="AL17" si="123">AL3/AH3-1</f>
         <v>7.8631296984360111E-2</v>
       </c>
       <c r="AM17" s="9">
-        <f t="shared" ref="AM17" si="134">AM3/AI3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AM17" si="124">AM3/AI3-1</f>
+        <v>0.11685971685971697</v>
       </c>
       <c r="AN17" s="9">
-        <f t="shared" ref="AN17" si="135">AN3/AJ3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AN17" si="125">AN3/AJ3-1</f>
+        <v>0.18035932321646619</v>
       </c>
       <c r="AO17" s="9">
-        <f t="shared" ref="AO17" si="136">AO3/AK3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AO17" si="126">AO3/AK3-1</f>
+        <v>0.17999999999999994</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" ref="AP17" si="137">AP3/AL3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AP17" si="127">AP3/AL3-1</f>
+        <v>0.12999999999999989</v>
       </c>
       <c r="AS17" s="9">
         <f>AS3/AR3-1</f>
         <v>0.18864213717938227</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" ref="AT17:BG17" si="138">AT3/AS3-1</f>
+        <f t="shared" ref="AT17:BG17" si="128">AT3/AS3-1</f>
         <v>0.27052740434332989</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="128"/>
         <v>0.24466330240382006</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="128"/>
         <v>0.15942610265107104</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="128"/>
         <v>0.41313339449817255</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="128"/>
         <v>0.28377946889468353</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="128"/>
         <v>-2.7815200945136453E-2</v>
       </c>
       <c r="AZ17" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="128"/>
         <v>7.9735635859716769E-3</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" si="138"/>
-        <v>2.4790921973814939E-2</v>
+        <f t="shared" si="128"/>
+        <v>0.15132067091097534</v>
       </c>
       <c r="BB17" s="9">
-        <f t="shared" si="138"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="128"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="BC17" s="9">
-        <f t="shared" si="138"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="128"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="BD17" s="9">
-        <f t="shared" si="138"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="128"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="BE17" s="9">
-        <f t="shared" si="138"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="128"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BF17" s="9">
-        <f t="shared" si="138"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="128"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BG17" s="9">
-        <f t="shared" si="138"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="128"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BH17" s="9">
-        <f t="shared" ref="BH17" si="139">BH3/BG3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BH17" si="129">BH3/BG3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BI17" s="9">
-        <f t="shared" ref="BI17" si="140">BI3/BH3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BI17" si="130">BI3/BH3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BJ17" s="9">
-        <f t="shared" ref="BJ17" si="141">BJ3/BI3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BJ17" si="131">BJ3/BI3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BK17" s="9">
-        <f t="shared" ref="BK17" si="142">BK3/BJ3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BK17" si="132">BK3/BJ3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="18" spans="2:66" x14ac:dyDescent="0.3">
@@ -4651,19 +4628,19 @@
         <v>42</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:F18" si="143">C5/C3</f>
+        <f t="shared" ref="C18:F18" si="133">C5/C3</f>
         <v>0.3603326147212812</v>
       </c>
       <c r="D18" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="133"/>
         <v>0.36293164200140943</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="133"/>
         <v>0.360375460945357</v>
       </c>
       <c r="F18" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="133"/>
         <v>0.3677830940988836</v>
       </c>
       <c r="G18" s="9">
@@ -4671,223 +4648,223 @@
         <v>0.3603326147212812</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" ref="H18:V18" si="144">H5/H3</f>
+        <f t="shared" ref="H18:V18" si="134">H5/H3</f>
         <v>0.36934097421203438</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.36582781456953639</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.36363636363636365</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.34543739684036784</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35113304913619026</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35689876121315672</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.36819172113289755</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.33876846345674272</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35473812070559657</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35810236354361508</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35192793931731975</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.34940128953024252</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.33656978399063853</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35081263416130032</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="134"/>
         <v>0.35618521078092602</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18:Z18" si="145">W5/W3</f>
+        <f t="shared" ref="W18:Z18" si="135">W5/W3</f>
         <v>0.33491290983606559</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="135"/>
         <v>0.33775811209439521</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="135"/>
         <v>0.33899848254931719</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="135"/>
         <v>0.34329571106094814</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18:AL18" si="146">AA5/AA3</f>
+        <f t="shared" ref="AA18:AL18" si="136">AA5/AA3</f>
         <v>0.33356094230112665</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.29173989455184546</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.32610644714320652</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.32364167952570461</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.29317036914691558</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.30892155187147496</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.31056331915632324</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.31080964313488291</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.2841698841698842</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.29277864992150704</v>
       </c>
       <c r="AK18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.34561027837259101</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="136"/>
         <v>0.3044140030441399</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" ref="AM18:AP18" si="147">AM5/AM3</f>
+        <f t="shared" ref="AM18:AP18" si="137">AM5/AM3</f>
+        <v>0.26864869017438736</v>
+      </c>
+      <c r="AN18" s="9">
+        <f t="shared" si="137"/>
+        <v>0.28771981675779523</v>
+      </c>
+      <c r="AO18" s="9">
+        <f t="shared" si="137"/>
         <v>0.3</v>
       </c>
-      <c r="AN18" s="9">
-        <f t="shared" si="147"/>
+      <c r="AP18" s="9">
+        <f t="shared" si="137"/>
         <v>0.3</v>
       </c>
-      <c r="AO18" s="9">
-        <f t="shared" si="147"/>
+      <c r="AR18" s="9">
+        <f t="shared" ref="AR18:BF18" si="138">AR5/AR3</f>
+        <v>0.36286159141194785</v>
+      </c>
+      <c r="AS18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.36483971044467428</v>
+      </c>
+      <c r="AT18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.35596071409192032</v>
+      </c>
+      <c r="AU18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.35119605543663551</v>
+      </c>
+      <c r="AV18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.34854182020545371</v>
+      </c>
+      <c r="AW18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.33912511308605187</v>
+      </c>
+      <c r="AX18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.31877629697183246</v>
+      </c>
+      <c r="AY18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.30572433642468821</v>
+      </c>
+      <c r="AZ18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.30677467797542246</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="138"/>
+        <v>0.28944947108653546</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" si="138"/>
         <v>0.3</v>
       </c>
-      <c r="AP18" s="9">
-        <f t="shared" si="147"/>
+      <c r="BC18" s="9">
+        <f t="shared" si="138"/>
         <v>0.3</v>
       </c>
-      <c r="AR18" s="9">
-        <f t="shared" ref="AR18:BF18" si="148">AR5/AR3</f>
-        <v>0.36286159141194785</v>
-      </c>
-      <c r="AS18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.36483971044467428</v>
-      </c>
-      <c r="AT18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.35596071409192032</v>
-      </c>
-      <c r="AU18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.35119605543663551</v>
-      </c>
-      <c r="AV18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.34854182020545371</v>
-      </c>
-      <c r="AW18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.33912511308605187</v>
-      </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.31877629697183246</v>
-      </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.30572433642468821</v>
-      </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="148"/>
-        <v>0.30677467797542246</v>
-      </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="148"/>
+      <c r="BD18" s="9">
+        <f t="shared" si="138"/>
         <v>0.3</v>
       </c>
-      <c r="BB18" s="9">
-        <f t="shared" si="148"/>
+      <c r="BE18" s="9">
+        <f t="shared" si="138"/>
         <v>0.3</v>
       </c>
-      <c r="BC18" s="9">
-        <f t="shared" si="148"/>
+      <c r="BF18" s="9">
+        <f t="shared" si="138"/>
         <v>0.3</v>
       </c>
-      <c r="BD18" s="9">
-        <f t="shared" si="148"/>
+      <c r="BG18" s="9">
+        <f t="shared" ref="BG18:BK18" si="139">BG5/BG3</f>
         <v>0.3</v>
       </c>
-      <c r="BE18" s="9">
-        <f t="shared" si="148"/>
+      <c r="BH18" s="9">
+        <f t="shared" si="139"/>
         <v>0.3</v>
       </c>
-      <c r="BF18" s="9">
-        <f t="shared" si="148"/>
+      <c r="BI18" s="9">
+        <f t="shared" si="139"/>
         <v>0.3</v>
       </c>
-      <c r="BG18" s="9">
-        <f t="shared" ref="BG18:BK18" si="149">BG5/BG3</f>
+      <c r="BJ18" s="9">
+        <f t="shared" si="139"/>
         <v>0.3</v>
       </c>
-      <c r="BH18" s="9">
-        <f t="shared" si="149"/>
-        <v>0.3</v>
-      </c>
-      <c r="BI18" s="9">
-        <f t="shared" si="149"/>
-        <v>0.3</v>
-      </c>
-      <c r="BJ18" s="9">
-        <f t="shared" si="149"/>
-        <v>0.3</v>
-      </c>
       <c r="BK18" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="139"/>
         <v>0.3</v>
       </c>
     </row>
@@ -4896,19 +4873,19 @@
         <v>43</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:F19" si="150">C8/C3</f>
+        <f t="shared" ref="C19:F19" si="140">C8/C3</f>
         <v>9.547274407145058E-2</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="140"/>
         <v>0.113107822410148</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="140"/>
         <v>0.11364398256788467</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="140"/>
         <v>0.11961722488038277</v>
       </c>
       <c r="G19" s="9">
@@ -4916,224 +4893,224 @@
         <v>9.547274407145058E-2</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ref="H19:V19" si="151">H8/H3</f>
+        <f t="shared" ref="H19:V19" si="141">H8/H3</f>
         <v>0.1169054441260745</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13033112582781453</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13047833708990739</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.11459561424192405</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.12183082791115099</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13797522426313535</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.15508021390374327</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.12392096681373484</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13218151163001507</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13705152185002553</v>
       </c>
       <c r="R19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.1338495575221238</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13447958243782618</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.13191435529270371</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.14780742103649197</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="141"/>
         <v>0.15480304077401519</v>
       </c>
       <c r="W19" s="9">
-        <f t="shared" ref="W19:Z19" si="152">W8/W3</f>
+        <f t="shared" ref="W19:Z19" si="142">W8/W3</f>
         <v>0.13742315573770492</v>
       </c>
       <c r="X19" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="142"/>
         <v>0.14216019968232349</v>
       </c>
       <c r="Y19" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="142"/>
         <v>0.14577642893272638</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="142"/>
         <v>0.14961625282167046</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" ref="AA19:AL19" si="153">AA8/AA3</f>
+        <f t="shared" ref="AA19:AL19" si="143">AA8/AA3</f>
         <v>0.11027654489586884</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>7.791446983011141E-2</v>
       </c>
       <c r="AC19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.14687423587904483</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.13839031917485592</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>9.9347592699644979E-2</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.12331225431550161</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>9.8949743945837998E-2</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.10593623088222587</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>9.4894894894894943E-2</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.10509331937903363</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.15160599571734476</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="143"/>
         <v>0.10926860530321224</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" ref="AM19:AP19" si="154">AM8/AM3</f>
-        <v>0.12159596178287764</v>
+        <f t="shared" ref="AM19:AP19" si="144">AM8/AM3</f>
+        <v>7.6361680878850757E-2</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="154"/>
-        <v>0.11085620335973943</v>
+        <f t="shared" si="144"/>
+        <v>9.3394414068272577E-2</v>
       </c>
       <c r="AO19" s="9">
-        <f t="shared" si="154"/>
-        <v>0.10336421650730382</v>
+        <f t="shared" si="144"/>
+        <v>0.11217871012230972</v>
       </c>
       <c r="AP19" s="9">
-        <f t="shared" si="154"/>
-        <v>0.10641474385362105</v>
+        <f t="shared" si="144"/>
+        <v>0.11005813924636612</v>
       </c>
       <c r="AR19" s="9">
-        <f t="shared" ref="AR19:BF19" si="155">AR8/AR3</f>
+        <f t="shared" ref="AR19:BF19" si="145">AR8/AR3</f>
         <v>0.11021879865606811</v>
       </c>
       <c r="AS19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.11933815925542919</v>
       </c>
       <c r="AT19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.13337674317651527</v>
       </c>
       <c r="AU19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.13201295672228064</v>
       </c>
       <c r="AV19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.14266698753139717</v>
       </c>
       <c r="AW19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.14432441062210632</v>
       </c>
       <c r="AX19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.11874313428814229</v>
       </c>
       <c r="AY19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.10685427992751306</v>
       </c>
       <c r="AZ19" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="145"/>
         <v>0.11516741047822494</v>
       </c>
       <c r="BA19" s="9">
-        <f t="shared" si="155"/>
-        <v>0.11064141178247999</v>
+        <f t="shared" si="145"/>
+        <v>9.8393593332315538E-2</v>
       </c>
       <c r="BB19" s="9">
-        <f t="shared" si="155"/>
-        <v>0.10819643720774257</v>
+        <f t="shared" si="145"/>
+        <v>0.13238492473998906</v>
       </c>
       <c r="BC19" s="9">
-        <f t="shared" si="155"/>
-        <v>0.10570467527810141</v>
+        <f t="shared" si="145"/>
+        <v>0.13554747332980058</v>
       </c>
       <c r="BD19" s="9">
-        <f t="shared" si="155"/>
-        <v>0.10488308769901994</v>
+        <f t="shared" si="145"/>
+        <v>0.13712874762470634</v>
       </c>
       <c r="BE19" s="9">
-        <f t="shared" si="155"/>
-        <v>0.10402896199799472</v>
+        <f t="shared" si="145"/>
+        <v>0.1387100219196121</v>
       </c>
       <c r="BF19" s="9">
-        <f t="shared" si="155"/>
-        <v>0.10314100953653281</v>
+        <f t="shared" si="145"/>
+        <v>0.14027594403689742</v>
       </c>
       <c r="BG19" s="9">
-        <f t="shared" ref="BG19:BK19" si="156">BG8/BG3</f>
-        <v>0.10221789064095357</v>
+        <f t="shared" ref="BG19:BK19" si="146">BG8/BG3</f>
+        <v>0.14182666302683045</v>
       </c>
       <c r="BH19" s="9">
-        <f t="shared" si="156"/>
-        <v>0.10125821258119307</v>
+        <f t="shared" si="146"/>
+        <v>0.1433623264925894</v>
       </c>
       <c r="BI19" s="9">
-        <f t="shared" si="156"/>
-        <v>0.10026052746956077</v>
+        <f t="shared" si="146"/>
+        <v>0.14488308060431185</v>
       </c>
       <c r="BJ19" s="9">
-        <f t="shared" si="156"/>
-        <v>9.9223330076279717E-2</v>
+        <f t="shared" si="146"/>
+        <v>0.14638907011300784</v>
       </c>
       <c r="BK19" s="9">
-        <f t="shared" si="156"/>
-        <v>9.8145055558512287E-2</v>
+        <f t="shared" si="146"/>
+        <v>0.14788043836433787</v>
       </c>
       <c r="BM19" t="s">
         <v>45</v>
@@ -5151,225 +5128,225 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9">
-        <f t="shared" ref="G20:V20" si="157">G6/C6-1</f>
+        <f t="shared" ref="G20:V20" si="147">G6/C6-1</f>
         <v>0</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.25154320987654333</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.20679468242245203</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.19273743016759748</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.1311475409836067</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.14919852034525261</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.14075887392900865</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.14051522248243575</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.13489409141583053</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.19914163090128767</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.27575107296137347</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.28336755646817235</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>0.22888015717092336</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>2.1743020758768772E-2</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>-2.0185029436501356E-2</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" si="157"/>
+        <f t="shared" si="147"/>
         <v>3.1200000000000117E-2</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" ref="W20" si="158">W6/S6-1</f>
+        <f t="shared" ref="W20" si="148">W6/S6-1</f>
         <v>9.0327737809752229E-2</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20" si="159">X6/T6-1</f>
+        <f t="shared" ref="X20" si="149">X6/T6-1</f>
         <v>0.33023907522550133</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="160">Y6/U6-1</f>
+        <f t="shared" ref="Y20" si="150">Y6/U6-1</f>
         <v>0.45493562231759666</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="161">Z6/V6-1</f>
+        <f t="shared" ref="Z20" si="151">Z6/V6-1</f>
         <v>0.48099301784328929</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" ref="AA20" si="162">AA6/W6-1</f>
+        <f t="shared" ref="AA20" si="152">AA6/W6-1</f>
         <v>0.73973607038123168</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" ref="AB20" si="163">AB6/X6-1</f>
+        <f t="shared" ref="AB20" si="153">AB6/X6-1</f>
         <v>0.53061224489795911</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" ref="AC20" si="164">AC6/Y6-1</f>
+        <f t="shared" ref="AC20" si="154">AC6/Y6-1</f>
         <v>0.16814159292035402</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20" si="165">AD6/Z6-1</f>
+        <f t="shared" ref="AD20" si="155">AD6/Z6-1</f>
         <v>7.386066003142977E-2</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" ref="AE20" si="166">AE6/AA6-1</f>
+        <f t="shared" ref="AE20" si="156">AE6/AA6-1</f>
         <v>-0.10703750526759381</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" ref="AF20" si="167">AF6/AB6-1</f>
+        <f t="shared" ref="AF20" si="157">AF6/AB6-1</f>
         <v>-0.16387096774193544</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" ref="AG20" si="168">AG6/AC6-1</f>
+        <f t="shared" ref="AG20" si="158">AG6/AC6-1</f>
         <v>-1.6161616161616155E-2</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" ref="AH20" si="169">AH6/AD6-1</f>
+        <f t="shared" ref="AH20" si="159">AH6/AD6-1</f>
         <v>4.3902439024390505E-2</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" ref="AI20" si="170">AI6/AE6-1</f>
+        <f t="shared" ref="AI20" si="160">AI6/AE6-1</f>
         <v>-6.3237376120811706E-2</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20" si="171">AJ6/AF6-1</f>
+        <f t="shared" ref="AJ20" si="161">AJ6/AF6-1</f>
         <v>-1.5432098765432167E-3</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" ref="AK20" si="172">AK6/AG6-1</f>
+        <f t="shared" ref="AK20" si="162">AK6/AG6-1</f>
         <v>6.1601642710472193E-2</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" ref="AL20" si="173">AL6/AH6-1</f>
+        <f t="shared" ref="AL20" si="163">AL6/AH6-1</f>
         <v>1.355140186915893E-2</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" ref="AM20" si="174">AM6/AI6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AM20" si="164">AM6/AI6-1</f>
+        <v>0.10277078085642311</v>
       </c>
       <c r="AN20" s="9">
-        <f t="shared" ref="AN20" si="175">AN6/AJ6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AN20" si="165">AN6/AJ6-1</f>
+        <v>0.19371458011334353</v>
       </c>
       <c r="AO20" s="9">
-        <f t="shared" ref="AO20" si="176">AO6/AK6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AO20" si="166">AO6/AK6-1</f>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AP20" s="9">
-        <f t="shared" ref="AP20" si="177">AP6/AL6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AP20" si="167">AP6/AL6-1</f>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AR20" s="9"/>
       <c r="AS20" s="9">
-        <f t="shared" ref="AS20:BG20" si="178">AS6/AR6-1</f>
+        <f t="shared" ref="AS20:BG20" si="168">AS6/AR6-1</f>
         <v>0.15561044460127005</v>
       </c>
       <c r="AT20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>0.1404580152671755</v>
       </c>
       <c r="AU20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>0.22479250334672041</v>
       </c>
       <c r="AV20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>5.9524329996065051E-2</v>
       </c>
       <c r="AW20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>0.33838123336565662</v>
       </c>
       <c r="AX20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>0.34546015107137329</v>
       </c>
       <c r="AY20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>-6.610907424381296E-2</v>
       </c>
       <c r="AZ20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
         <v>1.4722119985277615E-3</v>
       </c>
       <c r="BA20" s="9">
-        <f t="shared" si="178"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="168"/>
+        <v>0.13840499816244023</v>
       </c>
       <c r="BB20" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="168"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="BC20" s="9">
+        <f t="shared" si="168"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BD20" s="9">
+        <f t="shared" si="168"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BE20" s="9">
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC20" s="9">
-        <f t="shared" si="178"/>
+      <c r="BF20" s="9">
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD20" s="9">
-        <f t="shared" si="178"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BE20" s="9">
-        <f t="shared" si="178"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BF20" s="9">
-        <f t="shared" si="178"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BG20" s="9">
-        <f t="shared" si="178"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="168"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH20" s="9">
-        <f t="shared" ref="BH20" si="179">BH6/BG6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BH20" si="169">BH6/BG6-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BI20" s="9">
-        <f t="shared" ref="BI20" si="180">BI6/BH6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BI20" si="170">BI6/BH6-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BJ20" s="9">
-        <f t="shared" ref="BJ20" si="181">BJ6/BI6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BJ20" si="171">BJ6/BI6-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BK20" s="9">
-        <f t="shared" ref="BK20" si="182">BK6/BJ6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="BK20" si="172">BK6/BJ6-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BM20" t="s">
         <v>46</v>
@@ -5383,19 +5360,19 @@
         <v>35</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:F21" si="183">C12/C11</f>
+        <f t="shared" ref="C21:F21" si="173">C12/C11</f>
         <v>0.17482517482517479</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="173"/>
         <v>0.21035598705501618</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="173"/>
         <v>0.21084337349397594</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="173"/>
         <v>0.22741433021806853</v>
       </c>
       <c r="G21" s="9">
@@ -5403,231 +5380,231 @@
         <v>0.17482517482517479</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21:V21" si="184">H12/H11</f>
+        <f t="shared" ref="H21:V21" si="174">H12/H11</f>
         <v>0.13194444444444448</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.15841584158415847</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>1.593090211132437</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>-0.34518828451882855</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.12062937062937064</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>6.0606060606060632E-3</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.23857868020304579</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>5.4602184087363524E-2</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.16593391008367603</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.16249999999999995</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.12146226415094351</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.11295336787564771</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.12422768502694891</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.13946330672309309</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="174"/>
         <v>0.16160626836434872</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21:Z21" si="185">W12/W11</f>
+        <f t="shared" ref="W21:Z21" si="175">W12/W11</f>
         <v>5.1304347826086963E-2</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="175"/>
         <v>6.8993506493506537E-2</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="175"/>
         <v>0.14549483013293943</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="185"/>
+        <f t="shared" si="175"/>
         <v>0.11069418386491554</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" ref="AA21:AL21" si="186">AA12/AA11</f>
+        <f t="shared" ref="AA21:AL21" si="176">AA12/AA11</f>
         <v>0.15630885122410557</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>-1.124999999999984</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.183673469387755</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.22874191944306302</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.19654088050314444</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.27903225806451626</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.22099039172209917</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>5.9822150363783327E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.2632759910246823</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.28111814345991554</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="176"/>
         <v>0.24745269286754043</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" ref="AM21:AP21" si="187">AM12/AM11</f>
+        <f t="shared" ref="AM21:AP21" si="177">AM12/AM11</f>
+        <v>0.22116402116402109</v>
+      </c>
+      <c r="AN21" s="9">
+        <f t="shared" si="177"/>
+        <v>0.28860145513338703</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" si="177"/>
         <v>0.22</v>
       </c>
-      <c r="AN21" s="9">
-        <f t="shared" si="187"/>
+      <c r="AP21" s="9">
+        <f t="shared" si="177"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AR21" s="9">
+        <f t="shared" ref="AR21:BF21" si="178">AR12/AR11</f>
+        <v>0.20673076923076938</v>
+      </c>
+      <c r="AS21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.58314220183486232</v>
+      </c>
+      <c r="AT21" s="9">
+        <f t="shared" si="178"/>
+        <v>3.8430744595676546E-2</v>
+      </c>
+      <c r="AU21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.12858621956514474</v>
+      </c>
+      <c r="AV21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.13561694485527145</v>
+      </c>
+      <c r="AW21" s="9">
+        <f t="shared" si="178"/>
+        <v>9.709465791940021E-2</v>
+      </c>
+      <c r="AX21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.17310725552050468</v>
+      </c>
+      <c r="AY21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.22273998136067102</v>
+      </c>
+      <c r="AZ21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.22227926078028762</v>
+      </c>
+      <c r="BA21" s="9">
+        <f t="shared" si="178"/>
+        <v>0.23578737513216599</v>
+      </c>
+      <c r="BB21" s="9">
+        <f t="shared" si="178"/>
         <v>0.22</v>
       </c>
-      <c r="AO21" s="9">
-        <f t="shared" si="187"/>
+      <c r="BC21" s="9">
+        <f t="shared" si="178"/>
         <v>0.22</v>
       </c>
-      <c r="AP21" s="9">
-        <f t="shared" si="187"/>
+      <c r="BD21" s="9">
+        <f t="shared" si="178"/>
         <v>0.22</v>
       </c>
-      <c r="AR21" s="9">
-        <f t="shared" ref="AR21:BF21" si="188">AR12/AR11</f>
-        <v>0.20673076923076938</v>
-      </c>
-      <c r="AS21" s="9">
-        <f t="shared" si="188"/>
-        <v>0.58314220183486232</v>
-      </c>
-      <c r="AT21" s="9">
-        <f t="shared" si="188"/>
-        <v>3.8430744595676546E-2</v>
-      </c>
-      <c r="AU21" s="9">
-        <f t="shared" si="188"/>
-        <v>0.12858621956514474</v>
-      </c>
-      <c r="AV21" s="9">
-        <f t="shared" si="188"/>
-        <v>0.13561694485527145</v>
-      </c>
-      <c r="AW21" s="9">
-        <f t="shared" si="188"/>
-        <v>9.709465791940021E-2</v>
-      </c>
-      <c r="AX21" s="9">
-        <f t="shared" si="188"/>
-        <v>0.17310725552050468</v>
-      </c>
-      <c r="AY21" s="9">
-        <f t="shared" si="188"/>
-        <v>0.22273998136067102</v>
-      </c>
-      <c r="AZ21" s="9">
-        <f t="shared" si="188"/>
-        <v>0.22227926078028762</v>
-      </c>
-      <c r="BA21" s="9">
-        <f t="shared" si="188"/>
+      <c r="BE21" s="9">
+        <f t="shared" si="178"/>
         <v>0.22</v>
       </c>
-      <c r="BB21" s="9">
-        <f t="shared" si="188"/>
+      <c r="BF21" s="9">
+        <f t="shared" si="178"/>
         <v>0.22</v>
       </c>
-      <c r="BC21" s="9">
-        <f t="shared" si="188"/>
+      <c r="BG21" s="9">
+        <f t="shared" ref="BG21:BK21" si="179">BG12/BG11</f>
         <v>0.22</v>
       </c>
-      <c r="BD21" s="9">
-        <f t="shared" si="188"/>
+      <c r="BH21" s="9">
+        <f t="shared" si="179"/>
         <v>0.22</v>
       </c>
-      <c r="BE21" s="9">
-        <f t="shared" si="188"/>
+      <c r="BI21" s="9">
+        <f t="shared" si="179"/>
         <v>0.22</v>
       </c>
-      <c r="BF21" s="9">
-        <f t="shared" si="188"/>
+      <c r="BJ21" s="9">
+        <f t="shared" si="179"/>
         <v>0.22</v>
       </c>
-      <c r="BG21" s="9">
-        <f t="shared" ref="BG21:BK21" si="189">BG12/BG11</f>
-        <v>0.22</v>
-      </c>
-      <c r="BH21" s="9">
-        <f t="shared" si="189"/>
-        <v>0.22</v>
-      </c>
-      <c r="BI21" s="9">
-        <f t="shared" si="189"/>
-        <v>0.22</v>
-      </c>
-      <c r="BJ21" s="9">
-        <f t="shared" si="189"/>
-        <v>0.22</v>
-      </c>
       <c r="BK21" s="9">
-        <f t="shared" si="189"/>
+        <f t="shared" si="179"/>
         <v>0.22</v>
       </c>
       <c r="BM21" t="s">
         <v>47</v>
       </c>
       <c r="BN21" s="5">
-        <f>NPV(BN20,AV13:FQ13)</f>
-        <v>4723.4001547569496</v>
+        <f>NPV(BN20,BA13:FQ13)</f>
+        <v>8588.676683279371</v>
       </c>
     </row>
     <row r="22" spans="2:66" x14ac:dyDescent="0.3">
@@ -5639,247 +5616,247 @@
         <v>7.2682476131814E-2</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" ref="D22:AP22" si="190">D13/D3</f>
+        <f t="shared" ref="D22:AP22" si="180">D13/D3</f>
         <v>8.5976039464411555E-2</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>8.7831042574589319E-2</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>7.9106858054226473E-2</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>7.2682476131814E-2</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.10744985673352433</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11258278145695361</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>-7.7385424492862454E-2</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.15161518509785424</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11285618128786179</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.1401110636480136</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11883541295305997</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11624784193362742</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.10661904675574252</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11392620302669619</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.1177307206068267</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.13140927233650593</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.10534805022296714</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.13718184605949105</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11831375259156873</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.13972848360655737</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.13013387792148845</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11704602933737987</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.12839729119638829</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>7.6476613178559194E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>1.5649845175328581E-2</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.12714972695411209</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.12596442784049389</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>8.4400033033281127E-2</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.10254657323534436</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>7.7597430778578211E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>9.1074051671995143E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>9.9785499785499818E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>8.5906157334728714E-2</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>0.11674518201284798</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="180"/>
         <v>8.2832652407273749E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="190"/>
-        <v>0.1032572679488567</v>
+        <f t="shared" si="180"/>
+        <v>5.6541445801644018E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="190"/>
-        <v>9.3445679261803749E-2</v>
+        <f t="shared" si="180"/>
+        <v>6.5021427515885979E-2</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="190"/>
-        <v>8.8362736659104879E-2</v>
+        <f t="shared" si="180"/>
+        <v>9.412315174391174E-2</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="190"/>
-        <v>8.5971846067086841E-2</v>
+        <f t="shared" si="180"/>
+        <v>8.8498471904090395E-2</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" ref="AR22:BK22" si="191">AR13/AR3</f>
+        <f t="shared" ref="AR22:BK22" si="181">AR13/AR3</f>
         <v>8.1127591575841942E-2</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>5.0120648052395744E-2</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>0.13033805415377936</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>0.11374624529708477</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>0.12306541128340881</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>0.12817306157202912</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>8.6927684622878129E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>8.8903102014710592E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="181"/>
         <v>9.6131474861989405E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" si="191"/>
-        <v>9.2789207838255006E-2</v>
+        <f t="shared" si="181"/>
+        <v>7.6442714743128679E-2</v>
       </c>
       <c r="BB22" s="9">
-        <f t="shared" si="191"/>
-        <v>9.1035634439302446E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.10463299636206912</v>
       </c>
       <c r="BC22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.9241784188239193E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.10721878671999616</v>
       </c>
       <c r="BD22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.8747164767707373E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.10857951639939693</v>
       </c>
       <c r="BE22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.8223922036409622E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.10994109605118962</v>
       </c>
       <c r="BF22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.7671297432054193E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.11127827939151026</v>
       </c>
       <c r="BG22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.708847847038495E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.11259217140136746</v>
       </c>
       <c r="BH22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.6474598012417414E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.11388379890672193</v>
       </c>
       <c r="BI22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.5828733419165512E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.11515411657432777</v>
       </c>
       <c r="BJ22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.5149905594361558E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.11640401244260058</v>
       </c>
       <c r="BK22" s="9">
-        <f t="shared" si="191"/>
-        <v>8.443707791539623E-2</v>
+        <f t="shared" si="181"/>
+        <v>0.11763431302361885</v>
       </c>
       <c r="BM22" t="s">
         <v>48</v>
       </c>
       <c r="BN22" s="5">
         <f>Main!D8</f>
-        <v>1262.8</v>
+        <v>989.3</v>
       </c>
     </row>
     <row r="23" spans="2:66" x14ac:dyDescent="0.3">
@@ -5888,7 +5865,7 @@
       </c>
       <c r="BN23" s="5">
         <f>BN21+BN22</f>
-        <v>5986.2001547569498</v>
+        <v>9577.9766832793703</v>
       </c>
     </row>
     <row r="24" spans="2:66" x14ac:dyDescent="0.3">
@@ -5897,7 +5874,7 @@
       </c>
       <c r="BN24" s="4">
         <f>BN23/BF14</f>
-        <v>105.20562662138752</v>
+        <v>171.95649341614669</v>
       </c>
     </row>
     <row r="25" spans="2:66" x14ac:dyDescent="0.3">
@@ -5906,7 +5883,7 @@
       </c>
       <c r="BN25" s="4">
         <f>Main!D3</f>
-        <v>149.62</v>
+        <v>153.46</v>
       </c>
     </row>
     <row r="26" spans="2:66" x14ac:dyDescent="0.3">
@@ -5915,7 +5892,7 @@
       </c>
       <c r="BN26" s="10">
         <f>BN24/BN25-1</f>
-        <v>-0.29684783704459616</v>
+        <v>0.12052973684443291</v>
       </c>
     </row>
     <row r="27" spans="2:66" x14ac:dyDescent="0.3">

--- a/Financial Analysis/EPAM.xlsx
+++ b/Financial Analysis/EPAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48187BD9-3C1B-43B6-B4C5-9A0E1EB96207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C513FD3-8E80-42B1-A097-F7C4727CCAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{8184807C-F564-425B-AEBD-E3B1D55FAE77}"/>
   </bookViews>
@@ -293,7 +293,7 @@
     <t>Net Margin</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -406,14 +406,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -430,7 +430,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24848820" y="0"/>
+          <a:off x="25443180" y="0"/>
           <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -829,17 +829,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>153.46</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3">
-        <v>45918</v>
+        <v>45967</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45967</v>
       </c>
       <c r="G3" s="3">
-        <v>45960</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,11 +847,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>55.7</f>
-        <v>55.7</v>
+        <f>55.6</f>
+        <v>55.6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -860,7 +860,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>8547.7220000000016</v>
+        <v>9340.8000000000011</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>7558.4220000000014</v>
+        <v>8351.5000000000018</v>
       </c>
     </row>
   </sheetData>
@@ -1227,12 +1227,11 @@
         <v>1353.4</v>
       </c>
       <c r="AO3" s="7">
-        <f>AK3*1.18</f>
-        <v>1377.6499999999999</v>
+        <v>1394.4</v>
       </c>
       <c r="AP3" s="7">
-        <f>AL3*1.13</f>
-        <v>1410.5789999999995</v>
+        <f>AL3*1.11</f>
+        <v>1385.6129999999998</v>
       </c>
       <c r="AR3" s="7">
         <f>SUM(C3:F3)</f>
@@ -1269,47 +1268,47 @@
       </c>
       <c r="BA3" s="7">
         <f>SUM(AM3:AP3)</f>
-        <v>5443.3289999999997</v>
+        <v>5435.1130000000003</v>
       </c>
       <c r="BB3" s="7">
         <f>BA3*1.1</f>
-        <v>5987.6619000000001</v>
+        <v>5978.6243000000004</v>
       </c>
       <c r="BC3" s="7">
         <f>BB3*1.06</f>
-        <v>6346.9216140000008</v>
+        <v>6337.3417580000005</v>
       </c>
       <c r="BD3" s="7">
         <f>BC3*1.04</f>
-        <v>6600.7984785600011</v>
+        <v>6590.8354283200006</v>
       </c>
       <c r="BE3" s="7">
         <f>BD3*1.03</f>
-        <v>6798.8224329168015</v>
+        <v>6788.5604911696009</v>
       </c>
       <c r="BF3" s="7">
         <f t="shared" ref="BF3:BK3" si="0">BE3*1.03</f>
-        <v>7002.7871059043055</v>
+        <v>6992.2173059046891</v>
       </c>
       <c r="BG3" s="7">
         <f t="shared" si="0"/>
-        <v>7212.8707190814348</v>
+        <v>7201.9838250818302</v>
       </c>
       <c r="BH3" s="7">
         <f t="shared" si="0"/>
-        <v>7429.2568406538776</v>
+        <v>7418.0433398342857</v>
       </c>
       <c r="BI3" s="7">
         <f t="shared" si="0"/>
-        <v>7652.1345458734941</v>
+        <v>7640.5846400293149</v>
       </c>
       <c r="BJ3" s="7">
         <f t="shared" si="0"/>
-        <v>7881.698582249699</v>
+        <v>7869.8021792301943</v>
       </c>
       <c r="BK3" s="7">
         <f t="shared" si="0"/>
-        <v>8118.1495397171902</v>
+        <v>8105.8962446071</v>
       </c>
     </row>
     <row r="4" spans="2:173" x14ac:dyDescent="0.3">
@@ -1434,12 +1433,11 @@
         <v>964</v>
       </c>
       <c r="AO4" s="5">
-        <f t="shared" ref="AO4:AP4" si="1">AO3-AO5</f>
-        <v>964.3549999999999</v>
+        <v>983.2</v>
       </c>
       <c r="AP4" s="5">
-        <f t="shared" si="1"/>
-        <v>987.40529999999967</v>
+        <f t="shared" ref="AP4" si="1">AP3-AP5</f>
+        <v>969.92909999999983</v>
       </c>
       <c r="AR4" s="5">
         <f>SUM(C4:F4)</f>
@@ -1476,47 +1474,47 @@
       </c>
       <c r="BA4" s="5">
         <f>SUM(AM4:AP4)</f>
-        <v>3867.7602999999999</v>
+        <v>3869.1290999999997</v>
       </c>
       <c r="BB4" s="5">
         <f t="shared" ref="BB4:BF4" si="2">BB3-BB5</f>
-        <v>4191.3633300000001</v>
+        <v>4185.03701</v>
       </c>
       <c r="BC4" s="5">
         <f t="shared" si="2"/>
-        <v>4442.8451298000009</v>
+        <v>4436.1392306000007</v>
       </c>
       <c r="BD4" s="5">
         <f t="shared" si="2"/>
-        <v>4620.558934992001</v>
+        <v>4613.5847998240006</v>
       </c>
       <c r="BE4" s="5">
         <f t="shared" si="2"/>
-        <v>4759.1757030417612</v>
+        <v>4751.9923438187207</v>
       </c>
       <c r="BF4" s="5">
         <f t="shared" si="2"/>
-        <v>4901.9509741330139</v>
+        <v>4894.5521141332829</v>
       </c>
       <c r="BG4" s="5">
         <f t="shared" ref="BG4:BK4" si="3">BG3-BG5</f>
-        <v>5049.0095033570051</v>
+        <v>5041.388677557281</v>
       </c>
       <c r="BH4" s="5">
         <f t="shared" si="3"/>
-        <v>5200.4797884577147</v>
+        <v>5192.6303378840003</v>
       </c>
       <c r="BI4" s="5">
         <f t="shared" si="3"/>
-        <v>5356.4941821114462</v>
+        <v>5348.40924802052</v>
       </c>
       <c r="BJ4" s="5">
         <f t="shared" si="3"/>
-        <v>5517.1890075747888</v>
+        <v>5508.8615254611359</v>
       </c>
       <c r="BK4" s="5">
         <f t="shared" si="3"/>
-        <v>5682.7046778020331</v>
+        <v>5674.1273712249695</v>
       </c>
     </row>
     <row r="5" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1660,7 +1658,7 @@
         <v>335.69999999999993</v>
       </c>
       <c r="AK5" s="7">
-        <f t="shared" ref="AK5:AN5" si="13">AK3-AK4</f>
+        <f t="shared" ref="AK5:AO5" si="13">AK3-AK4</f>
         <v>403.5</v>
       </c>
       <c r="AL5" s="7">
@@ -1676,12 +1674,12 @@
         <v>389.40000000000009</v>
       </c>
       <c r="AO5" s="7">
-        <f t="shared" ref="AO5:AP5" si="14">AO3*0.3</f>
-        <v>413.29499999999996</v>
+        <f t="shared" si="13"/>
+        <v>411.20000000000005</v>
       </c>
       <c r="AP5" s="7">
-        <f t="shared" si="14"/>
-        <v>423.17369999999983</v>
+        <f t="shared" ref="AP5" si="14">AP3*0.3</f>
+        <v>415.68389999999994</v>
       </c>
       <c r="AR5" s="7">
         <f t="shared" ref="AR5:AS5" si="15">AR3-AR4</f>
@@ -1721,47 +1719,47 @@
       </c>
       <c r="BA5" s="7">
         <f>BA3-BA4</f>
-        <v>1575.5686999999998</v>
+        <v>1565.9839000000006</v>
       </c>
       <c r="BB5" s="7">
         <f>BB3*0.3</f>
-        <v>1796.2985699999999</v>
+        <v>1793.5872900000002</v>
       </c>
       <c r="BC5" s="7">
         <f t="shared" ref="BC5:BK5" si="18">BC3*0.3</f>
-        <v>1904.0764842000001</v>
+        <v>1901.2025274</v>
       </c>
       <c r="BD5" s="7">
         <f t="shared" si="18"/>
-        <v>1980.2395435680003</v>
+        <v>1977.250628496</v>
       </c>
       <c r="BE5" s="7">
         <f t="shared" si="18"/>
-        <v>2039.6467298750404</v>
+        <v>2036.5681473508803</v>
       </c>
       <c r="BF5" s="7">
         <f t="shared" si="18"/>
-        <v>2100.8361317712915</v>
+        <v>2097.6651917714066</v>
       </c>
       <c r="BG5" s="7">
         <f t="shared" si="18"/>
-        <v>2163.8612157244302</v>
+        <v>2160.5951475245488</v>
       </c>
       <c r="BH5" s="7">
         <f t="shared" si="18"/>
-        <v>2228.7770521961634</v>
+        <v>2225.4130019502854</v>
       </c>
       <c r="BI5" s="7">
         <f t="shared" si="18"/>
-        <v>2295.6403637620483</v>
+        <v>2292.1753920087945</v>
       </c>
       <c r="BJ5" s="7">
         <f t="shared" si="18"/>
-        <v>2364.5095746749098</v>
+        <v>2360.9406537690584</v>
       </c>
       <c r="BK5" s="7">
         <f t="shared" si="18"/>
-        <v>2435.4448619151572</v>
+        <v>2431.7688733821301</v>
       </c>
     </row>
     <row r="6" spans="2:173" x14ac:dyDescent="0.3">
@@ -1896,8 +1894,7 @@
         <v>231.7</v>
       </c>
       <c r="AO6" s="5">
-        <f>AK6*1.14</f>
-        <v>235.75199999999998</v>
+        <v>234.9</v>
       </c>
       <c r="AP6" s="5">
         <f>AL6*1.12</f>
@@ -1938,47 +1935,47 @@
       </c>
       <c r="BA6" s="5">
         <f>SUM(AM6:AP6)</f>
-        <v>929.28</v>
+        <v>928.428</v>
       </c>
       <c r="BB6" s="5">
         <f>BA6*1.08</f>
-        <v>1003.6224000000001</v>
+        <v>1002.7022400000001</v>
       </c>
       <c r="BC6" s="5">
         <f>BB6*1.04</f>
-        <v>1043.7672960000002</v>
+        <v>1042.8103296000002</v>
       </c>
       <c r="BD6" s="5">
         <f>BC6*1.03</f>
-        <v>1075.0803148800003</v>
+        <v>1074.0946394880002</v>
       </c>
       <c r="BE6" s="5">
         <f>BD6*1.02</f>
-        <v>1096.5819211776004</v>
+        <v>1095.5765322777602</v>
       </c>
       <c r="BF6" s="5">
         <f t="shared" ref="BF6:BK6" si="19">BE6*1.02</f>
-        <v>1118.5135596011523</v>
+        <v>1117.4880629233155</v>
       </c>
       <c r="BG6" s="5">
         <f t="shared" si="19"/>
-        <v>1140.8838307931753</v>
+        <v>1139.8378241817818</v>
       </c>
       <c r="BH6" s="5">
         <f t="shared" si="19"/>
-        <v>1163.7015074090389</v>
+        <v>1162.6345806654174</v>
       </c>
       <c r="BI6" s="5">
         <f t="shared" si="19"/>
-        <v>1186.9755375572197</v>
+        <v>1185.8872722787257</v>
       </c>
       <c r="BJ6" s="5">
         <f t="shared" si="19"/>
-        <v>1210.7150483083642</v>
+        <v>1209.6050177243003</v>
       </c>
       <c r="BK6" s="5">
         <f t="shared" si="19"/>
-        <v>1234.9293492745314</v>
+        <v>1233.7971180787863</v>
       </c>
     </row>
     <row r="7" spans="2:173" x14ac:dyDescent="0.3">
@@ -2104,7 +2101,7 @@
         <v>31.3</v>
       </c>
       <c r="AO7" s="5">
-        <v>23</v>
+        <v>31.3</v>
       </c>
       <c r="AP7" s="5">
         <v>25</v>
@@ -2145,7 +2142,7 @@
       </c>
       <c r="BA7" s="5">
         <f>SUM(AM7:AP7)</f>
-        <v>110.7</v>
+        <v>119</v>
       </c>
       <c r="BB7" s="5"/>
       <c r="BC7" s="5"/>
@@ -2316,11 +2313,11 @@
       </c>
       <c r="AO8" s="7">
         <f t="shared" si="29"/>
-        <v>154.54299999999998</v>
+        <v>145.00000000000003</v>
       </c>
       <c r="AP8" s="7">
         <f t="shared" si="29"/>
-        <v>155.24569999999983</v>
+        <v>147.75589999999994</v>
       </c>
       <c r="AR8" s="7">
         <f t="shared" ref="AR8:AS8" si="30">AR5-AR6-AR7</f>
@@ -2360,47 +2357,47 @@
       </c>
       <c r="BA8" s="7">
         <f t="shared" si="32"/>
-        <v>535.58869999999979</v>
+        <v>518.55590000000063</v>
       </c>
       <c r="BB8" s="7">
         <f t="shared" si="32"/>
-        <v>792.67616999999984</v>
+        <v>790.88505000000009</v>
       </c>
       <c r="BC8" s="7">
         <f t="shared" si="32"/>
-        <v>860.30918819999988</v>
+        <v>858.39219779999985</v>
       </c>
       <c r="BD8" s="7">
         <f t="shared" si="32"/>
-        <v>905.15922868799998</v>
+        <v>903.15598900799978</v>
       </c>
       <c r="BE8" s="7">
         <f t="shared" si="32"/>
-        <v>943.06480869743996</v>
+        <v>940.9916150731201</v>
       </c>
       <c r="BF8" s="7">
         <f t="shared" si="32"/>
-        <v>982.32257217013921</v>
+        <v>980.17712884809112</v>
       </c>
       <c r="BG8" s="7">
         <f t="shared" ref="BG8:BK8" si="34">BG5-BG6-BG7</f>
-        <v>1022.9773849312548</v>
+        <v>1020.757323342767</v>
       </c>
       <c r="BH8" s="7">
         <f t="shared" si="34"/>
-        <v>1065.0755447871245</v>
+        <v>1062.778421284868</v>
       </c>
       <c r="BI8" s="7">
         <f t="shared" si="34"/>
-        <v>1108.6648262048286</v>
+        <v>1106.2881197300687</v>
       </c>
       <c r="BJ8" s="7">
         <f t="shared" si="34"/>
-        <v>1153.7945263665456</v>
+        <v>1151.3356360447581</v>
       </c>
       <c r="BK8" s="7">
         <f t="shared" si="34"/>
-        <v>1200.5155126406257</v>
+        <v>1197.9717553033438</v>
       </c>
     </row>
     <row r="9" spans="2:173" x14ac:dyDescent="0.3">
@@ -2525,11 +2522,10 @@
         <v>-3.5</v>
       </c>
       <c r="AO9" s="5">
-        <f t="shared" ref="AO9:AP9" si="35">AK9*1.03</f>
-        <v>-13.699000000000002</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="AP9" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="AP9" si="35">AL9*1.03</f>
         <v>-6.7979999999999947</v>
       </c>
       <c r="AR9" s="5">
@@ -2567,47 +2563,47 @@
       </c>
       <c r="BA9" s="5">
         <f>SUM(AM9:AP9)</f>
-        <v>-29.796999999999997</v>
+        <v>-18.397999999999996</v>
       </c>
       <c r="BB9" s="5">
         <f t="shared" ref="BB9:BG9" si="36">BA9*1.02</f>
-        <v>-30.392939999999996</v>
+        <v>-18.765959999999996</v>
       </c>
       <c r="BC9" s="5">
         <f t="shared" si="36"/>
-        <v>-31.000798799999995</v>
+        <v>-19.141279199999996</v>
       </c>
       <c r="BD9" s="5">
         <f t="shared" si="36"/>
-        <v>-31.620814775999996</v>
+        <v>-19.524104783999995</v>
       </c>
       <c r="BE9" s="5">
         <f t="shared" si="36"/>
-        <v>-32.253231071519998</v>
+        <v>-19.914586879679995</v>
       </c>
       <c r="BF9" s="5">
         <f t="shared" si="36"/>
-        <v>-32.898295692950398</v>
+        <v>-20.312878617273594</v>
       </c>
       <c r="BG9" s="5">
         <f t="shared" si="36"/>
-        <v>-33.556261606809407</v>
+        <v>-20.719136189619064</v>
       </c>
       <c r="BH9" s="5">
         <f t="shared" ref="BH9" si="37">BG9*1.02</f>
-        <v>-34.227386838945598</v>
+        <v>-21.133518913411447</v>
       </c>
       <c r="BI9" s="5">
         <f t="shared" ref="BI9" si="38">BH9*1.02</f>
-        <v>-34.911934575724509</v>
+        <v>-21.556189291679676</v>
       </c>
       <c r="BJ9" s="5">
         <f t="shared" ref="BJ9" si="39">BI9*1.02</f>
-        <v>-35.610173267238999</v>
+        <v>-21.987313077513271</v>
       </c>
       <c r="BK9" s="5">
         <f t="shared" ref="BK9" si="40">BJ9*1.02</f>
-        <v>-36.322376732583777</v>
+        <v>-22.427059339063536</v>
       </c>
     </row>
     <row r="10" spans="2:173" x14ac:dyDescent="0.3">
@@ -2732,7 +2728,7 @@
         <v>6.2</v>
       </c>
       <c r="AO10" s="5">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AP10" s="5">
         <v>2</v>
@@ -2772,47 +2768,47 @@
       </c>
       <c r="BA10" s="5">
         <f>SUM(AM10:AP10)</f>
-        <v>20.9</v>
+        <v>22.5</v>
       </c>
       <c r="BB10" s="5">
         <f t="shared" ref="BB10:BG10" si="41">BA10*0.95</f>
-        <v>19.854999999999997</v>
+        <v>21.375</v>
       </c>
       <c r="BC10" s="5">
         <f t="shared" si="41"/>
-        <v>18.862249999999996</v>
+        <v>20.306249999999999</v>
       </c>
       <c r="BD10" s="5">
         <f t="shared" si="41"/>
-        <v>17.919137499999994</v>
+        <v>19.290937499999998</v>
       </c>
       <c r="BE10" s="5">
         <f t="shared" si="41"/>
-        <v>17.023180624999995</v>
+        <v>18.326390624999998</v>
       </c>
       <c r="BF10" s="5">
         <f t="shared" si="41"/>
-        <v>16.172021593749996</v>
+        <v>17.410071093749998</v>
       </c>
       <c r="BG10" s="5">
         <f t="shared" si="41"/>
-        <v>15.363420514062495</v>
+        <v>16.539567539062496</v>
       </c>
       <c r="BH10" s="5">
         <f t="shared" ref="BH10" si="42">BG10*0.95</f>
-        <v>14.59524948835937</v>
+        <v>15.712589162109371</v>
       </c>
       <c r="BI10" s="5">
         <f t="shared" ref="BI10" si="43">BH10*0.95</f>
-        <v>13.865487013941401</v>
+        <v>14.926959704003902</v>
       </c>
       <c r="BJ10" s="5">
         <f t="shared" ref="BJ10" si="44">BI10*0.95</f>
-        <v>13.172212663244331</v>
+        <v>14.180611718803707</v>
       </c>
       <c r="BK10" s="5">
         <f t="shared" ref="BK10" si="45">BJ10*0.95</f>
-        <v>12.513602030082113</v>
+        <v>13.471581132863522</v>
       </c>
     </row>
     <row r="11" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2973,11 +2969,11 @@
       </c>
       <c r="AO11" s="7">
         <f t="shared" si="55"/>
-        <v>166.24199999999999</v>
+        <v>143.70000000000005</v>
       </c>
       <c r="AP11" s="7">
         <f t="shared" si="55"/>
-        <v>160.04369999999983</v>
+        <v>152.55389999999994</v>
       </c>
       <c r="AR11" s="7">
         <f t="shared" ref="AR11:AS11" si="56">AR8-AR9-AR10</f>
@@ -3017,47 +3013,47 @@
       </c>
       <c r="BA11" s="7">
         <f t="shared" si="60"/>
-        <v>544.48569999999984</v>
+        <v>514.45390000000066</v>
       </c>
       <c r="BB11" s="7">
         <f t="shared" si="60"/>
-        <v>803.21410999999978</v>
+        <v>788.27601000000004</v>
       </c>
       <c r="BC11" s="7">
         <f t="shared" si="60"/>
-        <v>872.44773699999985</v>
+        <v>857.22722699999986</v>
       </c>
       <c r="BD11" s="7">
         <f t="shared" si="60"/>
-        <v>918.86090596399993</v>
+        <v>903.38915629199971</v>
       </c>
       <c r="BE11" s="7">
         <f t="shared" si="60"/>
-        <v>958.29485914395991</v>
+        <v>942.57981132780003</v>
       </c>
       <c r="BF11" s="7">
         <f t="shared" si="60"/>
-        <v>999.04884626933961</v>
+        <v>983.07993637161462</v>
       </c>
       <c r="BG11" s="7">
         <f t="shared" ref="BG11:BK11" si="61">BG8-BG9-BG10</f>
-        <v>1041.1702260240017</v>
+        <v>1024.9368919933236</v>
       </c>
       <c r="BH11" s="7">
         <f t="shared" si="61"/>
-        <v>1084.7076821377109</v>
+        <v>1068.1993510361701</v>
       </c>
       <c r="BI11" s="7">
         <f t="shared" si="61"/>
-        <v>1129.7112737666116</v>
+        <v>1112.9173493177445</v>
       </c>
       <c r="BJ11" s="7">
         <f t="shared" si="61"/>
-        <v>1176.2324869705401</v>
+        <v>1159.1423374034678</v>
       </c>
       <c r="BK11" s="7">
         <f t="shared" si="61"/>
-        <v>1224.3242873431273</v>
+        <v>1206.9272335095438</v>
       </c>
     </row>
     <row r="12" spans="2:173" x14ac:dyDescent="0.3">
@@ -3183,12 +3179,11 @@
         <v>35.700000000000003</v>
       </c>
       <c r="AO12" s="5">
-        <f t="shared" ref="AO12:AP12" si="62">AO11*0.22</f>
-        <v>36.573239999999998</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AP12" s="5">
-        <f t="shared" si="62"/>
-        <v>35.209613999999966</v>
+        <f t="shared" ref="AP12" si="62">AP11*0.22</f>
+        <v>33.561857999999987</v>
       </c>
       <c r="AR12" s="5">
         <f>SUM(C12:F12)</f>
@@ -3225,47 +3220,47 @@
       </c>
       <c r="BA12" s="5">
         <f>SUM(AM12:AP12)</f>
-        <v>128.38285399999995</v>
+        <v>126.96185799999999</v>
       </c>
       <c r="BB12" s="5">
         <f>BB11*0.22</f>
-        <v>176.70710419999995</v>
+        <v>173.4207222</v>
       </c>
       <c r="BC12" s="5">
         <f t="shared" ref="BC12:BK12" si="63">BC11*0.22</f>
-        <v>191.93850213999997</v>
+        <v>188.58998993999998</v>
       </c>
       <c r="BD12" s="5">
         <f t="shared" si="63"/>
-        <v>202.14939931207999</v>
+        <v>198.74561438423993</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="63"/>
-        <v>210.82486901167118</v>
+        <v>207.36755849211602</v>
       </c>
       <c r="BF12" s="5">
         <f t="shared" si="63"/>
-        <v>219.79074617925471</v>
+        <v>216.27758600175522</v>
       </c>
       <c r="BG12" s="5">
         <f t="shared" si="63"/>
-        <v>229.05744972528038</v>
+        <v>225.4861162385312</v>
       </c>
       <c r="BH12" s="5">
         <f t="shared" si="63"/>
-        <v>238.63569007029639</v>
+        <v>235.00385722795744</v>
       </c>
       <c r="BI12" s="5">
         <f t="shared" si="63"/>
-        <v>248.53648022865457</v>
+        <v>244.84181684990381</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="63"/>
-        <v>258.77114713351881</v>
+        <v>255.0113142287629</v>
       </c>
       <c r="BK12" s="5">
         <f t="shared" si="63"/>
-        <v>269.35134321548799</v>
+        <v>265.52399137209966</v>
       </c>
     </row>
     <row r="13" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3426,11 +3421,11 @@
       </c>
       <c r="AO13" s="7">
         <f t="shared" si="76"/>
-        <v>129.66875999999999</v>
+        <v>106.90000000000005</v>
       </c>
       <c r="AP13" s="7">
         <f t="shared" si="76"/>
-        <v>124.83408599999987</v>
+        <v>118.99204199999996</v>
       </c>
       <c r="AR13" s="7">
         <f t="shared" ref="AR13:AS13" si="77">AR11-AR12</f>
@@ -3470,487 +3465,487 @@
       </c>
       <c r="BA13" s="7">
         <f t="shared" si="81"/>
-        <v>416.10284599999989</v>
+        <v>387.49204200000065</v>
       </c>
       <c r="BB13" s="7">
         <f t="shared" si="81"/>
-        <v>626.50700579999989</v>
+        <v>614.85528780000004</v>
       </c>
       <c r="BC13" s="7">
         <f t="shared" si="81"/>
-        <v>680.50923485999988</v>
+        <v>668.63723705999985</v>
       </c>
       <c r="BD13" s="7">
         <f t="shared" si="81"/>
-        <v>716.71150665191999</v>
+        <v>704.64354190775975</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="81"/>
-        <v>747.46999013228879</v>
+        <v>735.21225283568401</v>
       </c>
       <c r="BF13" s="7">
         <f t="shared" si="81"/>
-        <v>779.25810009008489</v>
+        <v>766.80235036985937</v>
       </c>
       <c r="BG13" s="7">
         <f t="shared" ref="BG13:BK13" si="82">BG11-BG12</f>
-        <v>812.11277629872143</v>
+        <v>799.4507757547924</v>
       </c>
       <c r="BH13" s="7">
         <f t="shared" si="82"/>
-        <v>846.0719920674145</v>
+        <v>833.19549380821263</v>
       </c>
       <c r="BI13" s="7">
         <f t="shared" si="82"/>
-        <v>881.17479353795704</v>
+        <v>868.07553246784073</v>
       </c>
       <c r="BJ13" s="7">
         <f t="shared" si="82"/>
-        <v>917.46133983702134</v>
+        <v>904.13102317470486</v>
       </c>
       <c r="BK13" s="7">
         <f t="shared" si="82"/>
-        <v>954.97294412763927</v>
+        <v>941.40324213744418</v>
       </c>
       <c r="BL13" s="1">
         <f t="shared" ref="BL13:CQ13" si="83">BK13*(1+$BN$19)</f>
-        <v>945.42321468636283</v>
+        <v>931.98920971606969</v>
       </c>
       <c r="BM13" s="1">
         <f t="shared" si="83"/>
-        <v>935.96898253949917</v>
+        <v>922.66931761890896</v>
       </c>
       <c r="BN13" s="1">
         <f t="shared" si="83"/>
-        <v>926.60929271410419</v>
+        <v>913.44262444271988</v>
       </c>
       <c r="BO13" s="1">
         <f t="shared" si="83"/>
-        <v>917.34319978696317</v>
+        <v>904.30819819829264</v>
       </c>
       <c r="BP13" s="1">
         <f t="shared" si="83"/>
-        <v>908.1697677890935</v>
+        <v>895.26511621630971</v>
       </c>
       <c r="BQ13" s="1">
         <f t="shared" si="83"/>
-        <v>899.08807011120257</v>
+        <v>886.31246505414663</v>
       </c>
       <c r="BR13" s="1">
         <f t="shared" si="83"/>
-        <v>890.09718941009055</v>
+        <v>877.44934040360511</v>
       </c>
       <c r="BS13" s="1">
         <f t="shared" si="83"/>
-        <v>881.19621751598959</v>
+        <v>868.67484699956901</v>
       </c>
       <c r="BT13" s="1">
         <f t="shared" si="83"/>
-        <v>872.38425534082967</v>
+        <v>859.98809852957334</v>
       </c>
       <c r="BU13" s="1">
         <f t="shared" si="83"/>
-        <v>863.66041278742136</v>
+        <v>851.38821754427761</v>
       </c>
       <c r="BV13" s="1">
         <f t="shared" si="83"/>
-        <v>855.02380865954717</v>
+        <v>842.87433536883486</v>
       </c>
       <c r="BW13" s="1">
         <f t="shared" si="83"/>
-        <v>846.47357057295164</v>
+        <v>834.44559201514653</v>
       </c>
       <c r="BX13" s="1">
         <f t="shared" si="83"/>
-        <v>838.00883486722216</v>
+        <v>826.10113609499501</v>
       </c>
       <c r="BY13" s="1">
         <f t="shared" si="83"/>
-        <v>829.62874651854997</v>
+        <v>817.84012473404505</v>
       </c>
       <c r="BZ13" s="1">
         <f t="shared" si="83"/>
-        <v>821.33245905336446</v>
+        <v>809.66172348670455</v>
       </c>
       <c r="CA13" s="1">
         <f t="shared" si="83"/>
-        <v>813.11913446283086</v>
+        <v>801.56510625183751</v>
       </c>
       <c r="CB13" s="1">
         <f t="shared" si="83"/>
-        <v>804.98794311820257</v>
+        <v>793.54945518931913</v>
       </c>
       <c r="CC13" s="1">
         <f t="shared" si="83"/>
-        <v>796.93806368702053</v>
+        <v>785.61396063742598</v>
       </c>
       <c r="CD13" s="1">
         <f t="shared" si="83"/>
-        <v>788.96868305015028</v>
+        <v>777.75782103105166</v>
       </c>
       <c r="CE13" s="1">
         <f t="shared" si="83"/>
-        <v>781.07899621964873</v>
+        <v>769.98024282074118</v>
       </c>
       <c r="CF13" s="1">
         <f t="shared" si="83"/>
-        <v>773.26820625745222</v>
+        <v>762.28044039253382</v>
       </c>
       <c r="CG13" s="1">
         <f t="shared" si="83"/>
-        <v>765.53552419487767</v>
+        <v>754.65763598860849</v>
       </c>
       <c r="CH13" s="1">
         <f t="shared" si="83"/>
-        <v>757.8801689529289</v>
+        <v>747.11105962872239</v>
       </c>
       <c r="CI13" s="1">
         <f t="shared" si="83"/>
-        <v>750.30136726339958</v>
+        <v>739.6399490324352</v>
       </c>
       <c r="CJ13" s="1">
         <f t="shared" si="83"/>
-        <v>742.7983535907656</v>
+        <v>732.24354954211083</v>
       </c>
       <c r="CK13" s="1">
         <f t="shared" si="83"/>
-        <v>735.37037005485797</v>
+        <v>724.92111404668969</v>
       </c>
       <c r="CL13" s="1">
         <f t="shared" si="83"/>
-        <v>728.01666635430934</v>
+        <v>717.67190290622284</v>
       </c>
       <c r="CM13" s="1">
         <f t="shared" si="83"/>
-        <v>720.73649969076621</v>
+        <v>710.49518387716057</v>
       </c>
       <c r="CN13" s="1">
         <f t="shared" si="83"/>
-        <v>713.52913469385851</v>
+        <v>703.39023203838894</v>
       </c>
       <c r="CO13" s="1">
         <f t="shared" si="83"/>
-        <v>706.39384334691988</v>
+        <v>696.3563297180051</v>
       </c>
       <c r="CP13" s="1">
         <f t="shared" si="83"/>
-        <v>699.32990491345072</v>
+        <v>689.39276642082507</v>
       </c>
       <c r="CQ13" s="1">
         <f t="shared" si="83"/>
-        <v>692.3366058643162</v>
+        <v>682.49883875661681</v>
       </c>
       <c r="CR13" s="1">
         <f t="shared" ref="CR13:DW13" si="84">CQ13*(1+$BN$19)</f>
-        <v>685.41323980567302</v>
+        <v>675.67385036905068</v>
       </c>
       <c r="CS13" s="1">
         <f t="shared" si="84"/>
-        <v>678.55910740761624</v>
+        <v>668.9171118653602</v>
       </c>
       <c r="CT13" s="1">
         <f t="shared" si="84"/>
-        <v>671.7735163335401</v>
+        <v>662.22794074670662</v>
       </c>
       <c r="CU13" s="1">
         <f t="shared" si="84"/>
-        <v>665.05578117020468</v>
+        <v>655.60566133923953</v>
       </c>
       <c r="CV13" s="1">
         <f t="shared" si="84"/>
-        <v>658.40522335850267</v>
+        <v>649.04960472584708</v>
       </c>
       <c r="CW13" s="1">
         <f t="shared" si="84"/>
-        <v>651.82117112491767</v>
+        <v>642.55910867858859</v>
       </c>
       <c r="CX13" s="1">
         <f t="shared" si="84"/>
-        <v>645.30295941366853</v>
+        <v>636.13351759180273</v>
       </c>
       <c r="CY13" s="1">
         <f t="shared" si="84"/>
-        <v>638.84992981953189</v>
+        <v>629.77218241588469</v>
       </c>
       <c r="CZ13" s="1">
         <f t="shared" si="84"/>
-        <v>632.46143052133652</v>
+        <v>623.4744605917258</v>
       </c>
       <c r="DA13" s="1">
         <f t="shared" si="84"/>
-        <v>626.13681621612318</v>
+        <v>617.23971598580852</v>
       </c>
       <c r="DB13" s="1">
         <f t="shared" si="84"/>
-        <v>619.87544805396192</v>
+        <v>611.06731882595045</v>
       </c>
       <c r="DC13" s="1">
         <f t="shared" si="84"/>
-        <v>613.67669357342231</v>
+        <v>604.95664563769094</v>
       </c>
       <c r="DD13" s="1">
         <f t="shared" si="84"/>
-        <v>607.53992663768804</v>
+        <v>598.90707918131397</v>
       </c>
       <c r="DE13" s="1">
         <f t="shared" si="84"/>
-        <v>601.46452737131119</v>
+        <v>592.91800838950087</v>
       </c>
       <c r="DF13" s="1">
         <f t="shared" si="84"/>
-        <v>595.44988209759811</v>
+        <v>586.98882830560581</v>
       </c>
       <c r="DG13" s="1">
         <f t="shared" si="84"/>
-        <v>589.49538327662208</v>
+        <v>581.11894002254974</v>
       </c>
       <c r="DH13" s="1">
         <f t="shared" si="84"/>
-        <v>583.60042944385589</v>
+        <v>575.30775062232419</v>
       </c>
       <c r="DI13" s="1">
         <f t="shared" si="84"/>
-        <v>577.76442514941732</v>
+        <v>569.55467311610096</v>
       </c>
       <c r="DJ13" s="1">
         <f t="shared" si="84"/>
-        <v>571.98678089792315</v>
+        <v>563.85912638493994</v>
       </c>
       <c r="DK13" s="1">
         <f t="shared" si="84"/>
-        <v>566.26691308894397</v>
+        <v>558.22053512109051</v>
       </c>
       <c r="DL13" s="1">
         <f t="shared" si="84"/>
-        <v>560.60424395805455</v>
+        <v>552.63832976987965</v>
       </c>
       <c r="DM13" s="1">
         <f t="shared" si="84"/>
-        <v>554.99820151847405</v>
+        <v>547.11194647218088</v>
       </c>
       <c r="DN13" s="1">
         <f t="shared" si="84"/>
-        <v>549.44821950328935</v>
+        <v>541.64082700745905</v>
       </c>
       <c r="DO13" s="1">
         <f t="shared" si="84"/>
-        <v>543.95373730825645</v>
+        <v>536.22441873738444</v>
       </c>
       <c r="DP13" s="1">
         <f t="shared" si="84"/>
-        <v>538.51419993517391</v>
+        <v>530.86217455001054</v>
       </c>
       <c r="DQ13" s="1">
         <f t="shared" si="84"/>
-        <v>533.12905793582217</v>
+        <v>525.55355280451045</v>
       </c>
       <c r="DR13" s="1">
         <f t="shared" si="84"/>
-        <v>527.79776735646396</v>
+        <v>520.29801727646532</v>
       </c>
       <c r="DS13" s="1">
         <f t="shared" si="84"/>
-        <v>522.51978968289927</v>
+        <v>515.09503710370063</v>
       </c>
       <c r="DT13" s="1">
         <f t="shared" si="84"/>
-        <v>517.29459178607033</v>
+        <v>509.94408673266361</v>
       </c>
       <c r="DU13" s="1">
         <f t="shared" si="84"/>
-        <v>512.12164586820961</v>
+        <v>504.84464586533699</v>
       </c>
       <c r="DV13" s="1">
         <f t="shared" si="84"/>
-        <v>507.0004294095275</v>
+        <v>499.79619940668363</v>
       </c>
       <c r="DW13" s="1">
         <f t="shared" si="84"/>
-        <v>501.93042511543223</v>
+        <v>494.7982374126168</v>
       </c>
       <c r="DX13" s="1">
         <f t="shared" ref="DX13:FC13" si="85">DW13*(1+$BN$19)</f>
-        <v>496.9111208642779</v>
+        <v>489.85025503849062</v>
       </c>
       <c r="DY13" s="1">
         <f t="shared" si="85"/>
-        <v>491.9420096556351</v>
+        <v>484.95175248810568</v>
       </c>
       <c r="DZ13" s="1">
         <f t="shared" si="85"/>
-        <v>487.02258955907877</v>
+        <v>480.10223496322465</v>
       </c>
       <c r="EA13" s="1">
         <f t="shared" si="85"/>
-        <v>482.15236366348796</v>
+        <v>475.30121261359238</v>
       </c>
       <c r="EB13" s="1">
         <f t="shared" si="85"/>
-        <v>477.33084002685308</v>
+        <v>470.54820048745648</v>
       </c>
       <c r="EC13" s="1">
         <f t="shared" si="85"/>
-        <v>472.55753162658453</v>
+        <v>465.84271848258192</v>
       </c>
       <c r="ED13" s="1">
         <f t="shared" si="85"/>
-        <v>467.83195631031867</v>
+        <v>461.18429129775609</v>
       </c>
       <c r="EE13" s="1">
         <f t="shared" si="85"/>
-        <v>463.1536367472155</v>
+        <v>456.57244838477851</v>
       </c>
       <c r="EF13" s="1">
         <f t="shared" si="85"/>
-        <v>458.52210037974334</v>
+        <v>452.00672390093069</v>
       </c>
       <c r="EG13" s="1">
         <f t="shared" si="85"/>
-        <v>453.93687937594592</v>
+        <v>447.48665666192136</v>
       </c>
       <c r="EH13" s="1">
         <f t="shared" si="85"/>
-        <v>449.39751058218644</v>
+        <v>443.01179009530216</v>
       </c>
       <c r="EI13" s="1">
         <f t="shared" si="85"/>
-        <v>444.9035354763646</v>
+        <v>438.58167219434915</v>
       </c>
       <c r="EJ13" s="1">
         <f t="shared" si="85"/>
-        <v>440.45450012160097</v>
+        <v>434.19585547240564</v>
       </c>
       <c r="EK13" s="1">
         <f t="shared" si="85"/>
-        <v>436.04995512038494</v>
+        <v>429.8538969176816</v>
       </c>
       <c r="EL13" s="1">
         <f t="shared" si="85"/>
-        <v>431.68945556918106</v>
+        <v>425.55535794850476</v>
       </c>
       <c r="EM13" s="1">
         <f t="shared" si="85"/>
-        <v>427.37256101348925</v>
+        <v>421.29980436901974</v>
       </c>
       <c r="EN13" s="1">
         <f t="shared" si="85"/>
-        <v>423.09883540335437</v>
+        <v>417.08680632532952</v>
       </c>
       <c r="EO13" s="1">
         <f t="shared" si="85"/>
-        <v>418.8678470493208</v>
+        <v>412.91593826207622</v>
       </c>
       <c r="EP13" s="1">
         <f t="shared" si="85"/>
-        <v>414.67916857882761</v>
+        <v>408.78677887945548</v>
       </c>
       <c r="EQ13" s="1">
         <f t="shared" si="85"/>
-        <v>410.53237689303933</v>
+        <v>404.69891109066094</v>
       </c>
       <c r="ER13" s="1">
         <f t="shared" si="85"/>
-        <v>406.42705312410891</v>
+        <v>400.65192197975432</v>
       </c>
       <c r="ES13" s="1">
         <f t="shared" si="85"/>
-        <v>402.3627825928678</v>
+        <v>396.64540275995677</v>
       </c>
       <c r="ET13" s="1">
         <f t="shared" si="85"/>
-        <v>398.33915476693915</v>
+        <v>392.67894873235718</v>
       </c>
       <c r="EU13" s="1">
         <f t="shared" si="85"/>
-        <v>394.35576321926976</v>
+        <v>388.75215924503362</v>
       </c>
       <c r="EV13" s="1">
         <f t="shared" si="85"/>
-        <v>390.41220558707704</v>
+        <v>384.86463765258327</v>
       </c>
       <c r="EW13" s="1">
         <f t="shared" si="85"/>
-        <v>386.50808353120624</v>
+        <v>381.01599127605743</v>
       </c>
       <c r="EX13" s="1">
         <f t="shared" si="85"/>
-        <v>382.64300269589415</v>
+        <v>377.20583136329685</v>
       </c>
       <c r="EY13" s="1">
         <f t="shared" si="85"/>
-        <v>378.81657266893524</v>
+        <v>373.4337730496639</v>
       </c>
       <c r="EZ13" s="1">
         <f t="shared" si="85"/>
-        <v>375.02840694224591</v>
+        <v>369.69943531916726</v>
       </c>
       <c r="FA13" s="1">
         <f t="shared" si="85"/>
-        <v>371.27812287282347</v>
+        <v>366.00244096597561</v>
       </c>
       <c r="FB13" s="1">
         <f t="shared" si="85"/>
-        <v>367.56534164409521</v>
+        <v>362.34241655631587</v>
       </c>
       <c r="FC13" s="1">
         <f t="shared" si="85"/>
-        <v>363.88968822765423</v>
+        <v>358.7189923907527</v>
       </c>
       <c r="FD13" s="1">
         <f t="shared" ref="FD13:FQ13" si="86">FC13*(1+$BN$19)</f>
-        <v>360.25079134537771</v>
+        <v>355.13180246684516</v>
       </c>
       <c r="FE13" s="1">
         <f t="shared" si="86"/>
-        <v>356.64828343192391</v>
+        <v>351.58048444217673</v>
       </c>
       <c r="FF13" s="1">
         <f t="shared" si="86"/>
-        <v>353.08180059760468</v>
+        <v>348.06467959775495</v>
       </c>
       <c r="FG13" s="1">
         <f t="shared" si="86"/>
-        <v>349.55098259162861</v>
+        <v>344.58403280177737</v>
       </c>
       <c r="FH13" s="1">
         <f t="shared" si="86"/>
-        <v>346.0554727657123</v>
+        <v>341.1381924737596</v>
       </c>
       <c r="FI13" s="1">
         <f t="shared" si="86"/>
-        <v>342.59491803805514</v>
+        <v>337.72681054902199</v>
       </c>
       <c r="FJ13" s="1">
         <f t="shared" si="86"/>
-        <v>339.1689688576746</v>
+        <v>334.34954244353179</v>
       </c>
       <c r="FK13" s="1">
         <f t="shared" si="86"/>
-        <v>335.77727916909782</v>
+        <v>331.00604701909646</v>
       </c>
       <c r="FL13" s="1">
         <f t="shared" si="86"/>
-        <v>332.41950637740683</v>
+        <v>327.69598654890547</v>
       </c>
       <c r="FM13" s="1">
         <f t="shared" si="86"/>
-        <v>329.09531131363275</v>
+        <v>324.4190266834164</v>
       </c>
       <c r="FN13" s="1">
         <f t="shared" si="86"/>
-        <v>325.80435820049644</v>
+        <v>321.17483641658225</v>
       </c>
       <c r="FO13" s="1">
         <f t="shared" si="86"/>
-        <v>322.54631461849146</v>
+        <v>317.96308805241642</v>
       </c>
       <c r="FP13" s="1">
         <f t="shared" si="86"/>
-        <v>319.32085147230657</v>
+        <v>314.78345717189228</v>
       </c>
       <c r="FQ13" s="1">
         <f t="shared" si="86"/>
-        <v>316.12764295758348</v>
+        <v>311.63562260017335</v>
       </c>
     </row>
     <row r="14" spans="2:173" x14ac:dyDescent="0.3">
@@ -4074,12 +4069,12 @@
         <v>55.7</v>
       </c>
       <c r="AO14" s="5">
-        <f>55.7</f>
-        <v>55.7</v>
+        <f>55.6</f>
+        <v>55.6</v>
       </c>
       <c r="AP14" s="5">
-        <f>55.7</f>
-        <v>55.7</v>
+        <f>55.6</f>
+        <v>55.6</v>
       </c>
       <c r="AR14" s="5">
         <v>55.85</v>
@@ -4109,48 +4104,48 @@
         <v>56.9</v>
       </c>
       <c r="BA14" s="5">
-        <f t="shared" ref="BA14:BK14" si="87">55.7</f>
-        <v>55.7</v>
+        <f t="shared" ref="BA14:BK14" si="87">55.6</f>
+        <v>55.6</v>
       </c>
       <c r="BB14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BC14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BD14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BF14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BG14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BH14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BI14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="BK14" s="5">
         <f t="shared" si="87"/>
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="15" spans="2:173" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4311,11 +4306,11 @@
       </c>
       <c r="AO15" s="8">
         <f t="shared" si="100"/>
-        <v>2.3279849192100537</v>
+        <v>1.922661870503598</v>
       </c>
       <c r="AP15" s="8">
         <f t="shared" si="100"/>
-        <v>2.2411864631956888</v>
+        <v>2.1401446402877689</v>
       </c>
       <c r="AR15" s="8">
         <f t="shared" ref="AR15:AS15" si="101">AR13/AR14</f>
@@ -4355,47 +4350,47 @@
       </c>
       <c r="BA15" s="8">
         <f t="shared" si="105"/>
-        <v>7.4704281149012539</v>
+        <v>6.9692813309352637</v>
       </c>
       <c r="BB15" s="8">
         <f t="shared" si="105"/>
-        <v>11.247881612208255</v>
+        <v>11.058548341726619</v>
       </c>
       <c r="BC15" s="8">
         <f t="shared" si="105"/>
-        <v>12.217400984919207</v>
+        <v>12.025849587410068</v>
       </c>
       <c r="BD15" s="8">
         <f t="shared" si="105"/>
-        <v>12.8673520045228</v>
+        <v>12.673444998341003</v>
       </c>
       <c r="BE15" s="8">
         <f t="shared" si="105"/>
-        <v>13.419568943129061</v>
+        <v>13.223241957476331</v>
       </c>
       <c r="BF15" s="8">
         <f t="shared" si="105"/>
-        <v>13.990271096769925</v>
+        <v>13.791409179314018</v>
       </c>
       <c r="BG15" s="8">
         <f t="shared" ref="BG15:BK15" si="106">BG13/BG14</f>
-        <v>14.580121657068606</v>
+        <v>14.378611074726482</v>
       </c>
       <c r="BH15" s="8">
         <f t="shared" si="106"/>
-        <v>15.189802371048733</v>
+        <v>14.985530464176486</v>
       </c>
       <c r="BI15" s="8">
         <f t="shared" si="106"/>
-        <v>15.820014246641957</v>
+        <v>15.612869288989941</v>
       </c>
       <c r="BJ15" s="8">
         <f t="shared" si="106"/>
-        <v>16.471478273555139</v>
+        <v>16.261349337674549</v>
       </c>
       <c r="BK15" s="8">
         <f t="shared" si="106"/>
-        <v>17.144936160280775</v>
+        <v>16.931712988083529</v>
       </c>
     </row>
     <row r="17" spans="2:66" x14ac:dyDescent="0.3">
@@ -4540,11 +4535,11 @@
       </c>
       <c r="AO17" s="9">
         <f t="shared" ref="AO17" si="126">AO3/AK3-1</f>
-        <v>0.17999999999999994</v>
+        <v>0.19434689507494651</v>
       </c>
       <c r="AP17" s="9">
         <f t="shared" ref="AP17" si="127">AP3/AL3-1</f>
-        <v>0.12999999999999989</v>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AS17" s="9">
         <f>AS3/AR3-1</f>
@@ -4580,7 +4575,7 @@
       </c>
       <c r="BA17" s="9">
         <f t="shared" si="128"/>
-        <v>0.15132067091097534</v>
+        <v>0.14958290149960884</v>
       </c>
       <c r="BB17" s="9">
         <f t="shared" si="128"/>
@@ -4781,7 +4776,7 @@
       </c>
       <c r="AO18" s="9">
         <f t="shared" si="137"/>
-        <v>0.3</v>
+        <v>0.29489386115892141</v>
       </c>
       <c r="AP18" s="9">
         <f t="shared" si="137"/>
@@ -4825,7 +4820,7 @@
       </c>
       <c r="BA18" s="9">
         <f t="shared" si="138"/>
-        <v>0.28944947108653546</v>
+        <v>0.28812352199485097</v>
       </c>
       <c r="BB18" s="9">
         <f t="shared" si="138"/>
@@ -5026,11 +5021,11 @@
       </c>
       <c r="AO19" s="9">
         <f t="shared" si="144"/>
-        <v>0.11217871012230972</v>
+        <v>0.10398737808376364</v>
       </c>
       <c r="AP19" s="9">
         <f t="shared" si="144"/>
-        <v>0.11005813924636612</v>
+        <v>0.10663576337693134</v>
       </c>
       <c r="AR19" s="9">
         <f t="shared" ref="AR19:BF19" si="145">AR8/AR3</f>
@@ -5070,47 +5065,47 @@
       </c>
       <c r="BA19" s="9">
         <f t="shared" si="145"/>
-        <v>9.8393593332315538E-2</v>
+        <v>9.540848552734793E-2</v>
       </c>
       <c r="BB19" s="9">
         <f t="shared" si="145"/>
-        <v>0.13238492473998906</v>
+        <v>0.13228545737520253</v>
       </c>
       <c r="BC19" s="9">
         <f t="shared" si="145"/>
-        <v>0.13554747332980058</v>
+        <v>0.13544988270774583</v>
       </c>
       <c r="BD19" s="9">
         <f t="shared" si="145"/>
-        <v>0.13712874762470634</v>
+        <v>0.1370320953740175</v>
       </c>
       <c r="BE19" s="9">
         <f t="shared" si="145"/>
-        <v>0.1387100219196121</v>
+        <v>0.13861430804028921</v>
       </c>
       <c r="BF19" s="9">
         <f t="shared" si="145"/>
-        <v>0.14027594403689742</v>
+        <v>0.14018115941853881</v>
       </c>
       <c r="BG19" s="9">
         <f t="shared" ref="BG19:BK19" si="146">BG8/BG3</f>
-        <v>0.14182666302683045</v>
+        <v>0.141732798647485</v>
       </c>
       <c r="BH19" s="9">
         <f t="shared" si="146"/>
-        <v>0.1433623264925894</v>
+        <v>0.14326937341789781</v>
       </c>
       <c r="BI19" s="9">
         <f t="shared" si="146"/>
-        <v>0.14488308060431185</v>
+        <v>0.14479102998665613</v>
       </c>
       <c r="BJ19" s="9">
         <f t="shared" si="146"/>
-        <v>0.14638907011300784</v>
+        <v>0.14629791319066918</v>
       </c>
       <c r="BK19" s="9">
         <f t="shared" si="146"/>
-        <v>0.14788043836433787</v>
+        <v>0.14779016646066268</v>
       </c>
       <c r="BM19" t="s">
         <v>45</v>
@@ -5265,7 +5260,7 @@
       </c>
       <c r="AO20" s="9">
         <f t="shared" ref="AO20" si="166">AO6/AK6-1</f>
-        <v>0.1399999999999999</v>
+        <v>0.13588007736943908</v>
       </c>
       <c r="AP20" s="9">
         <f t="shared" ref="AP20" si="167">AP6/AL6-1</f>
@@ -5306,7 +5301,7 @@
       </c>
       <c r="BA20" s="9">
         <f t="shared" si="168"/>
-        <v>0.13840499816244023</v>
+        <v>0.13736126424108797</v>
       </c>
       <c r="BB20" s="9">
         <f t="shared" si="168"/>
@@ -5513,11 +5508,11 @@
       </c>
       <c r="AO21" s="9">
         <f t="shared" si="177"/>
-        <v>0.22</v>
+        <v>0.25608907446068185</v>
       </c>
       <c r="AP21" s="9">
         <f t="shared" si="177"/>
-        <v>0.22000000000000003</v>
+        <v>0.22</v>
       </c>
       <c r="AR21" s="9">
         <f t="shared" ref="AR21:BF21" si="178">AR12/AR11</f>
@@ -5557,7 +5552,7 @@
       </c>
       <c r="BA21" s="9">
         <f t="shared" si="178"/>
-        <v>0.23578737513216599</v>
+        <v>0.24678957239900373</v>
       </c>
       <c r="BB21" s="9">
         <f t="shared" si="178"/>
@@ -5604,7 +5599,7 @@
       </c>
       <c r="BN21" s="5">
         <f>NPV(BN20,BA13:FQ13)</f>
-        <v>8588.676683279371</v>
+        <v>8437.1414327765833</v>
       </c>
     </row>
     <row r="22" spans="2:66" x14ac:dyDescent="0.3">
@@ -5765,11 +5760,11 @@
       </c>
       <c r="AO22" s="9">
         <f t="shared" si="180"/>
-        <v>9.412315174391174E-2</v>
+        <v>7.6663798049340245E-2</v>
       </c>
       <c r="AP22" s="9">
         <f t="shared" si="180"/>
-        <v>8.8498471904090395E-2</v>
+        <v>8.5876822749209172E-2</v>
       </c>
       <c r="AR22" s="9">
         <f t="shared" ref="AR22:BK22" si="181">AR13/AR3</f>
@@ -5809,47 +5804,47 @@
       </c>
       <c r="BA22" s="9">
         <f t="shared" si="181"/>
-        <v>7.6442714743128679E-2</v>
+        <v>7.129420161089578E-2</v>
       </c>
       <c r="BB22" s="9">
         <f t="shared" si="181"/>
-        <v>0.10463299636206912</v>
+        <v>0.10284226888115382</v>
       </c>
       <c r="BC22" s="9">
         <f t="shared" si="181"/>
-        <v>0.10721878671999616</v>
+        <v>0.10550752391031139</v>
       </c>
       <c r="BD22" s="9">
         <f t="shared" si="181"/>
-        <v>0.10857951639939693</v>
+        <v>0.10691262884216378</v>
       </c>
       <c r="BE22" s="9">
         <f t="shared" si="181"/>
-        <v>0.10994109605118962</v>
+        <v>0.10830164271085611</v>
       </c>
       <c r="BF22" s="9">
         <f t="shared" si="181"/>
-        <v>0.11127827939151026</v>
+        <v>0.10966512006460682</v>
       </c>
       <c r="BG22" s="9">
         <f t="shared" si="181"/>
-        <v>0.11259217140136746</v>
+        <v>0.11100424482634948</v>
       </c>
       <c r="BH22" s="9">
         <f t="shared" si="181"/>
-        <v>0.11388379890672193</v>
+        <v>0.11232011672593244</v>
       </c>
       <c r="BI22" s="9">
         <f t="shared" si="181"/>
-        <v>0.11515411657432777</v>
+        <v>0.11361375776402761</v>
       </c>
       <c r="BJ22" s="9">
         <f t="shared" si="181"/>
-        <v>0.11640401244260058</v>
+        <v>0.11488611817471947</v>
       </c>
       <c r="BK22" s="9">
         <f t="shared" si="181"/>
-        <v>0.11763431302361885</v>
+        <v>0.11613808192570503</v>
       </c>
       <c r="BM22" t="s">
         <v>48</v>
@@ -5865,7 +5860,7 @@
       </c>
       <c r="BN23" s="5">
         <f>BN21+BN22</f>
-        <v>9577.9766832793703</v>
+        <v>9426.4414327765826</v>
       </c>
     </row>
     <row r="24" spans="2:66" x14ac:dyDescent="0.3">
@@ -5874,7 +5869,7 @@
       </c>
       <c r="BN24" s="4">
         <f>BN23/BF14</f>
-        <v>171.95649341614669</v>
+        <v>169.54031353914718</v>
       </c>
     </row>
     <row r="25" spans="2:66" x14ac:dyDescent="0.3">
@@ -5883,7 +5878,7 @@
       </c>
       <c r="BN25" s="4">
         <f>Main!D3</f>
-        <v>153.46</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="2:66" x14ac:dyDescent="0.3">
@@ -5892,7 +5887,7 @@
       </c>
       <c r="BN26" s="10">
         <f>BN24/BN25-1</f>
-        <v>0.12052973684443291</v>
+        <v>9.1685329711141961E-3</v>
       </c>
     </row>
     <row r="27" spans="2:66" x14ac:dyDescent="0.3">
